--- a/基本設計/04_認証とホーム_画面基本設計書.xlsx
+++ b/基本設計/04_認証とホーム_画面基本設計書.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rd402be0ddcf44420"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R1ad04be034ea4868"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_画面一覧" sheetId="13" r:id="R748af6b4c1da4c27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_画面遷移" sheetId="14" r:id="Refd55fb3e6524f74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_画面項目定義" sheetId="16" r:id="R3914ce6644db49f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_画面処理概要" sheetId="18" r:id="R112ceb8f9e3d4ed1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-001_ログイン" sheetId="19" r:id="R0152b58a41fe4e82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-002_ホームダッシュボード" sheetId="20" r:id="Ra92c8eafe4c64d0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-026_パスワード変更" sheetId="21" r:id="R343c4c09149b495f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Re77b1a0f674d4fc1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R5a963b64f71649ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_画面一覧" sheetId="13" r:id="R479e2e53626a459a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_画面遷移" sheetId="14" r:id="R6a498d640f3f4e75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_画面項目定義" sheetId="16" r:id="R543bf547d23047d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_画面処理概要" sheetId="18" r:id="Re4f2a2517fc34d9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-001_ログイン" sheetId="19" r:id="R3ac91b1333b64ca1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-002_ホームダッシュボード" sheetId="20" r:id="R25d2fd54859442f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-026_パスワード変更" sheetId="21" r:id="R3317fd5148ec4e31"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1842,10 +1842,7 @@
       <x:c r="F16" s="358"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.8 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
+      <x:c r="A17"/>
       <x:c r="C17"/>
       <x:c r="D17"/>
       <x:c r="E17"/>
@@ -1860,25 +1857,22 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19"/>
-      <x:c r="B19" s="401" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.7 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
-      <x:c r="C19" s="401"/>
-      <x:c r="D19" s="401"/>
-      <x:c r="E19" s="401"/>
-      <x:c r="F19" s="401"/>
-      <x:c r="G19" s="401"/>
-      <x:c r="H19" s="401"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
     </x:row>
     <x:row r="20">
-      <x:c r="B20" s="401"/>
-      <x:c r="C20" s="401"/>
-      <x:c r="D20" s="401"/>
-      <x:c r="E20" s="401"/>
-      <x:c r="F20" s="401"/>
-      <x:c r="G20" s="401"/>
-      <x:c r="H20" s="401"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
     </x:row>
     <x:row r="21">
       <x:c r="B21" s="401"/>
@@ -6176,54 +6170,22 @@
       <x:c r="P31" s="48"/>
     </x:row>
     <x:row r="32" ht="21" customHeight="1">
-      <x:c r="A32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="B32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="C32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="D32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="E32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="F32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="G32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="H32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="I32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="J32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="K32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="L32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="M32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="N32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="O32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="P32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+      <x:c r="I32"/>
+      <x:c r="J32"/>
+      <x:c r="K32"/>
+      <x:c r="L32"/>
+      <x:c r="M32"/>
+      <x:c r="N32"/>
+      <x:c r="O32"/>
+      <x:c r="P32"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -8260,54 +8222,22 @@
       <x:c r="P31" s="48"/>
     </x:row>
     <x:row r="32" ht="21" customHeight="1">
-      <x:c r="A32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="B32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="C32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="D32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="E32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="F32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="G32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="H32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="I32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="J32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="K32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="L32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="M32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="N32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="O32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="P32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+      <x:c r="I32"/>
+      <x:c r="J32"/>
+      <x:c r="K32"/>
+      <x:c r="L32"/>
+      <x:c r="M32"/>
+      <x:c r="N32"/>
+      <x:c r="O32"/>
+      <x:c r="P32"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -9156,54 +9086,22 @@
       <x:c r="P31" s="48"/>
     </x:row>
     <x:row r="32" ht="21" customHeight="1">
-      <x:c r="A32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="B32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="C32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="D32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="E32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="F32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="G32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="H32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="I32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="J32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="K32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="L32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="M32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="N32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="O32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
-      <x:c r="P32" s="58" t="str">
-        <x:v>※ 本Sheetは基本設計の画面ワイヤーフレームです。番号は画面項目定義のNo.と対応します。</x:v>
-      </x:c>
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+      <x:c r="I32"/>
+      <x:c r="J32"/>
+      <x:c r="K32"/>
+      <x:c r="L32"/>
+      <x:c r="M32"/>
+      <x:c r="N32"/>
+      <x:c r="O32"/>
+      <x:c r="P32"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/基本設計/04_認証とホーム_画面基本設計書.xlsx
+++ b/基本設計/04_認証とホーム_画面基本設計書.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Re77b1a0f674d4fc1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R5a963b64f71649ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_画面一覧" sheetId="13" r:id="R479e2e53626a459a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_画面遷移" sheetId="14" r:id="R6a498d640f3f4e75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_画面項目定義" sheetId="16" r:id="R543bf547d23047d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_画面処理概要" sheetId="18" r:id="Re4f2a2517fc34d9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-001_ログイン" sheetId="19" r:id="R3ac91b1333b64ca1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-002_ホームダッシュボード" sheetId="20" r:id="R25d2fd54859442f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-026_パスワード変更" sheetId="21" r:id="R3317fd5148ec4e31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rcf4e0ac6a1384732"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Ra8b680e4e7f0475d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_画面項目定義" sheetId="16" r:id="Rfbee701f09d2466d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_画面処理概要" sheetId="18" r:id="Ra861883efd074369"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-001_ログイン" sheetId="19" r:id="Rb8b90cceb5364bb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-002_ホームダッシュボード" sheetId="20" r:id="R454bd0d76d6b473b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WF_SCR-026_パスワード変更" sheetId="21" r:id="R1cce753308604529"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_対象画面INDEX" sheetId="22" r:id="R84fd145086384f56"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -24,7 +23,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="34">
+  <x:fonts count="45">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -215,8 +214,69 @@
       <x:color rgb="FF1F1F1F"/>
       <x:name val="Yu Gothic"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F1F1F"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="14"/>
+      <x:color rgb="FF1F4E78"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF1F4E78"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF333333"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="9"/>
+      <x:color rgb="FF333333"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="9"/>
+      <x:color rgb="FF7F6000"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Meiryo"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF333333"/>
+      <x:name val="Meiryo"/>
+    </x:font>
+    <x:font>
+      <x:sz val="9"/>
+      <x:color rgb="FF666666"/>
+      <x:name val="Meiryo"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF18283A"/>
+      <x:name val="Yu Gothic"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="17"/>
+      <x:color rgb="FF193C61"/>
+      <x:name val="Yu Gothic"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="31">
+  <x:fills count="40">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -368,8 +428,53 @@
         <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F6F9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCEAF5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD1E4F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF7E6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7E6E6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF234F77"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF1F5FA"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="25">
+  <x:borders count="27">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -545,11 +650,39 @@
         <x:color rgb="FF8EA9C1"/>
       </x:right>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF9FBAD0"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF9FBAD0"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF9FBAD0"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF9FBAD0"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="402">
+  <x:cellXfs count="483">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1414,6 +1547,205 @@
     <x:xf numFmtId="0" fontId="33" fillId="30" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="34" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="34" fillId="31" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="34" fillId="31" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="34" fillId="31" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="34" fillId="31" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="35" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="35" fillId="32" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="35" fillId="32" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="35" fillId="32" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="35" fillId="32" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="36" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="36" fillId="33" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="36" fillId="33" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="36" fillId="33" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="36" fillId="33" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="37" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="37" fillId="34" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="37" fillId="34" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="37" fillId="34" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="37" fillId="34" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="38" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="38" fillId="34" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="38" fillId="34" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="38" fillId="34" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="38" fillId="34" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="38" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="38" fillId="31" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="38" fillId="31" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="38" fillId="31" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="38" fillId="31" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="39" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="39" fillId="35" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="39" fillId="35" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="39" fillId="35" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="39" fillId="35" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="36" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="36" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="36" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="36" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="40" fillId="36" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="40" fillId="36" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="40" fillId="36" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="40" fillId="36" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="40" fillId="36" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="40" fillId="36" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="37" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="37" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="37" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="37" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="41" fillId="37" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="41" fillId="37" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="41" fillId="37" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="41" fillId="37" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="41" fillId="37" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="41" fillId="37" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="42" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0"/>
+    <x:xf numFmtId="0" fontId="42" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="42" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="42" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="32" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="43" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="43" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="43" fillId="39" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1782,8 +2114,8 @@
     </x:row>
     <x:row r="11">
       <x:c r="B11"/>
-      <x:c r="C11" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="C11" s="402" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="D11"/>
       <x:c r="E11"/>
@@ -1792,8 +2124,8 @@
       <x:c r="H11"/>
     </x:row>
     <x:row r="12">
-      <x:c r="C12" s="396" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="C12" s="468" t="str">
+        <x:v>Document ID</x:v>
       </x:c>
       <x:c r="D12" s="358" t="str">
         <x:v>CW-BD-SCR-AUTH</x:v>
@@ -1805,8 +2137,8 @@
       <x:c r="C13" s="396" t="str">
         <x:v>版数</x:v>
       </x:c>
-      <x:c r="D13" s="358" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="D13" s="469" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="E13" s="358"/>
       <x:c r="F13" s="358"/>
@@ -1815,8 +2147,8 @@
       <x:c r="C14" s="396" t="str">
         <x:v>改訂日</x:v>
       </x:c>
-      <x:c r="D14" s="358" t="str">
-        <x:v>2026-08-12</x:v>
+      <x:c r="D14" s="469" t="str">
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="E14" s="358"/>
       <x:c r="F14" s="358"/>
@@ -1835,23 +2167,29 @@
       <x:c r="C16" s="396" t="str">
         <x:v>状態</x:v>
       </x:c>
-      <x:c r="D16" s="358" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="D16" s="469" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="E16" s="358"/>
       <x:c r="F16" s="358"/>
     </x:row>
-    <x:row r="17">
-      <x:c r="A17"/>
-      <x:c r="C17"/>
-      <x:c r="D17"/>
+    <x:row r="17" ht="26" customHeight="1">
+      <x:c r="A17" s="471"/>
+      <x:c r="B17" s="471"/>
+      <x:c r="C17" s="471"/>
+      <x:c r="D17" s="471"/>
       <x:c r="E17"/>
       <x:c r="F17"/>
     </x:row>
-    <x:row r="18">
-      <x:c r="A18"/>
-      <x:c r="C18"/>
-      <x:c r="D18"/>
+    <x:row r="18" ht="26" customHeight="1">
+      <x:c r="A18" s="471"/>
+      <x:c r="B18" s="471"/>
+      <x:c r="C18" s="471" t="str">
+        <x:v>Baseline ID</x:v>
+      </x:c>
+      <x:c r="D18" s="471" t="str">
+        <x:v>BL-2026-09-24</x:v>
+      </x:c>
       <x:c r="E18"/>
       <x:c r="F18"/>
     </x:row>
@@ -1959,41 +2297,29 @@
       <x:c r="G2" s="339"/>
       <x:c r="H2" s="339"/>
     </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="341" t="str">
-        <x:v>システム名</x:v>
-      </x:c>
-      <x:c r="B3" s="326" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="C3" s="326"/>
-      <x:c r="D3" s="341" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="E3" s="326" t="str">
-        <x:v>DOCUMENT-REVISION</x:v>
-      </x:c>
-      <x:c r="F3" s="326"/>
-      <x:c r="G3" s="326"/>
-      <x:c r="H3" s="326"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="341" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="326" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
-      <x:c r="C4" s="326"/>
-      <x:c r="D4" s="341" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
-      <x:c r="E4" s="326" t="str">
-        <x:v>2026-08-12</x:v>
-      </x:c>
-      <x:c r="F4" s="326"/>
-      <x:c r="G4" s="326"/>
-      <x:c r="H4" s="326"/>
+    <x:row r="3" ht="24" customHeight="1">
+      <x:c r="A3" s="472" t="str">
+        <x:v>システム名：Company WorkHub</x:v>
+      </x:c>
+      <x:c r="B3" s="286"/>
+      <x:c r="C3" s="286"/>
+      <x:c r="D3" s="472"/>
+      <x:c r="E3" s="286"/>
+      <x:c r="F3" s="286"/>
+      <x:c r="G3" s="286"/>
+      <x:c r="H3" s="286"/>
+    </x:row>
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="472" t="str">
+        <x:v>版数：Ver.2.5    改訂日：2026-09-24    Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="B4" s="286"/>
+      <x:c r="C4" s="286"/>
+      <x:c r="D4" s="472"/>
+      <x:c r="E4" s="286"/>
+      <x:c r="F4" s="286"/>
+      <x:c r="G4" s="286"/>
+      <x:c r="H4" s="286"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5"/>
@@ -2025,7 +2351,7 @@
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="C7" s="348" t="str">
-        <x:v>2026-08-12</x:v>
+        <x:v>改訂内容</x:v>
       </x:c>
       <x:c r="D7" s="348" t="str">
         <x:v>作成者</x:v>
@@ -2063,7 +2389,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G8" s="290" t="str">
-        <x:v>作成済</x:v>
+        <x:v>作成中</x:v>
       </x:c>
       <x:c r="H8" s="290" t="str">
         <x:v>基本設計初版</x:v>
@@ -2089,7 +2415,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G9" s="290" t="str">
-        <x:v>作成済</x:v>
+        <x:v>作成中</x:v>
       </x:c>
       <x:c r="H9" s="290" t="str">
         <x:v>WF_SCR追加</x:v>
@@ -2115,7 +2441,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G10" s="290" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H10" s="290" t="str">
         <x:v>Leader Review後Baseline化</x:v>
@@ -2141,7 +2467,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G11" s="290" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H11" s="290" t="str">
         <x:v>再監査指摘対応</x:v>
@@ -2167,7 +2493,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G12" s="290" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H12" s="290" t="str">
         <x:v>再監査第2回指摘対応</x:v>
@@ -2192,8 +2518,8 @@
       <x:c r="F13" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="G13" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="G13" s="402" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H13" t="str">
         <x:v>再監査残項対応</x:v>
@@ -2218,8 +2544,8 @@
       <x:c r="F14" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="G14" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="G14" s="402" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H14" t="str">
         <x:v>再Review指摘対応</x:v>
@@ -2244,835 +2570,159 @@
       <x:c r="F15" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="G15" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="G15" s="402" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H15" t="str">
         <x:v>最大10回の反復監査対応</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>1.9</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>2026-08-17</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>画面一覧・遷移・項目・処理・線框図を再設計し不整合を解消</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F16" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G16" s="402" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H16" t="str">
+        <x:v>04全指摘対応</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>2.0</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>七項目Review指摘対応：画面・API・DB項目、論理削除、認証限流、日報関連Task、Baseline判定を整合</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F17" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G17" t="str">
+        <x:v>レビュー済</x:v>
+      </x:c>
+      <x:c r="H17" t="str">
+        <x:v>Leader最終承認待ち</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="110" customHeight="1">
+      <x:c r="A18" s="467" t="str">
+        <x:v>Ver.2.3</x:v>
+      </x:c>
+      <x:c r="B18" s="467" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="C18" s="467" t="str">
+        <x:v>内容・関連Reviewの既確定仕様を整合。業務未決事項は承認待ちとして管理。</x:v>
+      </x:c>
+      <x:c r="D18" s="467" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E18" s="467" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F18" s="467" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G18" s="467" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H18" s="467" t="str">
+        <x:v>2026-09-18指摘対応。正式承認を示すものではない。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="40" customHeight="1">
+      <x:c r="A19" s="467" t="str">
+        <x:v>Ver.2.4</x:v>
+      </x:c>
+      <x:c r="B19" s="467" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="C19" s="467" t="str">
+        <x:v>待確認12項目の方針選定、業務/API/DB/画面/運用を連動修正。章立て維持。</x:v>
+      </x:c>
+      <x:c r="D19" s="467" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E19" s="467" t="str">
+        <x:v>未実施</x:v>
+      </x:c>
+      <x:c r="F19" s="467" t="str">
+        <x:v>未承認</x:v>
+      </x:c>
+      <x:c r="G19" s="467" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H19" s="467" t="str">
+        <x:v>一般社内管理Systemの範囲。旧版はBackup保管。</x:v>
+      </x:c>
+      <x:c r="I19" s="467"/>
+      <x:c r="J19" s="467"/>
+      <x:c r="K19" s="467"/>
+      <x:c r="L19" s="467"/>
+    </x:row>
+    <x:row r="20" ht="100" customHeight="1">
+      <x:c r="A20" s="471" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="B20" s="471" t="str">
+        <x:v>2026-09-24</x:v>
+      </x:c>
+      <x:c r="C20" s="471" t="str">
+        <x:v>共通規則・正本参照・構成・文書管理を統合修正。Baseline承認前の最終整合修正。</x:v>
+      </x:c>
+      <x:c r="D20" s="471" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="E20" s="471" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F20" s="471" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G20" s="471" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="H20" s="471" t="str">
+        <x:v>BL-2026-09-24。責任者・Review者・承認者はProject Leaderが記入。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H2"/>
-    <x:mergeCell ref="A3:B3"/>
-    <x:mergeCell ref="C3:D3"/>
-    <x:mergeCell ref="E3:F3"/>
-    <x:mergeCell ref="G3:H3"/>
-    <x:mergeCell ref="A4:B4"/>
-    <x:mergeCell ref="C4:D4"/>
-    <x:mergeCell ref="E4:F4"/>
-    <x:mergeCell ref="G4:H4"/>
     <x:mergeCell ref="A6:H6"/>
+    <x:mergeCell ref="A3:H3"/>
+    <x:mergeCell ref="A4:H4"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="28" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="20" t="str">
-        <x:v>画面一覧</x:v>
-      </x:c>
-      <x:c r="B1" s="20"/>
-      <x:c r="C1" s="20"/>
-      <x:c r="D1" s="20"/>
-      <x:c r="E1" s="20"/>
-      <x:c r="F1" s="20"/>
-      <x:c r="G1" s="20"/>
-      <x:c r="H1" s="20"/>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="20"/>
-      <x:c r="B2" s="20"/>
-      <x:c r="C2" s="20"/>
-      <x:c r="D2" s="20"/>
-      <x:c r="E2" s="20"/>
-      <x:c r="F2" s="20"/>
-      <x:c r="G2" s="20"/>
-      <x:c r="H2" s="20"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="23" t="str">
-        <x:v>システム名</x:v>
-      </x:c>
-      <x:c r="B3" s="23"/>
-      <x:c r="C3" s="21" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="D3" s="21"/>
-      <x:c r="E3" s="23" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="F3" s="23"/>
-      <x:c r="G3" s="21" t="str">
-        <x:v>CW-BD-040</x:v>
-      </x:c>
-      <x:c r="H3" s="21"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="23" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="23"/>
-      <x:c r="C4" s="21" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
-      <x:c r="D4" s="21"/>
-      <x:c r="E4" s="23" t="str">
-        <x:v>作成日</x:v>
-      </x:c>
-      <x:c r="F4" s="23"/>
-      <x:c r="G4" s="24" t="n">
-        <x:v>46239</x:v>
-      </x:c>
-      <x:c r="H4" s="24"/>
-    </x:row>
-    <x:row r="6" ht="22" customHeight="1">
-      <x:c r="A6" s="26" t="str">
-        <x:v>1. 画面一覧</x:v>
-      </x:c>
-      <x:c r="B6" s="26"/>
-      <x:c r="C6" s="26"/>
-      <x:c r="D6" s="26"/>
-      <x:c r="E6" s="26"/>
-      <x:c r="F6" s="26"/>
-      <x:c r="G6" s="26"/>
-      <x:c r="H6" s="26"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="31" t="str">
-        <x:v>画面ID</x:v>
-      </x:c>
-      <x:c r="B7" s="31" t="str">
-        <x:v>画面名</x:v>
-      </x:c>
-      <x:c r="C7" s="31" t="str">
-        <x:v>メニュー</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="str">
-        <x:v>利用ロール</x:v>
-      </x:c>
-      <x:c r="E7" s="31" t="str">
-        <x:v>種別</x:v>
-      </x:c>
-      <x:c r="F7" s="31" t="str">
-        <x:v>主要操作</x:v>
-      </x:c>
-      <x:c r="G7" s="31" t="str">
-        <x:v>関連機能</x:v>
-      </x:c>
-      <x:c r="H7" s="31" t="str">
-        <x:v>備考</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="33" t="str">
-        <x:v>SCR-001</x:v>
-      </x:c>
-      <x:c r="B8" s="33" t="str">
-        <x:v>ログイン</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="str">
-        <x:v>認証</x:v>
-      </x:c>
-      <x:c r="D8" s="33" t="str">
-        <x:v>全員</x:v>
-      </x:c>
-      <x:c r="E8" s="33" t="str">
-        <x:v>入力</x:v>
-      </x:c>
-      <x:c r="F8" s="33" t="str">
-        <x:v>M01</x:v>
-      </x:c>
-      <x:c r="G8" s="33" t="str">
-        <x:v>保存/取消</x:v>
-      </x:c>
-      <x:c r="H8" s="33"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="33" t="str">
-        <x:v>SCR-002</x:v>
-      </x:c>
-      <x:c r="B9" s="33" t="str">
-        <x:v>ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="str">
-        <x:v>ホーム</x:v>
-      </x:c>
-      <x:c r="D9" s="33" t="str">
-        <x:v>全員</x:v>
-      </x:c>
-      <x:c r="E9" s="33" t="str">
-        <x:v>照会</x:v>
-      </x:c>
-      <x:c r="F9" s="33" t="str">
-        <x:v>M02</x:v>
-      </x:c>
-      <x:c r="G9" s="33" t="str">
-        <x:v>表示/操作</x:v>
-      </x:c>
-      <x:c r="H9" s="33"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="33" t="str">
-        <x:v>SCR-026</x:v>
-      </x:c>
-      <x:c r="B10" s="33" t="str">
-        <x:v>パスワード変更</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="str">
-        <x:v>ユーザー設定</x:v>
-      </x:c>
-      <x:c r="D10" s="33" t="str">
-        <x:v>全員</x:v>
-      </x:c>
-      <x:c r="E10" s="33" t="str">
-        <x:v>入力</x:v>
-      </x:c>
-      <x:c r="F10" s="33" t="str">
-        <x:v>M01</x:v>
-      </x:c>
-      <x:c r="G10" s="33" t="str">
-        <x:v>保存/取消</x:v>
-      </x:c>
-      <x:c r="H10" s="33"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11"/>
-      <x:c r="B11"/>
-      <x:c r="C11"/>
-      <x:c r="D11"/>
-      <x:c r="E11"/>
-      <x:c r="F11"/>
-      <x:c r="G11"/>
-      <x:c r="H11"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12"/>
-      <x:c r="B12"/>
-      <x:c r="C12"/>
-      <x:c r="D12"/>
-      <x:c r="E12"/>
-      <x:c r="F12"/>
-      <x:c r="G12"/>
-      <x:c r="H12"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13"/>
-      <x:c r="B13"/>
-      <x:c r="C13"/>
-      <x:c r="D13"/>
-      <x:c r="E13"/>
-      <x:c r="F13"/>
-      <x:c r="G13"/>
-      <x:c r="H13"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14"/>
-      <x:c r="B14"/>
-      <x:c r="C14"/>
-      <x:c r="D14"/>
-      <x:c r="E14"/>
-      <x:c r="F14"/>
-      <x:c r="G14"/>
-      <x:c r="H14"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15"/>
-      <x:c r="B15"/>
-      <x:c r="C15"/>
-      <x:c r="D15"/>
-      <x:c r="E15"/>
-      <x:c r="F15"/>
-      <x:c r="G15"/>
-      <x:c r="H15"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16"/>
-      <x:c r="B16"/>
-      <x:c r="C16"/>
-      <x:c r="D16"/>
-      <x:c r="E16"/>
-      <x:c r="F16"/>
-      <x:c r="G16"/>
-      <x:c r="H16"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17"/>
-      <x:c r="B17"/>
-      <x:c r="C17"/>
-      <x:c r="D17"/>
-      <x:c r="E17"/>
-      <x:c r="F17"/>
-      <x:c r="G17"/>
-      <x:c r="H17"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18"/>
-      <x:c r="B18"/>
-      <x:c r="C18"/>
-      <x:c r="D18"/>
-      <x:c r="E18"/>
-      <x:c r="F18"/>
-      <x:c r="G18"/>
-      <x:c r="H18"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19"/>
-      <x:c r="B19"/>
-      <x:c r="C19"/>
-      <x:c r="D19"/>
-      <x:c r="E19"/>
-      <x:c r="F19"/>
-      <x:c r="G19"/>
-      <x:c r="H19"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20"/>
-      <x:c r="B20"/>
-      <x:c r="C20"/>
-      <x:c r="D20"/>
-      <x:c r="E20"/>
-      <x:c r="F20"/>
-      <x:c r="G20"/>
-      <x:c r="H20"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21"/>
-      <x:c r="B21"/>
-      <x:c r="C21"/>
-      <x:c r="D21"/>
-      <x:c r="E21"/>
-      <x:c r="F21"/>
-      <x:c r="G21"/>
-      <x:c r="H21"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22"/>
-      <x:c r="B22"/>
-      <x:c r="C22"/>
-      <x:c r="D22"/>
-      <x:c r="E22"/>
-      <x:c r="F22"/>
-      <x:c r="G22"/>
-      <x:c r="H22"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23"/>
-      <x:c r="B23"/>
-      <x:c r="C23"/>
-      <x:c r="D23"/>
-      <x:c r="E23"/>
-      <x:c r="F23"/>
-      <x:c r="G23"/>
-      <x:c r="H23"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24"/>
-      <x:c r="B24"/>
-      <x:c r="C24"/>
-      <x:c r="D24"/>
-      <x:c r="E24"/>
-      <x:c r="F24"/>
-      <x:c r="G24"/>
-      <x:c r="H24"/>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25"/>
-      <x:c r="B25"/>
-      <x:c r="C25"/>
-      <x:c r="D25"/>
-      <x:c r="E25"/>
-      <x:c r="F25"/>
-      <x:c r="G25"/>
-      <x:c r="H25"/>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26"/>
-      <x:c r="B26"/>
-      <x:c r="C26"/>
-      <x:c r="D26"/>
-      <x:c r="E26"/>
-      <x:c r="F26"/>
-      <x:c r="G26"/>
-      <x:c r="H26"/>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27"/>
-      <x:c r="B27"/>
-      <x:c r="C27"/>
-      <x:c r="D27"/>
-      <x:c r="E27"/>
-      <x:c r="F27"/>
-      <x:c r="G27"/>
-      <x:c r="H27"/>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28"/>
-      <x:c r="B28"/>
-      <x:c r="C28"/>
-      <x:c r="D28"/>
-      <x:c r="E28"/>
-      <x:c r="F28"/>
-      <x:c r="G28"/>
-      <x:c r="H28"/>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29"/>
-      <x:c r="B29"/>
-      <x:c r="C29"/>
-      <x:c r="D29"/>
-      <x:c r="E29"/>
-      <x:c r="F29"/>
-      <x:c r="G29"/>
-      <x:c r="H29"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30"/>
-      <x:c r="B30"/>
-      <x:c r="C30"/>
-      <x:c r="D30"/>
-      <x:c r="E30"/>
-      <x:c r="F30"/>
-      <x:c r="G30"/>
-      <x:c r="H30"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31"/>
-      <x:c r="B31"/>
-      <x:c r="C31"/>
-      <x:c r="D31"/>
-      <x:c r="E31"/>
-      <x:c r="F31"/>
-      <x:c r="G31"/>
-      <x:c r="H31"/>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32"/>
-      <x:c r="B32"/>
-      <x:c r="C32"/>
-      <x:c r="D32"/>
-      <x:c r="E32"/>
-      <x:c r="F32"/>
-      <x:c r="G32"/>
-      <x:c r="H32"/>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33"/>
-      <x:c r="B33"/>
-      <x:c r="C33"/>
-      <x:c r="D33"/>
-      <x:c r="E33"/>
-      <x:c r="F33"/>
-      <x:c r="G33"/>
-      <x:c r="H33"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:H2"/>
-    <x:mergeCell ref="A3:B3"/>
-    <x:mergeCell ref="C3:D3"/>
-    <x:mergeCell ref="E3:F3"/>
-    <x:mergeCell ref="G3:H3"/>
-    <x:mergeCell ref="A4:B4"/>
-    <x:mergeCell ref="C4:D4"/>
-    <x:mergeCell ref="E4:F4"/>
-    <x:mergeCell ref="G4:H4"/>
-    <x:mergeCell ref="A6:H6"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="7" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="26" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="40" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="20" t="str">
-        <x:v>画面遷移</x:v>
-      </x:c>
-      <x:c r="B1" s="20"/>
-      <x:c r="C1" s="20"/>
-      <x:c r="D1" s="20"/>
-      <x:c r="E1" s="20"/>
-      <x:c r="F1" s="20"/>
-      <x:c r="G1" s="20"/>
-      <x:c r="H1" s="20"/>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="20"/>
-      <x:c r="B2" s="20"/>
-      <x:c r="C2" s="20"/>
-      <x:c r="D2" s="20"/>
-      <x:c r="E2" s="20"/>
-      <x:c r="F2" s="20"/>
-      <x:c r="G2" s="20"/>
-      <x:c r="H2" s="20"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="23" t="str">
-        <x:v>システム名</x:v>
-      </x:c>
-      <x:c r="B3" s="23"/>
-      <x:c r="C3" s="21" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="D3" s="21"/>
-      <x:c r="E3" s="23" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="F3" s="23"/>
-      <x:c r="G3" s="21" t="str">
-        <x:v>CW-BD-041</x:v>
-      </x:c>
-      <x:c r="H3" s="21"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="23" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="23"/>
-      <x:c r="C4" s="21" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
-      <x:c r="D4" s="21"/>
-      <x:c r="E4" s="23" t="str">
-        <x:v>作成日</x:v>
-      </x:c>
-      <x:c r="F4" s="23"/>
-      <x:c r="G4" s="24" t="n">
-        <x:v>46239</x:v>
-      </x:c>
-      <x:c r="H4" s="24"/>
-    </x:row>
-    <x:row r="6" ht="22" customHeight="1">
-      <x:c r="A6" s="26" t="str">
-        <x:v>1. 主要画面遷移</x:v>
-      </x:c>
-      <x:c r="B6" s="26"/>
-      <x:c r="C6" s="26"/>
-      <x:c r="D6" s="26"/>
-      <x:c r="E6" s="26"/>
-      <x:c r="F6" s="26"/>
-      <x:c r="G6" s="26"/>
-      <x:c r="H6" s="26"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="31" t="str">
-        <x:v>No.</x:v>
-      </x:c>
-      <x:c r="B7" s="31" t="str">
-        <x:v>遷移元</x:v>
-      </x:c>
-      <x:c r="C7" s="31" t="str">
-        <x:v>イベント</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="str">
-        <x:v>遷移先</x:v>
-      </x:c>
-      <x:c r="E7" s="31" t="str">
-        <x:v>引継情報</x:v>
-      </x:c>
-      <x:c r="F7" s="31" t="str">
-        <x:v>権限・条件</x:v>
-      </x:c>
-      <x:c r="G7" s="31" t="str">
-        <x:v>戻る動作</x:v>
-      </x:c>
-      <x:c r="H7" s="31" t="str">
-        <x:v>備考</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B8" s="33" t="str">
-        <x:v>未認証</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="str">
-        <x:v>URLアクセス</x:v>
-      </x:c>
-      <x:c r="D8" s="33" t="str">
-        <x:v>SCR-001</x:v>
-      </x:c>
-      <x:c r="E8" s="33" t="str">
-        <x:v>redirect URL</x:v>
-      </x:c>
-      <x:c r="F8" s="33" t="str">
-        <x:v>Tokenなし/無効</x:v>
-      </x:c>
-      <x:c r="G8" s="33" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="H8" s="33"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B9" s="33" t="str">
-        <x:v>SCR-001</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="str">
-        <x:v>ログイン成功</x:v>
-      </x:c>
-      <x:c r="D9" s="33" t="str">
-        <x:v>SCR-002</x:v>
-      </x:c>
-      <x:c r="E9" s="33" t="str">
-        <x:v>ユーザー/権限</x:v>
-      </x:c>
-      <x:c r="F9" s="33" t="str">
-        <x:v>有効ユーザー</x:v>
-      </x:c>
-      <x:c r="G9" s="33" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="H9" s="33"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B10" s="33" t="str">
-        <x:v>共通Header</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="str">
-        <x:v>ログアウト</x:v>
-      </x:c>
-      <x:c r="D10" s="33" t="str">
-        <x:v>SCR-001</x:v>
-      </x:c>
-      <x:c r="E10" s="33" t="str">
-        <x:v>なし</x:v>
-      </x:c>
-      <x:c r="F10" s="33" t="str">
-        <x:v>全員</x:v>
-      </x:c>
-      <x:c r="G10" s="33" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="H10" s="33" t="str">
-        <x:v>確認あり</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B11" s="33" t="str">
-        <x:v>SCR-002</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="str">
-        <x:v>通知アイコン</x:v>
-      </x:c>
-      <x:c r="D11" s="33" t="str">
-        <x:v>SCR-022</x:v>
-      </x:c>
-      <x:c r="E11" s="33" t="str">
-        <x:v>なし</x:v>
-      </x:c>
-      <x:c r="F11" s="33" t="str">
-        <x:v>全員</x:v>
-      </x:c>
-      <x:c r="G11" s="33" t="str">
-        <x:v>元画面へ</x:v>
-      </x:c>
-      <x:c r="H11" s="33"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B12" s="33" t="str">
-        <x:v>共通ユーザーMenu</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="str">
-        <x:v>Password変更</x:v>
-      </x:c>
-      <x:c r="D12" s="33" t="str">
-        <x:v>SCR-026</x:v>
-      </x:c>
-      <x:c r="E12" s="33" t="str">
-        <x:v>なし</x:v>
-      </x:c>
-      <x:c r="F12" s="33" t="str">
-        <x:v>全員</x:v>
-      </x:c>
-      <x:c r="G12" s="33" t="str">
-        <x:v>元画面へ</x:v>
-      </x:c>
-      <x:c r="H12" s="33"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B13" s="33" t="str">
-        <x:v>任意画面</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="str">
-        <x:v>Token期限切れ</x:v>
-      </x:c>
-      <x:c r="D13" s="33" t="str">
-        <x:v>SCR-001</x:v>
-      </x:c>
-      <x:c r="E13" s="33" t="str">
-        <x:v>redirect URL</x:v>
-      </x:c>
-      <x:c r="F13" s="33" t="str">
-        <x:v>Refresh失敗</x:v>
-      </x:c>
-      <x:c r="G13" s="33" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="H13" s="33" t="str">
-        <x:v>MSG-E-005</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14"/>
-      <x:c r="B14"/>
-      <x:c r="C14"/>
-      <x:c r="D14"/>
-      <x:c r="E14"/>
-      <x:c r="F14"/>
-      <x:c r="G14"/>
-      <x:c r="H14"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15"/>
-      <x:c r="B15"/>
-      <x:c r="C15"/>
-      <x:c r="D15"/>
-      <x:c r="E15"/>
-      <x:c r="F15"/>
-      <x:c r="G15"/>
-      <x:c r="H15"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16"/>
-      <x:c r="B16"/>
-      <x:c r="C16"/>
-      <x:c r="D16"/>
-      <x:c r="E16"/>
-      <x:c r="F16"/>
-      <x:c r="G16"/>
-      <x:c r="H16"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17"/>
-      <x:c r="B17"/>
-      <x:c r="C17"/>
-      <x:c r="D17"/>
-      <x:c r="E17"/>
-      <x:c r="F17"/>
-      <x:c r="G17"/>
-      <x:c r="H17"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18"/>
-      <x:c r="B18"/>
-      <x:c r="C18"/>
-      <x:c r="D18"/>
-      <x:c r="E18"/>
-      <x:c r="F18"/>
-      <x:c r="G18"/>
-      <x:c r="H18"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19"/>
-      <x:c r="B19"/>
-      <x:c r="C19"/>
-      <x:c r="D19"/>
-      <x:c r="E19"/>
-      <x:c r="F19"/>
-      <x:c r="G19"/>
-      <x:c r="H19"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20"/>
-      <x:c r="B20"/>
-      <x:c r="C20"/>
-      <x:c r="D20"/>
-      <x:c r="E20"/>
-      <x:c r="F20"/>
-      <x:c r="G20"/>
-      <x:c r="H20"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21"/>
-      <x:c r="B21"/>
-      <x:c r="C21"/>
-      <x:c r="D21"/>
-      <x:c r="E21"/>
-      <x:c r="F21"/>
-      <x:c r="G21"/>
-      <x:c r="H21"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22"/>
-      <x:c r="B22"/>
-      <x:c r="C22"/>
-      <x:c r="D22"/>
-      <x:c r="E22"/>
-      <x:c r="F22"/>
-      <x:c r="G22"/>
-      <x:c r="H22"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23"/>
-      <x:c r="B23"/>
-      <x:c r="C23"/>
-      <x:c r="D23"/>
-      <x:c r="E23"/>
-      <x:c r="F23"/>
-      <x:c r="G23"/>
-      <x:c r="H23"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:H2"/>
-    <x:mergeCell ref="A3:B3"/>
-    <x:mergeCell ref="C3:D3"/>
-    <x:mergeCell ref="E3:F3"/>
-    <x:mergeCell ref="G3:H3"/>
-    <x:mergeCell ref="A4:B4"/>
-    <x:mergeCell ref="C4:D4"/>
-    <x:mergeCell ref="E4:F4"/>
-    <x:mergeCell ref="G4:H4"/>
-    <x:mergeCell ref="A6:H6"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -3124,15 +2774,11 @@
       <x:c r="A3" s="285" t="str">
         <x:v>システム名</x:v>
       </x:c>
-      <x:c r="B3" s="286" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
+      <x:c r="B3" s="286" t="str"/>
       <x:c r="C3" s="286"/>
       <x:c r="D3" s="286"/>
       <x:c r="E3" s="286"/>
-      <x:c r="F3" s="285" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
+      <x:c r="F3" s="285" t="str"/>
       <x:c r="G3" s="286" t="str">
         <x:v>CW-BD-043</x:v>
       </x:c>
@@ -3143,20 +2789,16 @@
       <x:c r="L3" s="286"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="285" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="286" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
+      <x:c r="A4" s="472" t="str">
+        <x:v>版数：Ver.2.5</x:v>
+      </x:c>
+      <x:c r="B4" s="286"/>
       <x:c r="C4" s="286"/>
       <x:c r="D4" s="286"/>
       <x:c r="E4" s="286"/>
-      <x:c r="F4" s="285" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
+      <x:c r="F4" s="285" t="str"/>
       <x:c r="G4" s="286" t="str">
-        <x:v>2026-08-12</x:v>
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="H4" s="286"/>
       <x:c r="I4" s="286"/>
@@ -3228,9 +2870,7 @@
       <x:c r="K7" s="289" t="str">
         <x:v>関連API.Field</x:v>
       </x:c>
-      <x:c r="L7" s="289" t="str">
-        <x:v>DB/Response</x:v>
-      </x:c>
+      <x:c r="L7" s="289"/>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
       <x:c r="A8" s="290" t="str">
@@ -3264,11 +2904,9 @@
         <x:v>VAL-001, VAL-002</x:v>
       </x:c>
       <x:c r="K8" s="290" t="str">
-        <x:v>API-AUTH-001.username</x:v>
-      </x:c>
-      <x:c r="L8" s="290" t="str">
-        <x:v>users.username</x:v>
-      </x:c>
+        <x:v>API-AUTH-001.request.body.username</x:v>
+      </x:c>
+      <x:c r="L8" s="290"/>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
       <x:c r="A9" s="290" t="str">
@@ -3302,11 +2940,9 @@
         <x:v>VAL-001/ログ出力禁止</x:v>
       </x:c>
       <x:c r="K9" s="290" t="str">
-        <x:v>API-AUTH-001.password</x:v>
-      </x:c>
-      <x:c r="L9" s="290" t="str">
-        <x:v>非保存</x:v>
-      </x:c>
+        <x:v>API-AUTH-001.request.body.password</x:v>
+      </x:c>
+      <x:c r="L9" s="290"/>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
       <x:c r="A10" s="290" t="str">
@@ -3316,86 +2952,82 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C10" s="290" t="str">
-        <x:v>keepLogin</x:v>
+        <x:v>btnLogin</x:v>
       </x:c>
       <x:c r="D10" s="290" t="str">
-        <x:v>ログイン保持</x:v>
+        <x:v>ログイン</x:v>
       </x:c>
       <x:c r="E10" s="290" t="str">
-        <x:v>Check</x:v>
+        <x:v>Button</x:v>
       </x:c>
       <x:c r="F10" s="290" t="str">
-        <x:v>I</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="G10" s="290" t="str">
         <x:v>-</x:v>
       </x:c>
       <x:c r="H10" s="290" t="str">
-        <x:v>Boolean</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="I10" s="290" t="str">
-        <x:v>OFF</x:v>
+        <x:v>活性</x:v>
       </x:c>
       <x:c r="J10" s="290" t="str">
-        <x:v>端末共有時注意</x:v>
+        <x:v>送信中非活性</x:v>
       </x:c>
       <x:c r="K10" s="290" t="str">
-        <x:v>Front only</x:v>
-      </x:c>
-      <x:c r="L10" s="290" t="str">
-        <x:v>-</x:v>
-      </x:c>
+        <x:v>API-AUTH-001</x:v>
+      </x:c>
+      <x:c r="L10" s="290"/>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">
       <x:c r="A11" s="290" t="str">
-        <x:v>SCR-001</x:v>
+        <x:v>SCR-002</x:v>
       </x:c>
       <x:c r="B11" s="290" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C11" s="290" t="str">
-        <x:v>btnLogin</x:v>
+        <x:v>periodFrom</x:v>
       </x:c>
       <x:c r="D11" s="290" t="str">
-        <x:v>ログイン</x:v>
+        <x:v>集計開始日</x:v>
       </x:c>
       <x:c r="E11" s="290" t="str">
-        <x:v>Button</x:v>
+        <x:v>Date</x:v>
       </x:c>
       <x:c r="F11" s="290" t="str">
-        <x:v>-</x:v>
+        <x:v>I</x:v>
       </x:c>
       <x:c r="G11" s="290" t="str">
-        <x:v>-</x:v>
+        <x:v>○</x:v>
       </x:c>
       <x:c r="H11" s="290" t="str">
-        <x:v>-</x:v>
+        <x:v>yyyy-MM-dd</x:v>
       </x:c>
       <x:c r="I11" s="290" t="str">
-        <x:v>活性</x:v>
+        <x:v>当月初日</x:v>
       </x:c>
       <x:c r="J11" s="290" t="str">
-        <x:v>送信中非活性</x:v>
+        <x:v>VAL-004,VAL-005。期間最大366日</x:v>
       </x:c>
       <x:c r="K11" s="290" t="str">
-        <x:v>API-AUTH-001</x:v>
-      </x:c>
-      <x:c r="L11" s="290" t="str">
-        <x:v>-</x:v>
-      </x:c>
+        <x:v>API-DASH-001.request.query.periodFrom</x:v>
+      </x:c>
+      <x:c r="L11" s="290"/>
     </x:row>
     <x:row r="12" ht="30" customHeight="1">
       <x:c r="A12" s="290" t="str">
         <x:v>SCR-002</x:v>
       </x:c>
       <x:c r="B12" s="290" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C12" s="290" t="str">
-        <x:v>periodFrom</x:v>
+        <x:v>periodTo</x:v>
       </x:c>
       <x:c r="D12" s="290" t="str">
-        <x:v>集計開始日</x:v>
+        <x:v>集計終了日</x:v>
       </x:c>
       <x:c r="E12" s="290" t="str">
         <x:v>Date</x:v>
@@ -3404,68 +3036,64 @@
         <x:v>I</x:v>
       </x:c>
       <x:c r="G12" s="290" t="str">
-        <x:v>-</x:v>
+        <x:v>○</x:v>
       </x:c>
       <x:c r="H12" s="290" t="str">
         <x:v>yyyy-MM-dd</x:v>
       </x:c>
       <x:c r="I12" s="290" t="str">
-        <x:v>当月初日</x:v>
+        <x:v>当日</x:v>
       </x:c>
       <x:c r="J12" s="290" t="str">
-        <x:v>VAL-004, VAL-005</x:v>
+        <x:v>VAL-004,VAL-005。期間最大366日</x:v>
       </x:c>
       <x:c r="K12" s="290" t="str">
-        <x:v>API-DASH-001.periodFrom</x:v>
-      </x:c>
-      <x:c r="L12" s="290" t="str">
-        <x:v>-</x:v>
-      </x:c>
+        <x:v>API-DASH-001.request.query.periodTo</x:v>
+      </x:c>
+      <x:c r="L12" s="290"/>
     </x:row>
     <x:row r="13" ht="30" customHeight="1">
       <x:c r="A13" s="290" t="str">
         <x:v>SCR-002</x:v>
       </x:c>
       <x:c r="B13" s="290" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C13" s="290" t="str">
-        <x:v>periodTo</x:v>
+        <x:v>btnDisplay</x:v>
       </x:c>
       <x:c r="D13" s="290" t="str">
-        <x:v>集計終了日</x:v>
+        <x:v>表示</x:v>
       </x:c>
       <x:c r="E13" s="290" t="str">
-        <x:v>Date</x:v>
+        <x:v>Button</x:v>
       </x:c>
       <x:c r="F13" s="290" t="str">
-        <x:v>I</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="G13" s="290" t="str">
         <x:v>-</x:v>
       </x:c>
       <x:c r="H13" s="290" t="str">
-        <x:v>yyyy-MM-dd</x:v>
+        <x:v>-</x:v>
       </x:c>
       <x:c r="I13" s="290" t="str">
-        <x:v>当日</x:v>
+        <x:v>活性</x:v>
       </x:c>
       <x:c r="J13" s="290" t="str">
-        <x:v>VAL-004, VAL-005</x:v>
+        <x:v>期間検証後に再取得。処理中非活性</x:v>
       </x:c>
       <x:c r="K13" s="290" t="str">
-        <x:v>API-DASH-001.periodTo</x:v>
-      </x:c>
-      <x:c r="L13" s="290" t="str">
-        <x:v>-</x:v>
-      </x:c>
+        <x:v>API-DASH-001</x:v>
+      </x:c>
+      <x:c r="L13" s="290"/>
     </x:row>
     <x:row r="14" ht="30" customHeight="1">
       <x:c r="A14" s="290" t="str">
         <x:v>SCR-002</x:v>
       </x:c>
       <x:c r="B14" s="290" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C14" s="290" t="str">
         <x:v>projectCount</x:v>
@@ -3489,21 +3117,19 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="J14" s="290" t="str">
-        <x:v>権限範囲集計</x:v>
+        <x:v>権限範囲かつ指定期間と日程重複するPJ</x:v>
       </x:c>
       <x:c r="K14" s="290" t="str">
-        <x:v>API-DASH-001.projectCount</x:v>
-      </x:c>
-      <x:c r="L14" s="290" t="str">
-        <x:v>projects</x:v>
-      </x:c>
+        <x:v>API-DASH-001.response.body.data.projectCount</x:v>
+      </x:c>
+      <x:c r="L14" s="290"/>
     </x:row>
     <x:row r="15" ht="30" customHeight="1">
       <x:c r="A15" s="290" t="str">
         <x:v>SCR-002</x:v>
       </x:c>
       <x:c r="B15" s="290" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C15" s="290" t="str">
         <x:v>taskStatusCounts</x:v>
@@ -3512,7 +3138,7 @@
         <x:v>Task状態別件数</x:v>
       </x:c>
       <x:c r="E15" s="290" t="str">
-        <x:v>Card/List</x:v>
+        <x:v>List</x:v>
       </x:c>
       <x:c r="F15" s="290" t="str">
         <x:v>O</x:v>
@@ -3527,21 +3153,19 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="J15" s="290" t="str">
-        <x:v>図表を使用せず一覧表示</x:v>
+        <x:v>権限範囲かつ期限日が指定期間内のTaskを状態別表示</x:v>
       </x:c>
       <x:c r="K15" s="290" t="str">
-        <x:v>API-DASH-001.taskStatusCounts</x:v>
-      </x:c>
-      <x:c r="L15" s="290" t="str">
-        <x:v>tasks</x:v>
-      </x:c>
+        <x:v>API-DASH-001.response.body.data.taskStatusCounts</x:v>
+      </x:c>
+      <x:c r="L15" s="290"/>
     </x:row>
     <x:row r="16" ht="30" customHeight="1">
       <x:c r="A16" s="290" t="str">
         <x:v>SCR-002</x:v>
       </x:c>
       <x:c r="B16" s="290" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C16" s="290" t="str">
         <x:v>dueSoonCount</x:v>
@@ -3565,21 +3189,19 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="J16" s="290" t="str">
-        <x:v>3日以内未完了</x:v>
+        <x:v>System日～3日後の未完了Task。指定期間に非連動</x:v>
       </x:c>
       <x:c r="K16" s="290" t="str">
-        <x:v>API-DASH-001.dueSoonCount</x:v>
-      </x:c>
-      <x:c r="L16" s="290" t="str">
-        <x:v>tasks</x:v>
-      </x:c>
+        <x:v>API-DASH-001.response.body.data.dueSoonCount</x:v>
+      </x:c>
+      <x:c r="L16" s="290"/>
     </x:row>
     <x:row r="17" ht="30" customHeight="1">
       <x:c r="A17" s="290" t="str">
         <x:v>SCR-002</x:v>
       </x:c>
       <x:c r="B17" s="290" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C17" s="290" t="str">
         <x:v>reportSubmittedCount</x:v>
@@ -3603,21 +3225,19 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="J17" s="290" t="str">
-        <x:v>期間内提出数</x:v>
+        <x:v>report_dateが指定期間内</x:v>
       </x:c>
       <x:c r="K17" s="290" t="str">
-        <x:v>API-DASH-001.reportSubmittedCount</x:v>
-      </x:c>
-      <x:c r="L17" s="290" t="str">
-        <x:v>daily_reports</x:v>
-      </x:c>
+        <x:v>API-DASH-001.response.body.data.reportSubmittedCount</x:v>
+      </x:c>
+      <x:c r="L17" s="290"/>
     </x:row>
     <x:row r="18" ht="30" customHeight="1">
       <x:c r="A18" s="290" t="str">
         <x:v>SCR-002</x:v>
       </x:c>
       <x:c r="B18" s="290" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C18" s="290" t="str">
         <x:v>recentNotifications</x:v>
@@ -3641,14 +3261,12 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="J18" s="290" t="str">
-        <x:v>title/createdAt/read</x:v>
+        <x:v>title/createdAt/isRead。指定期間に非連動</x:v>
       </x:c>
       <x:c r="K18" s="290" t="str">
-        <x:v>API-DASH-001.recentNotifications</x:v>
-      </x:c>
-      <x:c r="L18" s="290" t="str">
-        <x:v>notifications</x:v>
-      </x:c>
+        <x:v>API-DASH-001.response.body.data.recentNotifications[]</x:v>
+      </x:c>
+      <x:c r="L18" s="290"/>
     </x:row>
     <x:row r="19" ht="30" customHeight="1">
       <x:c r="A19" s="290" t="str">
@@ -3682,11 +3300,9 @@
         <x:v>認証/ログ禁止</x:v>
       </x:c>
       <x:c r="K19" s="290" t="str">
-        <x:v>API-AUTH-005.currentPassword</x:v>
-      </x:c>
-      <x:c r="L19" s="290" t="str">
-        <x:v>非保存</x:v>
-      </x:c>
+        <x:v>API-AUTH-005.request.body.currentPassword</x:v>
+      </x:c>
+      <x:c r="L19" s="290"/>
     </x:row>
     <x:row r="20" ht="30" customHeight="1">
       <x:c r="A20" s="290" t="str">
@@ -3720,11 +3336,9 @@
         <x:v>VAL-011</x:v>
       </x:c>
       <x:c r="K20" s="290" t="str">
-        <x:v>API-AUTH-005.newPassword</x:v>
-      </x:c>
-      <x:c r="L20" s="290" t="str">
-        <x:v>users.password_hash</x:v>
-      </x:c>
+        <x:v>API-AUTH-005.request.body.newPassword</x:v>
+      </x:c>
+      <x:c r="L20" s="290"/>
     </x:row>
     <x:row r="21" ht="30" customHeight="1">
       <x:c r="A21" s="290" t="str">
@@ -3758,11 +3372,9 @@
         <x:v>newPassword一致</x:v>
       </x:c>
       <x:c r="K21" s="290" t="str">
-        <x:v>API-AUTH-005.confirmPassword</x:v>
-      </x:c>
-      <x:c r="L21" s="290" t="str">
-        <x:v>非保存</x:v>
-      </x:c>
+        <x:v>API-AUTH-005.request.body.confirmPassword</x:v>
+      </x:c>
+      <x:c r="L21" s="290"/>
     </x:row>
     <x:row r="22" ht="30" customHeight="1">
       <x:c r="A22" s="290" t="str">
@@ -3793,26 +3405,48 @@
         <x:v>活性</x:v>
       </x:c>
       <x:c r="J22" s="290" t="str">
-        <x:v>確認/二重送信防止</x:v>
+        <x:v>MSG-C-001確認/二重送信防止</x:v>
       </x:c>
       <x:c r="K22" s="290" t="str">
         <x:v>API-AUTH-005</x:v>
       </x:c>
-      <x:c r="L22" s="290" t="str">
+      <x:c r="L22" s="290"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>SCR-026</x:v>
+      </x:c>
+      <x:c r="B23" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>btnCancel</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>取消（強制変更Mode：ログアウト）</x:v>
+      </x:c>
+      <x:c r="E23" t="str">
+        <x:v>Button</x:v>
+      </x:c>
+      <x:c r="F23" t="str">
         <x:v>-</x:v>
       </x:c>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23"/>
-      <x:c r="B23"/>
-      <x:c r="C23"/>
-      <x:c r="D23"/>
-      <x:c r="E23"/>
-      <x:c r="F23"/>
-      <x:c r="G23"/>
-      <x:c r="H23"/>
-      <x:c r="I23"/>
-      <x:c r="J23"/>
+      <x:c r="G23" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="H23" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="I23" t="str">
+        <x:v>活性</x:v>
+      </x:c>
+      <x:c r="J23" t="str">
+        <x:v>17_画面処理概要／SCR-026取消を参照。強制変更中は業務画面へ戻らない。</x:v>
+      </x:c>
+      <x:c r="K23" t="str">
+        <x:v>通常：Front only／強制：API-AUTH-002</x:v>
+      </x:c>
+      <x:c r="L23"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24"/>
@@ -4901,7 +4535,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -4941,13 +4575,9 @@
       <x:c r="A3" s="285" t="str">
         <x:v>システム名</x:v>
       </x:c>
-      <x:c r="B3" s="286" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
+      <x:c r="B3" s="286" t="str"/>
       <x:c r="C3" s="286"/>
-      <x:c r="D3" s="285" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
+      <x:c r="D3" s="285" t="str"/>
       <x:c r="E3" s="286" t="str">
         <x:v>CW-BD-045</x:v>
       </x:c>
@@ -4956,18 +4586,14 @@
       <x:c r="H3"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="285" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="286" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
+      <x:c r="A4" s="472" t="str">
+        <x:v>版数：Ver.2.5</x:v>
+      </x:c>
+      <x:c r="B4" s="286"/>
       <x:c r="C4" s="286"/>
-      <x:c r="D4" s="285" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
+      <x:c r="D4" s="285" t="str"/>
       <x:c r="E4" s="286" t="str">
-        <x:v>2026-08-12</x:v>
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="F4" s="286"/>
       <x:c r="G4" s="286"/>
@@ -5018,7 +4644,7 @@
       </x:c>
       <x:c r="H7"/>
     </x:row>
-    <x:row r="8" ht="30" customHeight="1">
+    <x:row r="8" ht="104" customHeight="1">
       <x:c r="A8" s="290" t="str">
         <x:v>SCR-001</x:v>
       </x:c>
@@ -5029,20 +4655,20 @@
         <x:v>初期表示</x:v>
       </x:c>
       <x:c r="D8" s="290" t="str">
-        <x:v>-</x:v>
+        <x:v>API-AUTH-004</x:v>
       </x:c>
       <x:c r="E8" s="290" t="str">
-        <x:v>入力欄初期化、usernameへFocus</x:v>
+        <x:v>Token有効時はAPI-AUTH-004でUser情報を取得。passwordMustChange=trueならredirectより優先してSCR-026強制変更Modeへ。falseなら許可済redirect先、なければSCR-002。未認証時は入力初期化しusernameへFocus。</x:v>
       </x:c>
       <x:c r="F8" s="290" t="str">
-        <x:v>-</x:v>
+        <x:v>18／31B_ErrorMessage対応のAPI-AUTH-004別処理。AUTH-4005は403、Session破棄後SCR-001留置。</x:v>
       </x:c>
       <x:c r="G8" s="290" t="str">
-        <x:v>-</x:v>
+        <x:v>初期化中はLogin非活性</x:v>
       </x:c>
       <x:c r="H8"/>
     </x:row>
-    <x:row r="9" ht="30" customHeight="1">
+    <x:row r="9" ht="104" customHeight="1">
       <x:c r="A9" s="290" t="str">
         <x:v>SCR-001</x:v>
       </x:c>
@@ -5053,20 +4679,20 @@
         <x:v>ログイン</x:v>
       </x:c>
       <x:c r="D9" s="290" t="str">
-        <x:v>API-AUTH-001</x:v>
+        <x:v>API-AUTH-001,API-AUTH-004</x:v>
       </x:c>
       <x:c r="E9" s="290" t="str">
-        <x:v>入力検証→確認→API→TokenをMemory保存→SCR-002</x:v>
+        <x:v>入力検証→API-AUTH-001→Access TokenをMemory保存→API-AUTH-004。passwordMustChange=trueはSCR-026強制変更Mode、falseは許可済redirect先、なければSCR-002。AUTH-004失敗時はSessionを破棄しSCR-001に留まる。</x:v>
       </x:c>
       <x:c r="F9" s="290" t="str">
-        <x:v>項目Errorまたは共通Error表示</x:v>
+        <x:v>18／31B_ErrorMessage対応を対象API別に適用。AUTH-004失敗はSession破棄。429待機とFocusは03／21_ValidationLifecycle、秒数は10／19_API共通I-O。</x:v>
       </x:c>
       <x:c r="G9" s="290" t="str">
         <x:v>送信中Button非活性</x:v>
       </x:c>
       <x:c r="H9"/>
     </x:row>
-    <x:row r="10" ht="30" customHeight="1">
+    <x:row r="10" ht="42" customHeight="1">
       <x:c r="A10" s="290" t="str">
         <x:v>SCR-002</x:v>
       </x:c>
@@ -5074,74 +4700,116 @@
         <x:v>ホームダッシュボード</x:v>
       </x:c>
       <x:c r="C10" s="290" t="str">
-        <x:v>初期表示/期間変更</x:v>
+        <x:v>初期表示</x:v>
       </x:c>
       <x:c r="D10" s="290" t="str">
-        <x:v>API-DASH-001,API-NTF-002</x:v>
+        <x:v>API-DASH-001</x:v>
       </x:c>
       <x:c r="E10" s="290" t="str">
-        <x:v>権限範囲の集計Card・状態別一覧・最新通知を表示</x:v>
+        <x:v>期間を当月初日～当日で初期化しBR-DASH-001に従って集計Card・状態別件数・最新通知を表示</x:v>
       </x:c>
       <x:c r="F10" s="290" t="str">
-        <x:v>取得失敗時は該当領域Error、他領域は表示継続</x:v>
+        <x:v>取得失敗時はDashboard領域にError。共通Headerは継続</x:v>
       </x:c>
       <x:c r="G10" s="290" t="str">
-        <x:v>前回Request cancel</x:v>
+        <x:v>初期表示中は表示Button非活性</x:v>
       </x:c>
       <x:c r="H10"/>
     </x:row>
-    <x:row r="11" ht="30" customHeight="1">
+    <x:row r="11" ht="42" customHeight="1">
       <x:c r="A11" s="290" t="str">
+        <x:v>SCR-002</x:v>
+      </x:c>
+      <x:c r="B11" s="290" t="str">
+        <x:v>ホームダッシュボード</x:v>
+      </x:c>
+      <x:c r="C11" s="290" t="str">
+        <x:v>表示</x:v>
+      </x:c>
+      <x:c r="D11" s="290" t="str">
+        <x:v>API-DASH-001</x:v>
+      </x:c>
+      <x:c r="E11" s="290" t="str">
+        <x:v>期間必須/実在日/開始&lt;=終了/366日以内を検証後、Dashboardを再取得</x:v>
+      </x:c>
+      <x:c r="F11" s="290" t="str">
+        <x:v>入力Errorは項目下、通信ErrorはDashboard領域</x:v>
+      </x:c>
+      <x:c r="G11" s="290" t="str">
+        <x:v>前回Request cancel、処理中Button非活性</x:v>
+      </x:c>
+      <x:c r="H11"/>
+    </x:row>
+    <x:row r="12" ht="65" customHeight="1">
+      <x:c r="A12" s="402" t="str">
         <x:v>SCR-026</x:v>
       </x:c>
-      <x:c r="B11" s="290" t="str">
+      <x:c r="B12" s="402" t="str">
         <x:v>パスワード変更</x:v>
       </x:c>
-      <x:c r="C11" s="290" t="str">
-        <x:v>保存</x:v>
-      </x:c>
-      <x:c r="D11" s="290" t="str">
+      <x:c r="C12" s="402" t="str">
+        <x:v>初期表示</x:v>
+      </x:c>
+      <x:c r="D12" s="402" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="E12" s="402" t="str">
+        <x:v>3項目を空欄初期化。passwordMustChange=trueは強制変更Modeとし共通Menu・他画面遷移を禁止。falseは通常Modeとして遷移元を保持。</x:v>
+      </x:c>
+      <x:c r="F12" s="402" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G12" s="402" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="H12"/>
+    </x:row>
+    <x:row r="13" ht="42" customHeight="1">
+      <x:c r="A13" s="402" t="str">
+        <x:v>SCR-026</x:v>
+      </x:c>
+      <x:c r="B13" s="402" t="str">
+        <x:v>パスワード変更</x:v>
+      </x:c>
+      <x:c r="C13" s="402" t="str">
+        <x:v>変更</x:v>
+      </x:c>
+      <x:c r="D13" s="402" t="str">
         <x:v>API-AUTH-005</x:v>
       </x:c>
-      <x:c r="E11" s="290" t="str">
-        <x:v>Password規則/一致→変更→全Refresh失効→Loginへ</x:v>
-      </x:c>
-      <x:c r="F11" s="290" t="str">
-        <x:v>認証/項目Error</x:v>
-      </x:c>
-      <x:c r="G11" s="290" t="str">
-        <x:v>Button非活性</x:v>
-      </x:c>
-      <x:c r="H11"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12"/>
-      <x:c r="B12"/>
-      <x:c r="C12"/>
-      <x:c r="D12"/>
-      <x:c r="E12"/>
-      <x:c r="F12"/>
-      <x:c r="G12"/>
-      <x:c r="H12"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13"/>
-      <x:c r="B13"/>
-      <x:c r="C13"/>
-      <x:c r="D13"/>
-      <x:c r="E13"/>
-      <x:c r="F13"/>
-      <x:c r="G13"/>
+      <x:c r="E13" s="402" t="str">
+        <x:v>Password規則/一致→MSG-C-001確認→変更→MSG-I-005を次画面へ引継→Client Session Clear→SCR-001</x:v>
+      </x:c>
+      <x:c r="F13" s="402" t="str">
+        <x:v>認証/項目Error時は入力保持</x:v>
+      </x:c>
+      <x:c r="G13" s="402" t="str">
+        <x:v>処理中Button非活性</x:v>
+      </x:c>
       <x:c r="H13"/>
     </x:row>
-    <x:row r="14">
-      <x:c r="A14"/>
-      <x:c r="B14"/>
-      <x:c r="C14"/>
-      <x:c r="D14"/>
-      <x:c r="E14"/>
-      <x:c r="F14"/>
-      <x:c r="G14"/>
+    <x:row r="14" ht="65" customHeight="1">
+      <x:c r="A14" s="402" t="str">
+        <x:v>SCR-026</x:v>
+      </x:c>
+      <x:c r="B14" s="402" t="str">
+        <x:v>パスワード変更</x:v>
+      </x:c>
+      <x:c r="C14" s="402" t="str">
+        <x:v>取消</x:v>
+      </x:c>
+      <x:c r="D14" s="402" t="str">
+        <x:v>通常Mode：なし／強制変更Mode：API-AUTH-002</x:v>
+      </x:c>
+      <x:c r="E14" s="402" t="str">
+        <x:v>通常Modeは入力破棄後に遷移元へ戻る。強制変更Modeは取消ではなくLogoutとしてAPI-AUTH-002を実行し、Client Sessionを破棄してSCR-001へ戻る。</x:v>
+      </x:c>
+      <x:c r="F14" s="402" t="str">
+        <x:v>通常Modeの遷移元不明時はSCR-002。強制変更ModeのLogout通信失敗時もClient Sessionを破棄しSCR-001へ。他業務画面へ遷移しない。</x:v>
+      </x:c>
+      <x:c r="G14" s="402" t="str">
+        <x:v>-</x:v>
+      </x:c>
       <x:c r="H14"/>
     </x:row>
     <x:row r="15">
@@ -5348,6 +5016,1333 @@
     <x:mergeCell ref="A6:H6"/>
     <x:mergeCell ref="A1:G2"/>
     <x:mergeCell ref="A6:G6"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="11" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="11" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="11" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="9" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="9" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="9" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="9" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="9" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="9" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="9" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="9" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="9" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="9" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="9" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="9" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="9" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="21" customHeight="1">
+      <x:c r="A1" s="52" t="str">
+        <x:v>SCR-001  ログイン  画面レイアウト</x:v>
+      </x:c>
+      <x:c r="B1" s="52" t="str"/>
+      <x:c r="C1" s="52" t="str"/>
+      <x:c r="D1" s="52" t="str"/>
+      <x:c r="E1" s="52" t="str"/>
+      <x:c r="F1" s="52" t="str"/>
+      <x:c r="G1" s="52" t="str"/>
+      <x:c r="H1" s="52" t="str"/>
+      <x:c r="I1" s="52" t="str"/>
+      <x:c r="J1" s="52" t="str"/>
+      <x:c r="K1" s="52" t="str"/>
+      <x:c r="L1" s="52" t="str"/>
+      <x:c r="M1" s="52" t="str"/>
+      <x:c r="N1" s="52" t="str"/>
+      <x:c r="O1" s="52" t="str"/>
+      <x:c r="P1" s="52" t="str"/>
+    </x:row>
+    <x:row r="2" ht="21" customHeight="1">
+      <x:c r="A2" s="54" t="str">
+        <x:v>画面ID: SCR-001    画面名: ログイン</x:v>
+      </x:c>
+      <x:c r="B2" s="54" t="str"/>
+      <x:c r="C2" s="54" t="str"/>
+      <x:c r="D2" s="54" t="str"/>
+      <x:c r="E2" s="54" t="str"/>
+      <x:c r="F2" s="54" t="str"/>
+      <x:c r="G2" s="54" t="str"/>
+      <x:c r="H2" s="54" t="str"/>
+      <x:c r="I2" s="473" t="str">
+        <x:v>Ver.2.5    2026-09-24</x:v>
+      </x:c>
+      <x:c r="J2" s="55" t="str"/>
+      <x:c r="K2" s="55" t="str"/>
+      <x:c r="L2" s="55" t="str"/>
+      <x:c r="M2" s="55" t="str"/>
+      <x:c r="N2" s="55" t="str"/>
+      <x:c r="O2" s="55" t="str"/>
+      <x:c r="P2" s="55" t="str"/>
+    </x:row>
+    <x:row r="3" ht="21" customHeight="1">
+      <x:c r="A3" s="48"/>
+      <x:c r="B3" s="48"/>
+      <x:c r="C3" s="48"/>
+      <x:c r="D3" s="48"/>
+      <x:c r="E3" s="48"/>
+      <x:c r="F3" s="48"/>
+      <x:c r="G3" s="48"/>
+      <x:c r="H3" s="48"/>
+      <x:c r="I3" s="48"/>
+      <x:c r="J3" s="48"/>
+      <x:c r="K3" s="48"/>
+      <x:c r="L3" s="48"/>
+      <x:c r="M3" s="48"/>
+      <x:c r="N3" s="48"/>
+      <x:c r="O3" s="48"/>
+      <x:c r="P3" s="48"/>
+    </x:row>
+    <x:row r="4" ht="21" customHeight="1">
+      <x:c r="A4" s="61" t="str">
+        <x:v>Company WorkHub</x:v>
+      </x:c>
+      <x:c r="B4" s="61" t="str"/>
+      <x:c r="C4" s="61" t="str"/>
+      <x:c r="D4" s="61" t="str"/>
+      <x:c r="E4" s="61" t="str"/>
+      <x:c r="F4" s="61" t="str"/>
+      <x:c r="G4" s="61" t="str"/>
+      <x:c r="H4" s="61" t="str"/>
+      <x:c r="I4" s="61" t="str"/>
+      <x:c r="J4" s="61" t="str"/>
+      <x:c r="K4" s="61" t="str"/>
+      <x:c r="L4" s="61" t="str"/>
+      <x:c r="M4" s="61" t="str"/>
+      <x:c r="N4" s="61" t="str"/>
+      <x:c r="O4" s="61" t="str"/>
+      <x:c r="P4" s="61" t="str"/>
+    </x:row>
+    <x:row r="5" ht="21" customHeight="1">
+      <x:c r="A5" s="61" t="str"/>
+      <x:c r="B5" s="61" t="str"/>
+      <x:c r="C5" s="61" t="str"/>
+      <x:c r="D5" s="61" t="str"/>
+      <x:c r="E5" s="61" t="str"/>
+      <x:c r="F5" s="61" t="str"/>
+      <x:c r="G5" s="61" t="str"/>
+      <x:c r="H5" s="61" t="str"/>
+      <x:c r="I5" s="61" t="str"/>
+      <x:c r="J5" s="61" t="str"/>
+      <x:c r="K5" s="61" t="str"/>
+      <x:c r="L5" s="61" t="str"/>
+      <x:c r="M5" s="61" t="str"/>
+      <x:c r="N5" s="61" t="str"/>
+      <x:c r="O5" s="61" t="str"/>
+      <x:c r="P5" s="61" t="str"/>
+    </x:row>
+    <x:row r="6" ht="21" customHeight="1">
+      <x:c r="A6" s="48"/>
+      <x:c r="B6" s="48"/>
+      <x:c r="C6" s="48"/>
+      <x:c r="D6" s="48"/>
+      <x:c r="E6" s="48"/>
+      <x:c r="F6" s="48"/>
+      <x:c r="G6" s="48"/>
+      <x:c r="H6" s="48"/>
+      <x:c r="I6" s="48"/>
+      <x:c r="J6" s="48"/>
+      <x:c r="K6" s="48"/>
+      <x:c r="L6" s="48"/>
+      <x:c r="M6" s="48"/>
+      <x:c r="N6" s="48"/>
+      <x:c r="O6" s="48"/>
+      <x:c r="P6" s="48"/>
+    </x:row>
+    <x:row r="7" ht="21" customHeight="1">
+      <x:c r="A7" s="48"/>
+      <x:c r="B7" s="48"/>
+      <x:c r="C7" s="48"/>
+      <x:c r="D7" s="107"/>
+      <x:c r="E7" s="108"/>
+      <x:c r="F7" s="108"/>
+      <x:c r="G7" s="108"/>
+      <x:c r="H7" s="108"/>
+      <x:c r="I7" s="108"/>
+      <x:c r="J7" s="108"/>
+      <x:c r="K7" s="108"/>
+      <x:c r="L7" s="108"/>
+      <x:c r="M7" s="109"/>
+      <x:c r="N7" s="48"/>
+      <x:c r="O7" s="48"/>
+      <x:c r="P7" s="48"/>
+    </x:row>
+    <x:row r="8" ht="21" customHeight="1">
+      <x:c r="A8" s="48"/>
+      <x:c r="B8" s="48"/>
+      <x:c r="C8" s="48"/>
+      <x:c r="D8" s="110"/>
+      <x:c r="E8" s="75" t="str">
+        <x:v>LOGIN</x:v>
+      </x:c>
+      <x:c r="F8" s="76" t="str"/>
+      <x:c r="G8" s="76" t="str"/>
+      <x:c r="H8" s="76" t="str"/>
+      <x:c r="I8" s="76" t="str"/>
+      <x:c r="J8" s="76" t="str"/>
+      <x:c r="K8" s="76" t="str"/>
+      <x:c r="L8" s="77" t="str"/>
+      <x:c r="M8" s="111"/>
+      <x:c r="N8" s="48"/>
+      <x:c r="O8" s="48"/>
+      <x:c r="P8" s="48"/>
+    </x:row>
+    <x:row r="9" ht="21" customHeight="1">
+      <x:c r="A9" s="48"/>
+      <x:c r="B9" s="48"/>
+      <x:c r="C9" s="48"/>
+      <x:c r="D9" s="110"/>
+      <x:c r="E9" s="78" t="str"/>
+      <x:c r="F9" s="79" t="str"/>
+      <x:c r="G9" s="79" t="str"/>
+      <x:c r="H9" s="79" t="str"/>
+      <x:c r="I9" s="79" t="str"/>
+      <x:c r="J9" s="79" t="str"/>
+      <x:c r="K9" s="79" t="str"/>
+      <x:c r="L9" s="80" t="str"/>
+      <x:c r="M9" s="111"/>
+      <x:c r="N9" s="48"/>
+      <x:c r="O9" s="48"/>
+      <x:c r="P9" s="48"/>
+    </x:row>
+    <x:row r="10" ht="21" customHeight="1">
+      <x:c r="A10" s="48"/>
+      <x:c r="B10" s="48"/>
+      <x:c r="C10" s="48"/>
+      <x:c r="D10" s="110"/>
+      <x:c r="E10" s="112"/>
+      <x:c r="F10" s="112"/>
+      <x:c r="G10" s="112"/>
+      <x:c r="H10" s="112"/>
+      <x:c r="I10" s="112"/>
+      <x:c r="J10" s="112"/>
+      <x:c r="K10" s="112"/>
+      <x:c r="L10" s="112"/>
+      <x:c r="M10" s="111"/>
+      <x:c r="N10" s="48"/>
+      <x:c r="O10" s="48"/>
+      <x:c r="P10" s="48"/>
+    </x:row>
+    <x:row r="11" ht="21" customHeight="1">
+      <x:c r="A11" s="48"/>
+      <x:c r="B11" s="48"/>
+      <x:c r="C11" s="48"/>
+      <x:c r="D11" s="110"/>
+      <x:c r="E11" s="113" t="str">
+        <x:v>1. ユーザー名</x:v>
+      </x:c>
+      <x:c r="F11" s="113" t="str"/>
+      <x:c r="G11" s="113" t="str"/>
+      <x:c r="H11" s="85" t="str"/>
+      <x:c r="I11" s="85" t="str"/>
+      <x:c r="J11" s="85" t="str"/>
+      <x:c r="K11" s="85" t="str"/>
+      <x:c r="L11" s="85" t="str"/>
+      <x:c r="M11" s="111"/>
+      <x:c r="N11" s="48"/>
+      <x:c r="O11" s="48"/>
+      <x:c r="P11" s="48"/>
+    </x:row>
+    <x:row r="12" ht="21" customHeight="1">
+      <x:c r="A12" s="48"/>
+      <x:c r="B12" s="48"/>
+      <x:c r="C12" s="48"/>
+      <x:c r="D12" s="110"/>
+      <x:c r="E12" s="112"/>
+      <x:c r="F12" s="112"/>
+      <x:c r="G12" s="112"/>
+      <x:c r="H12" s="112"/>
+      <x:c r="I12" s="112"/>
+      <x:c r="J12" s="112"/>
+      <x:c r="K12" s="112"/>
+      <x:c r="L12" s="112"/>
+      <x:c r="M12" s="111"/>
+      <x:c r="N12" s="48"/>
+      <x:c r="O12" s="48"/>
+      <x:c r="P12" s="48"/>
+    </x:row>
+    <x:row r="13" ht="21" customHeight="1">
+      <x:c r="A13" s="48"/>
+      <x:c r="B13" s="48"/>
+      <x:c r="C13" s="48"/>
+      <x:c r="D13" s="110"/>
+      <x:c r="E13" s="113" t="str">
+        <x:v>2. パスワード</x:v>
+      </x:c>
+      <x:c r="F13" s="113" t="str"/>
+      <x:c r="G13" s="113" t="str"/>
+      <x:c r="H13" s="85" t="str">
+        <x:v>********</x:v>
+      </x:c>
+      <x:c r="I13" s="85" t="str"/>
+      <x:c r="J13" s="85" t="str"/>
+      <x:c r="K13" s="85" t="str"/>
+      <x:c r="L13" s="85" t="str"/>
+      <x:c r="M13" s="111"/>
+      <x:c r="N13" s="48"/>
+      <x:c r="O13" s="48"/>
+      <x:c r="P13" s="48"/>
+    </x:row>
+    <x:row r="14" ht="21" customHeight="1">
+      <x:c r="A14" s="48"/>
+      <x:c r="B14" s="48"/>
+      <x:c r="C14" s="48"/>
+      <x:c r="D14" s="110"/>
+      <x:c r="E14" s="112"/>
+      <x:c r="F14" s="112"/>
+      <x:c r="G14" s="112"/>
+      <x:c r="H14" s="112"/>
+      <x:c r="I14" s="112"/>
+      <x:c r="J14" s="112"/>
+      <x:c r="K14" s="112"/>
+      <x:c r="L14" s="112"/>
+      <x:c r="M14" s="111"/>
+      <x:c r="N14" s="48"/>
+      <x:c r="O14" s="48"/>
+      <x:c r="P14" s="48"/>
+    </x:row>
+    <x:row r="15" ht="21" customHeight="1">
+      <x:c r="A15" s="48"/>
+      <x:c r="B15" s="48"/>
+      <x:c r="C15" s="48"/>
+      <x:c r="D15" s="110"/>
+      <x:c r="E15"/>
+      <x:c r="F15"/>
+      <x:c r="G15"/>
+      <x:c r="H15"/>
+      <x:c r="I15"/>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
+      <x:c r="M15" s="111"/>
+      <x:c r="N15" s="48"/>
+      <x:c r="O15" s="48"/>
+      <x:c r="P15" s="48"/>
+    </x:row>
+    <x:row r="16" ht="21" customHeight="1">
+      <x:c r="A16" s="48"/>
+      <x:c r="B16" s="48"/>
+      <x:c r="C16" s="48"/>
+      <x:c r="D16" s="110"/>
+      <x:c r="E16" s="112"/>
+      <x:c r="F16" s="112"/>
+      <x:c r="G16" s="112"/>
+      <x:c r="H16" s="112"/>
+      <x:c r="I16" s="112"/>
+      <x:c r="J16" s="112"/>
+      <x:c r="K16" s="112"/>
+      <x:c r="L16" s="112"/>
+      <x:c r="M16" s="111"/>
+      <x:c r="N16" s="48"/>
+      <x:c r="O16" s="48"/>
+      <x:c r="P16" s="48"/>
+    </x:row>
+    <x:row r="17" ht="21" customHeight="1">
+      <x:c r="A17" s="48"/>
+      <x:c r="B17" s="48"/>
+      <x:c r="C17" s="48"/>
+      <x:c r="D17" s="110"/>
+      <x:c r="E17" s="99" t="str">
+        <x:v>Login</x:v>
+      </x:c>
+      <x:c r="F17" s="100" t="str"/>
+      <x:c r="G17" s="100" t="str"/>
+      <x:c r="H17" s="100" t="str"/>
+      <x:c r="I17" s="100" t="str"/>
+      <x:c r="J17" s="100" t="str"/>
+      <x:c r="K17" s="100" t="str"/>
+      <x:c r="L17" s="101" t="str"/>
+      <x:c r="M17" s="111"/>
+      <x:c r="N17" s="48"/>
+      <x:c r="O17" s="48"/>
+      <x:c r="P17" s="48"/>
+    </x:row>
+    <x:row r="18" ht="21" customHeight="1">
+      <x:c r="A18" s="48"/>
+      <x:c r="B18" s="48"/>
+      <x:c r="C18" s="48"/>
+      <x:c r="D18" s="110"/>
+      <x:c r="E18" s="102" t="str"/>
+      <x:c r="F18" s="103" t="str"/>
+      <x:c r="G18" s="103" t="str"/>
+      <x:c r="H18" s="103" t="str"/>
+      <x:c r="I18" s="103" t="str"/>
+      <x:c r="J18" s="103" t="str"/>
+      <x:c r="K18" s="103" t="str"/>
+      <x:c r="L18" s="104" t="str"/>
+      <x:c r="M18" s="111"/>
+      <x:c r="N18" s="48"/>
+      <x:c r="O18" s="48"/>
+      <x:c r="P18" s="48"/>
+    </x:row>
+    <x:row r="19" ht="21" customHeight="1">
+      <x:c r="A19" s="48"/>
+      <x:c r="B19" s="48"/>
+      <x:c r="C19" s="48"/>
+      <x:c r="D19" s="110"/>
+      <x:c r="E19" s="112"/>
+      <x:c r="F19" s="112"/>
+      <x:c r="G19" s="112"/>
+      <x:c r="H19" s="112"/>
+      <x:c r="I19" s="112"/>
+      <x:c r="J19" s="112"/>
+      <x:c r="K19" s="112"/>
+      <x:c r="L19" s="112"/>
+      <x:c r="M19" s="111"/>
+      <x:c r="N19" s="48"/>
+      <x:c r="O19" s="48"/>
+      <x:c r="P19" s="48"/>
+    </x:row>
+    <x:row r="20" ht="21" customHeight="1">
+      <x:c r="A20" s="48"/>
+      <x:c r="B20" s="48"/>
+      <x:c r="C20" s="48"/>
+      <x:c r="D20" s="110"/>
+      <x:c r="E20" s="114"/>
+      <x:c r="F20" s="114"/>
+      <x:c r="G20" s="114"/>
+      <x:c r="H20" s="114"/>
+      <x:c r="I20" s="114"/>
+      <x:c r="J20" s="114"/>
+      <x:c r="K20" s="114"/>
+      <x:c r="L20" s="114"/>
+      <x:c r="M20" s="111"/>
+      <x:c r="N20" s="48"/>
+      <x:c r="O20" s="48"/>
+      <x:c r="P20" s="48"/>
+    </x:row>
+    <x:row r="21" ht="21" customHeight="1">
+      <x:c r="A21" s="48"/>
+      <x:c r="B21" s="48"/>
+      <x:c r="C21" s="48"/>
+      <x:c r="D21" s="110"/>
+      <x:c r="E21" s="112"/>
+      <x:c r="F21" s="112"/>
+      <x:c r="G21" s="112"/>
+      <x:c r="H21" s="112"/>
+      <x:c r="I21" s="112"/>
+      <x:c r="J21" s="112"/>
+      <x:c r="K21" s="112"/>
+      <x:c r="L21" s="112"/>
+      <x:c r="M21" s="111"/>
+      <x:c r="N21" s="48"/>
+      <x:c r="O21" s="48"/>
+      <x:c r="P21" s="48"/>
+    </x:row>
+    <x:row r="22" ht="21" customHeight="1">
+      <x:c r="A22" s="48"/>
+      <x:c r="B22" s="48"/>
+      <x:c r="C22" s="48"/>
+      <x:c r="D22" s="110"/>
+      <x:c r="E22" s="112"/>
+      <x:c r="F22" s="112"/>
+      <x:c r="G22" s="112"/>
+      <x:c r="H22" s="112"/>
+      <x:c r="I22" s="112"/>
+      <x:c r="J22" s="112"/>
+      <x:c r="K22" s="112"/>
+      <x:c r="L22" s="112"/>
+      <x:c r="M22" s="111"/>
+      <x:c r="N22" s="48"/>
+      <x:c r="O22" s="48"/>
+      <x:c r="P22" s="48"/>
+    </x:row>
+    <x:row r="23" ht="21" customHeight="1">
+      <x:c r="A23" s="48"/>
+      <x:c r="B23" s="48"/>
+      <x:c r="C23" s="48"/>
+      <x:c r="D23" s="110"/>
+      <x:c r="E23" s="112"/>
+      <x:c r="F23" s="112"/>
+      <x:c r="G23" s="112"/>
+      <x:c r="H23" s="112"/>
+      <x:c r="I23" s="112"/>
+      <x:c r="J23" s="112"/>
+      <x:c r="K23" s="112"/>
+      <x:c r="L23" s="112"/>
+      <x:c r="M23" s="111"/>
+      <x:c r="N23" s="48"/>
+      <x:c r="O23" s="48"/>
+      <x:c r="P23" s="48"/>
+    </x:row>
+    <x:row r="24" ht="21" customHeight="1">
+      <x:c r="A24" s="48"/>
+      <x:c r="B24" s="48"/>
+      <x:c r="C24" s="48"/>
+      <x:c r="D24" s="110"/>
+      <x:c r="E24" s="112"/>
+      <x:c r="F24" s="112"/>
+      <x:c r="G24" s="112"/>
+      <x:c r="H24" s="112"/>
+      <x:c r="I24" s="112"/>
+      <x:c r="J24" s="112"/>
+      <x:c r="K24" s="112"/>
+      <x:c r="L24" s="112"/>
+      <x:c r="M24" s="111"/>
+      <x:c r="N24" s="48"/>
+      <x:c r="O24" s="48"/>
+      <x:c r="P24" s="48"/>
+    </x:row>
+    <x:row r="25" ht="21" customHeight="1">
+      <x:c r="A25" s="48"/>
+      <x:c r="B25" s="48"/>
+      <x:c r="C25" s="48"/>
+      <x:c r="D25" s="110"/>
+      <x:c r="E25" s="112"/>
+      <x:c r="F25" s="112"/>
+      <x:c r="G25" s="112"/>
+      <x:c r="H25" s="112"/>
+      <x:c r="I25" s="112"/>
+      <x:c r="J25" s="112"/>
+      <x:c r="K25" s="112"/>
+      <x:c r="L25" s="112"/>
+      <x:c r="M25" s="111"/>
+      <x:c r="N25" s="48"/>
+      <x:c r="O25" s="48"/>
+      <x:c r="P25" s="48"/>
+    </x:row>
+    <x:row r="26" ht="21" customHeight="1">
+      <x:c r="A26" s="48"/>
+      <x:c r="B26" s="48"/>
+      <x:c r="C26" s="48"/>
+      <x:c r="D26" s="110"/>
+      <x:c r="E26" s="112"/>
+      <x:c r="F26" s="112"/>
+      <x:c r="G26" s="112"/>
+      <x:c r="H26" s="112"/>
+      <x:c r="I26" s="112"/>
+      <x:c r="J26" s="112"/>
+      <x:c r="K26" s="112"/>
+      <x:c r="L26" s="112"/>
+      <x:c r="M26" s="111"/>
+      <x:c r="N26" s="48"/>
+      <x:c r="O26" s="48"/>
+      <x:c r="P26" s="48"/>
+    </x:row>
+    <x:row r="27" ht="21" customHeight="1">
+      <x:c r="A27" s="48"/>
+      <x:c r="B27" s="48"/>
+      <x:c r="C27" s="48"/>
+      <x:c r="D27" s="115"/>
+      <x:c r="E27" s="116"/>
+      <x:c r="F27" s="116"/>
+      <x:c r="G27" s="116"/>
+      <x:c r="H27" s="116"/>
+      <x:c r="I27" s="116"/>
+      <x:c r="J27" s="116"/>
+      <x:c r="K27" s="116"/>
+      <x:c r="L27" s="116"/>
+      <x:c r="M27" s="117"/>
+      <x:c r="N27" s="48"/>
+      <x:c r="O27" s="48"/>
+      <x:c r="P27" s="48"/>
+    </x:row>
+    <x:row r="28" ht="21" customHeight="1">
+      <x:c r="A28" s="48"/>
+      <x:c r="B28" s="48"/>
+      <x:c r="C28" s="48"/>
+      <x:c r="D28" s="48"/>
+      <x:c r="E28" s="48"/>
+      <x:c r="F28" s="48"/>
+      <x:c r="G28" s="48"/>
+      <x:c r="H28" s="48"/>
+      <x:c r="I28" s="48"/>
+      <x:c r="J28" s="48"/>
+      <x:c r="K28" s="48"/>
+      <x:c r="L28" s="48"/>
+      <x:c r="M28" s="48"/>
+      <x:c r="N28" s="48"/>
+      <x:c r="O28" s="48"/>
+      <x:c r="P28" s="48"/>
+    </x:row>
+    <x:row r="29" ht="21" customHeight="1">
+      <x:c r="A29" s="48"/>
+      <x:c r="B29" s="48"/>
+      <x:c r="C29" s="48"/>
+      <x:c r="D29" s="48"/>
+      <x:c r="E29" s="48"/>
+      <x:c r="F29" s="48"/>
+      <x:c r="G29" s="48"/>
+      <x:c r="H29" s="48"/>
+      <x:c r="I29" s="48"/>
+      <x:c r="J29" s="48"/>
+      <x:c r="K29" s="48"/>
+      <x:c r="L29" s="48"/>
+      <x:c r="M29" s="48"/>
+      <x:c r="N29" s="48"/>
+      <x:c r="O29" s="48"/>
+      <x:c r="P29" s="48"/>
+    </x:row>
+    <x:row r="30" ht="21" customHeight="1">
+      <x:c r="A30" s="48"/>
+      <x:c r="B30" s="48"/>
+      <x:c r="C30" s="48"/>
+      <x:c r="D30" s="48"/>
+      <x:c r="E30" s="48"/>
+      <x:c r="F30" s="48"/>
+      <x:c r="G30" s="48"/>
+      <x:c r="H30" s="48"/>
+      <x:c r="I30" s="48"/>
+      <x:c r="J30" s="48"/>
+      <x:c r="K30" s="48"/>
+      <x:c r="L30" s="48"/>
+      <x:c r="M30" s="48"/>
+      <x:c r="N30" s="48"/>
+      <x:c r="O30" s="48"/>
+      <x:c r="P30" s="48"/>
+    </x:row>
+    <x:row r="31" ht="21" customHeight="1">
+      <x:c r="A31" s="48"/>
+      <x:c r="B31" s="48"/>
+      <x:c r="C31" s="48"/>
+      <x:c r="D31" s="48"/>
+      <x:c r="E31" s="48"/>
+      <x:c r="F31" s="48"/>
+      <x:c r="G31" s="48"/>
+      <x:c r="H31" s="48"/>
+      <x:c r="I31" s="48"/>
+      <x:c r="J31" s="48"/>
+      <x:c r="K31" s="48"/>
+      <x:c r="L31" s="48"/>
+      <x:c r="M31" s="48"/>
+      <x:c r="N31" s="48"/>
+      <x:c r="O31" s="48"/>
+      <x:c r="P31" s="48"/>
+    </x:row>
+    <x:row r="32" ht="21" customHeight="1">
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+      <x:c r="I32"/>
+      <x:c r="J32"/>
+      <x:c r="K32"/>
+      <x:c r="L32"/>
+      <x:c r="M32"/>
+      <x:c r="N32"/>
+      <x:c r="O32"/>
+      <x:c r="P32"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:P1"/>
+    <x:mergeCell ref="A2:H2"/>
+    <x:mergeCell ref="I2:P2"/>
+    <x:mergeCell ref="A32:P32"/>
+    <x:mergeCell ref="A4:P5"/>
+    <x:mergeCell ref="E8:L9"/>
+    <x:mergeCell ref="E11:G11"/>
+    <x:mergeCell ref="H11:L11"/>
+    <x:mergeCell ref="E13:G13"/>
+    <x:mergeCell ref="H13:L13"/>
+    <x:mergeCell ref="E15:G15"/>
+    <x:mergeCell ref="H15:L15"/>
+    <x:mergeCell ref="E17:L18"/>
+    <x:mergeCell ref="E20:L20"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="11" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="11" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="11" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="9" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="9" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="9" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="9" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="9" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="9" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="9" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="9" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="9" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="9" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="9" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="9" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="9" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="21" customHeight="1">
+      <x:c r="A1" s="52" t="str">
+        <x:v>SCR-002  ホームダッシュボード  画面レイアウト</x:v>
+      </x:c>
+      <x:c r="B1" s="52" t="str"/>
+      <x:c r="C1" s="52" t="str"/>
+      <x:c r="D1" s="52" t="str"/>
+      <x:c r="E1" s="52" t="str"/>
+      <x:c r="F1" s="52" t="str"/>
+      <x:c r="G1" s="52" t="str"/>
+      <x:c r="H1" s="52" t="str"/>
+      <x:c r="I1" s="52" t="str"/>
+      <x:c r="J1" s="52" t="str"/>
+      <x:c r="K1" s="52" t="str"/>
+      <x:c r="L1" s="52" t="str"/>
+      <x:c r="M1" s="52" t="str"/>
+      <x:c r="N1" s="52" t="str"/>
+      <x:c r="O1" s="52" t="str"/>
+      <x:c r="P1" s="52" t="str"/>
+    </x:row>
+    <x:row r="2" ht="21" customHeight="1">
+      <x:c r="A2" s="54" t="str">
+        <x:v>画面ID: SCR-002    画面名: ホームダッシュボード</x:v>
+      </x:c>
+      <x:c r="B2" s="54" t="str"/>
+      <x:c r="C2" s="54" t="str"/>
+      <x:c r="D2" s="54" t="str"/>
+      <x:c r="E2" s="54" t="str"/>
+      <x:c r="F2" s="54" t="str"/>
+      <x:c r="G2" s="54" t="str"/>
+      <x:c r="H2" s="54" t="str"/>
+      <x:c r="I2" s="473" t="str">
+        <x:v>Ver.2.5    2026-09-24</x:v>
+      </x:c>
+      <x:c r="J2" s="55" t="str"/>
+      <x:c r="K2" s="55" t="str"/>
+      <x:c r="L2" s="55" t="str"/>
+      <x:c r="M2" s="55" t="str"/>
+      <x:c r="N2" s="55" t="str"/>
+      <x:c r="O2" s="55" t="str"/>
+      <x:c r="P2" s="55" t="str"/>
+    </x:row>
+    <x:row r="3" ht="21" customHeight="1">
+      <x:c r="A3" s="48"/>
+      <x:c r="B3" s="48"/>
+      <x:c r="C3" s="48"/>
+      <x:c r="D3" s="48"/>
+      <x:c r="E3" s="48"/>
+      <x:c r="F3" s="48"/>
+      <x:c r="G3" s="48"/>
+      <x:c r="H3" s="48"/>
+      <x:c r="I3" s="48"/>
+      <x:c r="J3" s="48"/>
+      <x:c r="K3" s="48"/>
+      <x:c r="L3" s="48"/>
+      <x:c r="M3" s="48"/>
+      <x:c r="N3" s="48"/>
+      <x:c r="O3" s="48"/>
+      <x:c r="P3" s="48"/>
+    </x:row>
+    <x:row r="4" ht="21" customHeight="1">
+      <x:c r="A4" s="130" t="str">
+        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
+      </x:c>
+      <x:c r="B4" s="131" t="str"/>
+      <x:c r="C4" s="131" t="str"/>
+      <x:c r="D4" s="131" t="str"/>
+      <x:c r="E4" s="131" t="str"/>
+      <x:c r="F4" s="131" t="str"/>
+      <x:c r="G4" s="131" t="str"/>
+      <x:c r="H4" s="131" t="str"/>
+      <x:c r="I4" s="131" t="str"/>
+      <x:c r="J4" s="131" t="str"/>
+      <x:c r="K4" s="131" t="str"/>
+      <x:c r="L4" s="131" t="str"/>
+      <x:c r="M4" s="131" t="str"/>
+      <x:c r="N4" s="131" t="str"/>
+      <x:c r="O4" s="131" t="str"/>
+      <x:c r="P4" s="132" t="str"/>
+    </x:row>
+    <x:row r="5" ht="21" customHeight="1">
+      <x:c r="A5" s="133" t="str"/>
+      <x:c r="B5" s="134" t="str"/>
+      <x:c r="C5" s="134" t="str"/>
+      <x:c r="D5" s="134" t="str"/>
+      <x:c r="E5" s="134" t="str"/>
+      <x:c r="F5" s="134" t="str"/>
+      <x:c r="G5" s="134" t="str"/>
+      <x:c r="H5" s="134" t="str"/>
+      <x:c r="I5" s="134" t="str"/>
+      <x:c r="J5" s="134" t="str"/>
+      <x:c r="K5" s="134" t="str"/>
+      <x:c r="L5" s="134" t="str"/>
+      <x:c r="M5" s="134" t="str"/>
+      <x:c r="N5" s="134" t="str"/>
+      <x:c r="O5" s="134" t="str"/>
+      <x:c r="P5" s="135" t="str"/>
+    </x:row>
+    <x:row r="6" ht="21" customHeight="1">
+      <x:c r="A6" s="165" t="str">
+        <x:v>Home
+組織管理
+プロジェクト
+タスク
+日報
+通知
+System</x:v>
+      </x:c>
+      <x:c r="B6" s="166" t="str"/>
+      <x:c r="C6" s="167" t="str"/>
+      <x:c r="D6" s="176" t="str">
+        <x:v>Home  &gt;  ホームダッシュボード</x:v>
+      </x:c>
+      <x:c r="E6" s="176" t="str"/>
+      <x:c r="F6" s="176" t="str"/>
+      <x:c r="G6" s="176" t="str"/>
+      <x:c r="H6" s="176" t="str"/>
+      <x:c r="I6" s="176" t="str"/>
+      <x:c r="J6" s="176" t="str"/>
+      <x:c r="K6" s="176" t="str"/>
+      <x:c r="L6" s="176" t="str"/>
+      <x:c r="M6" s="176" t="str"/>
+      <x:c r="N6" s="176" t="str"/>
+      <x:c r="O6" s="176" t="str"/>
+      <x:c r="P6" s="176" t="str"/>
+    </x:row>
+    <x:row r="7" ht="21" customHeight="1">
+      <x:c r="A7" s="168" t="str"/>
+      <x:c r="B7" s="169" t="str"/>
+      <x:c r="C7" s="170" t="str"/>
+      <x:c r="D7" s="178" t="str">
+        <x:v>ホームダッシュボード</x:v>
+      </x:c>
+      <x:c r="E7" s="178" t="str"/>
+      <x:c r="F7" s="178" t="str"/>
+      <x:c r="G7" s="178" t="str"/>
+      <x:c r="H7" s="178" t="str"/>
+      <x:c r="I7" s="178" t="str"/>
+      <x:c r="J7" s="178" t="str"/>
+      <x:c r="K7" s="178" t="str"/>
+      <x:c r="L7" s="178" t="str"/>
+      <x:c r="M7" s="48"/>
+      <x:c r="N7" s="48"/>
+      <x:c r="O7" s="48"/>
+      <x:c r="P7" s="48"/>
+    </x:row>
+    <x:row r="8" ht="21" customHeight="1">
+      <x:c r="A8" s="168" t="str"/>
+      <x:c r="B8" s="169" t="str"/>
+      <x:c r="C8" s="170" t="str"/>
+      <x:c r="D8" s="178" t="str"/>
+      <x:c r="E8" s="178" t="str"/>
+      <x:c r="F8" s="178" t="str"/>
+      <x:c r="G8" s="178" t="str"/>
+      <x:c r="H8" s="178" t="str"/>
+      <x:c r="I8" s="178" t="str"/>
+      <x:c r="J8" s="178" t="str"/>
+      <x:c r="K8" s="178" t="str"/>
+      <x:c r="L8" s="178" t="str"/>
+      <x:c r="M8" s="48"/>
+      <x:c r="N8" s="48"/>
+      <x:c r="O8" s="48"/>
+      <x:c r="P8" s="48"/>
+    </x:row>
+    <x:row r="9" ht="21" customHeight="1">
+      <x:c r="A9" s="168" t="str"/>
+      <x:c r="B9" s="169" t="str"/>
+      <x:c r="C9" s="170" t="str"/>
+      <x:c r="D9" s="408" t="str">
+        <x:v>集計期間</x:v>
+      </x:c>
+      <x:c r="E9" s="408" t="str"/>
+      <x:c r="F9" s="408" t="str">
+        <x:v>2026-08-01</x:v>
+      </x:c>
+      <x:c r="G9" s="408" t="str"/>
+      <x:c r="H9" s="408" t="str"/>
+      <x:c r="I9" s="408" t="str">
+        <x:v>～</x:v>
+      </x:c>
+      <x:c r="J9" s="408" t="str">
+        <x:v>2026-08-17</x:v>
+      </x:c>
+      <x:c r="K9" s="408" t="str"/>
+      <x:c r="L9" s="408" t="str"/>
+      <x:c r="M9" s="408" t="str">
+        <x:v>表示</x:v>
+      </x:c>
+      <x:c r="N9" s="408" t="str"/>
+      <x:c r="O9" s="408" t="str"/>
+      <x:c r="P9" s="408" t="str"/>
+    </x:row>
+    <x:row r="10" ht="21" customHeight="1">
+      <x:c r="A10" s="168" t="str"/>
+      <x:c r="B10" s="169" t="str"/>
+      <x:c r="C10" s="170" t="str"/>
+      <x:c r="D10" s="414" t="str">
+        <x:v>対象PJ数
+5</x:v>
+      </x:c>
+      <x:c r="E10" s="414" t="str"/>
+      <x:c r="F10" s="414" t="str"/>
+      <x:c r="G10" s="414" t="str"/>
+      <x:c r="H10" s="414" t="str">
+        <x:v>期限間近Task
+3</x:v>
+      </x:c>
+      <x:c r="I10" s="414" t="str"/>
+      <x:c r="J10" s="414" t="str"/>
+      <x:c r="K10" s="414" t="str"/>
+      <x:c r="L10" s="414" t="str">
+        <x:v>日報提出件数
+12</x:v>
+      </x:c>
+      <x:c r="M10" s="414" t="str"/>
+      <x:c r="N10" s="414" t="str"/>
+      <x:c r="O10" s="414" t="str"/>
+      <x:c r="P10" s="414" t="str"/>
+    </x:row>
+    <x:row r="11" ht="21" customHeight="1">
+      <x:c r="A11" s="168" t="str"/>
+      <x:c r="B11" s="169" t="str"/>
+      <x:c r="C11" s="170" t="str"/>
+      <x:c r="D11" s="414" t="str"/>
+      <x:c r="E11" s="414" t="str"/>
+      <x:c r="F11" s="414" t="str"/>
+      <x:c r="G11" s="414" t="str"/>
+      <x:c r="H11" s="414" t="str"/>
+      <x:c r="I11" s="414" t="str"/>
+      <x:c r="J11" s="414" t="str"/>
+      <x:c r="K11" s="414" t="str"/>
+      <x:c r="L11" s="414" t="str"/>
+      <x:c r="M11" s="414" t="str"/>
+      <x:c r="N11" s="414" t="str"/>
+      <x:c r="O11" s="414" t="str"/>
+      <x:c r="P11" s="414" t="str"/>
+    </x:row>
+    <x:row r="12" ht="21" customHeight="1">
+      <x:c r="A12" s="168" t="str"/>
+      <x:c r="B12" s="169" t="str"/>
+      <x:c r="C12" s="170" t="str"/>
+      <x:c r="D12" s="414" t="str"/>
+      <x:c r="E12" s="414" t="str"/>
+      <x:c r="F12" s="414" t="str"/>
+      <x:c r="G12" s="414" t="str"/>
+      <x:c r="H12" s="414" t="str"/>
+      <x:c r="I12" s="414" t="str"/>
+      <x:c r="J12" s="414" t="str"/>
+      <x:c r="K12" s="414" t="str"/>
+      <x:c r="L12" s="414" t="str"/>
+      <x:c r="M12" s="414" t="str"/>
+      <x:c r="N12" s="414" t="str"/>
+      <x:c r="O12" s="414" t="str"/>
+      <x:c r="P12" s="414" t="str"/>
+    </x:row>
+    <x:row r="13" ht="21" customHeight="1">
+      <x:c r="A13" s="168" t="str"/>
+      <x:c r="B13" s="169" t="str"/>
+      <x:c r="C13" s="170" t="str"/>
+      <x:c r="D13" s="414" t="str"/>
+      <x:c r="E13" s="414" t="str"/>
+      <x:c r="F13" s="414" t="str"/>
+      <x:c r="G13" s="414" t="str"/>
+      <x:c r="H13" s="414" t="str"/>
+      <x:c r="I13" s="414" t="str"/>
+      <x:c r="J13" s="414" t="str"/>
+      <x:c r="K13" s="414" t="str"/>
+      <x:c r="L13" s="414" t="str"/>
+      <x:c r="M13" s="414" t="str"/>
+      <x:c r="N13" s="414" t="str"/>
+      <x:c r="O13" s="414" t="str"/>
+      <x:c r="P13" s="414" t="str"/>
+    </x:row>
+    <x:row r="14" ht="21" customHeight="1">
+      <x:c r="A14" s="168" t="str"/>
+      <x:c r="B14" s="169" t="str"/>
+      <x:c r="C14" s="170" t="str"/>
+      <x:c r="D14"/>
+      <x:c r="E14"/>
+      <x:c r="F14"/>
+      <x:c r="G14"/>
+      <x:c r="H14"/>
+      <x:c r="I14"/>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
+      <x:c r="M14"/>
+      <x:c r="N14"/>
+      <x:c r="O14"/>
+      <x:c r="P14"/>
+    </x:row>
+    <x:row r="15" ht="21" customHeight="1">
+      <x:c r="A15" s="168" t="str"/>
+      <x:c r="B15" s="169" t="str"/>
+      <x:c r="C15" s="170" t="str"/>
+      <x:c r="D15" s="420" t="str">
+        <x:v>Task状態別件数</x:v>
+      </x:c>
+      <x:c r="E15" s="420" t="str"/>
+      <x:c r="F15" s="420" t="str"/>
+      <x:c r="G15" s="420" t="str"/>
+      <x:c r="H15" s="420" t="str"/>
+      <x:c r="I15" s="420" t="str"/>
+      <x:c r="J15" s="420" t="str"/>
+      <x:c r="K15" s="420" t="str">
+        <x:v>最近の通知（最大5件）</x:v>
+      </x:c>
+      <x:c r="L15" s="420" t="str"/>
+      <x:c r="M15" s="420" t="str"/>
+      <x:c r="N15" s="420" t="str"/>
+      <x:c r="O15" s="420" t="str"/>
+      <x:c r="P15" s="420" t="str"/>
+    </x:row>
+    <x:row r="16" ht="21" customHeight="1">
+      <x:c r="A16" s="168" t="str"/>
+      <x:c r="B16" s="169" t="str"/>
+      <x:c r="C16" s="170" t="str"/>
+      <x:c r="D16" s="420" t="str"/>
+      <x:c r="E16" s="420" t="str"/>
+      <x:c r="F16" s="420" t="str"/>
+      <x:c r="G16" s="420" t="str"/>
+      <x:c r="H16" s="420" t="str"/>
+      <x:c r="I16" s="420" t="str"/>
+      <x:c r="J16" s="420" t="str"/>
+      <x:c r="K16" s="420" t="str"/>
+      <x:c r="L16" s="420" t="str"/>
+      <x:c r="M16" s="420" t="str"/>
+      <x:c r="N16" s="420" t="str"/>
+      <x:c r="O16" s="420" t="str"/>
+      <x:c r="P16" s="420" t="str"/>
+    </x:row>
+    <x:row r="17" ht="21" customHeight="1">
+      <x:c r="A17" s="168" t="str"/>
+      <x:c r="B17" s="169" t="str"/>
+      <x:c r="C17" s="170" t="str"/>
+      <x:c r="D17" s="426" t="str">
+        <x:v>TODO              10件
+IN PROGRESS       8件
+REVIEW             3件
+COMPLETED         20件
+CANCELLED          1件</x:v>
+      </x:c>
+      <x:c r="E17" s="426" t="str"/>
+      <x:c r="F17" s="426" t="str"/>
+      <x:c r="G17" s="426" t="str"/>
+      <x:c r="H17" s="426" t="str"/>
+      <x:c r="I17" s="426" t="str"/>
+      <x:c r="J17" s="426" t="str"/>
+      <x:c r="K17" s="431" t="str">
+        <x:v>2026-08-17  Task期限通知  ［未読］</x:v>
+      </x:c>
+      <x:c r="L17" s="431" t="str"/>
+      <x:c r="M17" s="431" t="str"/>
+      <x:c r="N17" s="431" t="str"/>
+      <x:c r="O17" s="431" t="str"/>
+      <x:c r="P17" s="431" t="str"/>
+    </x:row>
+    <x:row r="18" ht="21" customHeight="1">
+      <x:c r="A18" s="168" t="str"/>
+      <x:c r="B18" s="169" t="str"/>
+      <x:c r="C18" s="170" t="str"/>
+      <x:c r="D18" s="426" t="str"/>
+      <x:c r="E18" s="426" t="str"/>
+      <x:c r="F18" s="426" t="str"/>
+      <x:c r="G18" s="426" t="str"/>
+      <x:c r="H18" s="426" t="str"/>
+      <x:c r="I18" s="426" t="str"/>
+      <x:c r="J18" s="426" t="str"/>
+      <x:c r="K18" s="431" t="str"/>
+      <x:c r="L18" s="431" t="str"/>
+      <x:c r="M18" s="431" t="str"/>
+      <x:c r="N18" s="431" t="str"/>
+      <x:c r="O18" s="431" t="str"/>
+      <x:c r="P18" s="431" t="str"/>
+    </x:row>
+    <x:row r="19" ht="21" customHeight="1">
+      <x:c r="A19" s="168" t="str"/>
+      <x:c r="B19" s="169" t="str"/>
+      <x:c r="C19" s="170" t="str"/>
+      <x:c r="D19" s="426" t="str"/>
+      <x:c r="E19" s="426" t="str"/>
+      <x:c r="F19" s="426" t="str"/>
+      <x:c r="G19" s="426" t="str"/>
+      <x:c r="H19" s="426" t="str"/>
+      <x:c r="I19" s="426" t="str"/>
+      <x:c r="J19" s="426" t="str"/>
+      <x:c r="K19" s="436" t="str">
+        <x:v>2026-08-16  日報未提出通知［未読］</x:v>
+      </x:c>
+      <x:c r="L19" s="436" t="str"/>
+      <x:c r="M19" s="436" t="str"/>
+      <x:c r="N19" s="436" t="str"/>
+      <x:c r="O19" s="436" t="str"/>
+      <x:c r="P19" s="436" t="str"/>
+    </x:row>
+    <x:row r="20" ht="21" customHeight="1">
+      <x:c r="A20" s="168" t="str"/>
+      <x:c r="B20" s="169" t="str"/>
+      <x:c r="C20" s="170" t="str"/>
+      <x:c r="D20" s="426" t="str"/>
+      <x:c r="E20" s="426" t="str"/>
+      <x:c r="F20" s="426" t="str"/>
+      <x:c r="G20" s="426" t="str"/>
+      <x:c r="H20" s="426" t="str"/>
+      <x:c r="I20" s="426" t="str"/>
+      <x:c r="J20" s="426" t="str"/>
+      <x:c r="K20" s="436" t="str"/>
+      <x:c r="L20" s="436" t="str"/>
+      <x:c r="M20" s="436" t="str"/>
+      <x:c r="N20" s="436" t="str"/>
+      <x:c r="O20" s="436" t="str"/>
+      <x:c r="P20" s="436" t="str"/>
+    </x:row>
+    <x:row r="21" ht="21" customHeight="1">
+      <x:c r="A21" s="168" t="str"/>
+      <x:c r="B21" s="169" t="str"/>
+      <x:c r="C21" s="170" t="str"/>
+      <x:c r="D21" s="426" t="str"/>
+      <x:c r="E21" s="426" t="str"/>
+      <x:c r="F21" s="426" t="str"/>
+      <x:c r="G21" s="426" t="str"/>
+      <x:c r="H21" s="426" t="str"/>
+      <x:c r="I21" s="426" t="str"/>
+      <x:c r="J21" s="426" t="str"/>
+      <x:c r="K21" s="431" t="str">
+        <x:v>2026-08-15  Task更新通知  ［既読］</x:v>
+      </x:c>
+      <x:c r="L21" s="431" t="str"/>
+      <x:c r="M21" s="431" t="str"/>
+      <x:c r="N21" s="431" t="str"/>
+      <x:c r="O21" s="431" t="str"/>
+      <x:c r="P21" s="431" t="str"/>
+    </x:row>
+    <x:row r="22" ht="21" customHeight="1">
+      <x:c r="A22" s="168" t="str"/>
+      <x:c r="B22" s="169" t="str"/>
+      <x:c r="C22" s="170" t="str"/>
+      <x:c r="D22" s="426" t="str"/>
+      <x:c r="E22" s="426" t="str"/>
+      <x:c r="F22" s="426" t="str"/>
+      <x:c r="G22" s="426" t="str"/>
+      <x:c r="H22" s="426" t="str"/>
+      <x:c r="I22" s="426" t="str"/>
+      <x:c r="J22" s="426" t="str"/>
+      <x:c r="K22" s="431" t="str"/>
+      <x:c r="L22" s="431" t="str"/>
+      <x:c r="M22" s="431" t="str"/>
+      <x:c r="N22" s="431" t="str"/>
+      <x:c r="O22" s="431" t="str"/>
+      <x:c r="P22" s="431" t="str"/>
+    </x:row>
+    <x:row r="23" ht="21" customHeight="1">
+      <x:c r="A23" s="168" t="str"/>
+      <x:c r="B23" s="169" t="str"/>
+      <x:c r="C23" s="170" t="str"/>
+      <x:c r="D23" s="426" t="str"/>
+      <x:c r="E23" s="426" t="str"/>
+      <x:c r="F23" s="426" t="str"/>
+      <x:c r="G23" s="426" t="str"/>
+      <x:c r="H23" s="426" t="str"/>
+      <x:c r="I23" s="426" t="str"/>
+      <x:c r="J23" s="426" t="str"/>
+      <x:c r="K23" s="436" t="str">
+        <x:v>2026-08-14  Project通知   ［既読］</x:v>
+      </x:c>
+      <x:c r="L23" s="436" t="str"/>
+      <x:c r="M23" s="436" t="str"/>
+      <x:c r="N23" s="436" t="str"/>
+      <x:c r="O23" s="436" t="str"/>
+      <x:c r="P23" s="436" t="str"/>
+    </x:row>
+    <x:row r="24" ht="21" customHeight="1">
+      <x:c r="A24" s="168" t="str"/>
+      <x:c r="B24" s="169" t="str"/>
+      <x:c r="C24" s="170" t="str"/>
+      <x:c r="D24" s="426" t="str"/>
+      <x:c r="E24" s="426" t="str"/>
+      <x:c r="F24" s="426" t="str"/>
+      <x:c r="G24" s="426" t="str"/>
+      <x:c r="H24" s="426" t="str"/>
+      <x:c r="I24" s="426" t="str"/>
+      <x:c r="J24" s="426" t="str"/>
+      <x:c r="K24" s="436" t="str"/>
+      <x:c r="L24" s="436" t="str"/>
+      <x:c r="M24" s="436" t="str"/>
+      <x:c r="N24" s="436" t="str"/>
+      <x:c r="O24" s="436" t="str"/>
+      <x:c r="P24" s="436" t="str"/>
+    </x:row>
+    <x:row r="25" ht="21" customHeight="1">
+      <x:c r="A25" s="168" t="str"/>
+      <x:c r="B25" s="169" t="str"/>
+      <x:c r="C25" s="170" t="str"/>
+      <x:c r="D25" s="426" t="str"/>
+      <x:c r="E25" s="426" t="str"/>
+      <x:c r="F25" s="426" t="str"/>
+      <x:c r="G25" s="426" t="str"/>
+      <x:c r="H25" s="426" t="str"/>
+      <x:c r="I25" s="426" t="str"/>
+      <x:c r="J25" s="426" t="str"/>
+      <x:c r="K25" s="431" t="str">
+        <x:v>2026-08-13  System通知    ［既読］</x:v>
+      </x:c>
+      <x:c r="L25" s="431" t="str"/>
+      <x:c r="M25" s="431" t="str"/>
+      <x:c r="N25" s="431" t="str"/>
+      <x:c r="O25" s="431" t="str"/>
+      <x:c r="P25" s="431" t="str"/>
+    </x:row>
+    <x:row r="26" ht="21" customHeight="1">
+      <x:c r="A26" s="168" t="str"/>
+      <x:c r="B26" s="169" t="str"/>
+      <x:c r="C26" s="170" t="str"/>
+      <x:c r="D26"/>
+      <x:c r="E26"/>
+      <x:c r="F26"/>
+      <x:c r="G26"/>
+      <x:c r="H26"/>
+      <x:c r="I26"/>
+      <x:c r="J26"/>
+      <x:c r="K26" s="431" t="str"/>
+      <x:c r="L26" s="431" t="str"/>
+      <x:c r="M26" s="431" t="str"/>
+      <x:c r="N26" s="431" t="str"/>
+      <x:c r="O26" s="431" t="str"/>
+      <x:c r="P26" s="431" t="str"/>
+    </x:row>
+    <x:row r="27" ht="21" customHeight="1">
+      <x:c r="A27" s="168" t="str"/>
+      <x:c r="B27" s="169" t="str"/>
+      <x:c r="C27" s="170" t="str"/>
+      <x:c r="D27" s="442" t="str">
+        <x:v>※ 対象PJ・Task状態・日報は指定期間で集計。期限間近Taskと最近通知は指定期間に連動しない。</x:v>
+      </x:c>
+      <x:c r="E27" s="442" t="str"/>
+      <x:c r="F27" s="442" t="str"/>
+      <x:c r="G27" s="442" t="str"/>
+      <x:c r="H27" s="442" t="str"/>
+      <x:c r="I27" s="442" t="str"/>
+      <x:c r="J27" s="442" t="str"/>
+      <x:c r="K27" s="442" t="str"/>
+      <x:c r="L27" s="442" t="str"/>
+      <x:c r="M27" s="442" t="str"/>
+      <x:c r="N27" s="442" t="str"/>
+      <x:c r="O27" s="442" t="str"/>
+      <x:c r="P27" s="442" t="str"/>
+    </x:row>
+    <x:row r="28" ht="21" customHeight="1">
+      <x:c r="A28" s="168" t="str"/>
+      <x:c r="B28" s="169" t="str"/>
+      <x:c r="C28" s="170" t="str"/>
+      <x:c r="D28" s="442" t="str"/>
+      <x:c r="E28" s="442" t="str"/>
+      <x:c r="F28" s="442" t="str"/>
+      <x:c r="G28" s="442" t="str"/>
+      <x:c r="H28" s="442" t="str"/>
+      <x:c r="I28" s="442" t="str"/>
+      <x:c r="J28" s="442" t="str"/>
+      <x:c r="K28" s="442" t="str"/>
+      <x:c r="L28" s="442" t="str"/>
+      <x:c r="M28" s="442" t="str"/>
+      <x:c r="N28" s="442" t="str"/>
+      <x:c r="O28" s="442" t="str"/>
+      <x:c r="P28" s="442" t="str"/>
+    </x:row>
+    <x:row r="29" ht="21" customHeight="1">
+      <x:c r="A29" s="168" t="str"/>
+      <x:c r="B29" s="169" t="str"/>
+      <x:c r="C29" s="170" t="str"/>
+      <x:c r="D29" s="48"/>
+      <x:c r="E29" s="48"/>
+      <x:c r="F29" s="48"/>
+      <x:c r="G29" s="48"/>
+      <x:c r="H29" s="48"/>
+      <x:c r="I29" s="48"/>
+      <x:c r="J29" s="48"/>
+      <x:c r="K29" s="48"/>
+      <x:c r="L29" s="48"/>
+      <x:c r="M29" s="48"/>
+      <x:c r="N29" s="48"/>
+      <x:c r="O29" s="48"/>
+      <x:c r="P29" s="48"/>
+    </x:row>
+    <x:row r="30" ht="21" customHeight="1">
+      <x:c r="A30" s="171" t="str"/>
+      <x:c r="B30" s="172" t="str"/>
+      <x:c r="C30" s="173" t="str"/>
+      <x:c r="D30" s="48"/>
+      <x:c r="E30" s="48"/>
+      <x:c r="F30" s="48"/>
+      <x:c r="G30" s="48"/>
+      <x:c r="H30" s="48"/>
+      <x:c r="I30" s="48"/>
+      <x:c r="J30" s="48"/>
+      <x:c r="K30" s="48"/>
+      <x:c r="L30" s="48"/>
+      <x:c r="M30" s="48"/>
+      <x:c r="N30" s="48"/>
+      <x:c r="O30" s="48"/>
+      <x:c r="P30" s="48"/>
+    </x:row>
+    <x:row r="31" ht="21" customHeight="1">
+      <x:c r="A31" s="48"/>
+      <x:c r="B31" s="48"/>
+      <x:c r="C31" s="48"/>
+      <x:c r="D31" s="48"/>
+      <x:c r="E31" s="48"/>
+      <x:c r="F31" s="48"/>
+      <x:c r="G31" s="48"/>
+      <x:c r="H31" s="48"/>
+      <x:c r="I31" s="48"/>
+      <x:c r="J31" s="48"/>
+      <x:c r="K31" s="48"/>
+      <x:c r="L31" s="48"/>
+      <x:c r="M31" s="48"/>
+      <x:c r="N31" s="48"/>
+      <x:c r="O31" s="48"/>
+      <x:c r="P31" s="48"/>
+    </x:row>
+    <x:row r="32" ht="21" customHeight="1">
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+      <x:c r="I32"/>
+      <x:c r="J32"/>
+      <x:c r="K32"/>
+      <x:c r="L32"/>
+      <x:c r="M32"/>
+      <x:c r="N32"/>
+      <x:c r="O32"/>
+      <x:c r="P32"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:P1"/>
+    <x:mergeCell ref="A2:H2"/>
+    <x:mergeCell ref="I2:P2"/>
+    <x:mergeCell ref="A32:P32"/>
+    <x:mergeCell ref="A4:P5"/>
+    <x:mergeCell ref="A6:C30"/>
+    <x:mergeCell ref="D6:P6"/>
+    <x:mergeCell ref="D7:L8"/>
+    <x:mergeCell ref="D9:E9"/>
+    <x:mergeCell ref="F9:H9"/>
+    <x:mergeCell ref="J9:L9"/>
+    <x:mergeCell ref="M9:P9"/>
+    <x:mergeCell ref="D10:G13"/>
+    <x:mergeCell ref="H10:K13"/>
+    <x:mergeCell ref="L10:P13"/>
+    <x:mergeCell ref="D15:J16"/>
+    <x:mergeCell ref="D17:J25"/>
+    <x:mergeCell ref="K15:P16"/>
+    <x:mergeCell ref="K17:P18"/>
+    <x:mergeCell ref="K19:P20"/>
+    <x:mergeCell ref="K21:P22"/>
+    <x:mergeCell ref="K23:P24"/>
+    <x:mergeCell ref="K25:P26"/>
+    <x:mergeCell ref="D27:P28"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -5377,103 +6372,45 @@
   <x:sheetData>
     <x:row r="1" ht="21" customHeight="1">
       <x:c r="A1" s="52" t="str">
-        <x:v>SCR-001  ログイン  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="B1" s="52" t="str">
-        <x:v>SCR-001  ログイン  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="C1" s="52" t="str">
-        <x:v>SCR-001  ログイン  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="D1" s="52" t="str">
-        <x:v>SCR-001  ログイン  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="E1" s="52" t="str">
-        <x:v>SCR-001  ログイン  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="F1" s="52" t="str">
-        <x:v>SCR-001  ログイン  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="G1" s="52" t="str">
-        <x:v>SCR-001  ログイン  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="H1" s="52" t="str">
-        <x:v>SCR-001  ログイン  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="I1" s="52" t="str">
-        <x:v>SCR-001  ログイン  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="J1" s="52" t="str">
-        <x:v>SCR-001  ログイン  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="K1" s="52" t="str">
-        <x:v>SCR-001  ログイン  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="L1" s="52" t="str">
-        <x:v>SCR-001  ログイン  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="M1" s="52" t="str">
-        <x:v>SCR-001  ログイン  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="N1" s="52" t="str">
-        <x:v>SCR-001  ログイン  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="O1" s="52" t="str">
-        <x:v>SCR-001  ログイン  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="P1" s="52" t="str">
-        <x:v>SCR-001  ログイン  画面レイアウト</x:v>
-      </x:c>
+        <x:v>SCR-026  パスワード変更  画面レイアウト</x:v>
+      </x:c>
+      <x:c r="B1" s="52" t="str"/>
+      <x:c r="C1" s="52" t="str"/>
+      <x:c r="D1" s="52" t="str"/>
+      <x:c r="E1" s="52" t="str"/>
+      <x:c r="F1" s="52" t="str"/>
+      <x:c r="G1" s="52" t="str"/>
+      <x:c r="H1" s="52" t="str"/>
+      <x:c r="I1" s="52" t="str"/>
+      <x:c r="J1" s="52" t="str"/>
+      <x:c r="K1" s="52" t="str"/>
+      <x:c r="L1" s="52" t="str"/>
+      <x:c r="M1" s="52" t="str"/>
+      <x:c r="N1" s="52" t="str"/>
+      <x:c r="O1" s="52" t="str"/>
+      <x:c r="P1" s="52" t="str"/>
     </x:row>
     <x:row r="2" ht="21" customHeight="1">
       <x:c r="A2" s="54" t="str">
-        <x:v>画面ID: SCR-001    画面名: ログイン</x:v>
-      </x:c>
-      <x:c r="B2" s="54" t="str">
-        <x:v>画面ID: SCR-001    画面名: ログイン</x:v>
-      </x:c>
-      <x:c r="C2" s="54" t="str">
-        <x:v>画面ID: SCR-001    画面名: ログイン</x:v>
-      </x:c>
-      <x:c r="D2" s="54" t="str">
-        <x:v>画面ID: SCR-001    画面名: ログイン</x:v>
-      </x:c>
-      <x:c r="E2" s="54" t="str">
-        <x:v>画面ID: SCR-001    画面名: ログイン</x:v>
-      </x:c>
-      <x:c r="F2" s="54" t="str">
-        <x:v>画面ID: SCR-001    画面名: ログイン</x:v>
-      </x:c>
-      <x:c r="G2" s="54" t="str">
-        <x:v>画面ID: SCR-001    画面名: ログイン</x:v>
-      </x:c>
-      <x:c r="H2" s="54" t="str">
-        <x:v>画面ID: SCR-001    画面名: ログイン</x:v>
-      </x:c>
-      <x:c r="I2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="J2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="K2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="L2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="M2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="N2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="O2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="P2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
+        <x:v>画面ID: SCR-026    画面名: パスワード変更</x:v>
+      </x:c>
+      <x:c r="B2" s="54" t="str"/>
+      <x:c r="C2" s="54" t="str"/>
+      <x:c r="D2" s="54" t="str"/>
+      <x:c r="E2" s="54" t="str"/>
+      <x:c r="F2" s="54" t="str"/>
+      <x:c r="G2" s="54" t="str"/>
+      <x:c r="H2" s="54" t="str"/>
+      <x:c r="I2" s="473" t="str">
+        <x:v>Ver.2.5    2026-09-24</x:v>
+      </x:c>
+      <x:c r="J2" s="55" t="str"/>
+      <x:c r="K2" s="55" t="str"/>
+      <x:c r="L2" s="55" t="str"/>
+      <x:c r="M2" s="55" t="str"/>
+      <x:c r="N2" s="55" t="str"/>
+      <x:c r="O2" s="55" t="str"/>
+      <x:c r="P2" s="55" t="str"/>
     </x:row>
     <x:row r="3" ht="21" customHeight="1">
       <x:c r="A3" s="48"/>
@@ -5497,101 +6434,39 @@
       <x:c r="A4" s="61" t="str">
         <x:v>Company WorkHub</x:v>
       </x:c>
-      <x:c r="B4" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="C4" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="D4" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="E4" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="F4" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="G4" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="H4" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="I4" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="J4" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="K4" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="L4" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="M4" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="N4" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="O4" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="P4" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
+      <x:c r="B4" s="61" t="str"/>
+      <x:c r="C4" s="61" t="str"/>
+      <x:c r="D4" s="61" t="str"/>
+      <x:c r="E4" s="61" t="str"/>
+      <x:c r="F4" s="61" t="str"/>
+      <x:c r="G4" s="61" t="str"/>
+      <x:c r="H4" s="61" t="str"/>
+      <x:c r="I4" s="61" t="str"/>
+      <x:c r="J4" s="61" t="str"/>
+      <x:c r="K4" s="61" t="str"/>
+      <x:c r="L4" s="61" t="str"/>
+      <x:c r="M4" s="61" t="str"/>
+      <x:c r="N4" s="61" t="str"/>
+      <x:c r="O4" s="61" t="str"/>
+      <x:c r="P4" s="61" t="str"/>
     </x:row>
     <x:row r="5" ht="21" customHeight="1">
-      <x:c r="A5" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="B5" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="C5" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="D5" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="E5" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="F5" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="G5" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="H5" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="I5" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="J5" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="K5" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="L5" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="M5" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="N5" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="O5" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="P5" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
+      <x:c r="A5" s="61" t="str"/>
+      <x:c r="B5" s="61" t="str"/>
+      <x:c r="C5" s="61" t="str"/>
+      <x:c r="D5" s="61" t="str"/>
+      <x:c r="E5" s="61" t="str"/>
+      <x:c r="F5" s="61" t="str"/>
+      <x:c r="G5" s="61" t="str"/>
+      <x:c r="H5" s="61" t="str"/>
+      <x:c r="I5" s="61" t="str"/>
+      <x:c r="J5" s="61" t="str"/>
+      <x:c r="K5" s="61" t="str"/>
+      <x:c r="L5" s="61" t="str"/>
+      <x:c r="M5" s="61" t="str"/>
+      <x:c r="N5" s="61" t="str"/>
+      <x:c r="O5" s="61" t="str"/>
+      <x:c r="P5" s="61" t="str"/>
     </x:row>
     <x:row r="6" ht="21" customHeight="1">
       <x:c r="A6" s="48"/>
@@ -5635,29 +6510,15 @@
       <x:c r="C8" s="48"/>
       <x:c r="D8" s="110"/>
       <x:c r="E8" s="75" t="str">
-        <x:v>LOGIN</x:v>
-      </x:c>
-      <x:c r="F8" s="76" t="str">
-        <x:v>LOGIN</x:v>
-      </x:c>
-      <x:c r="G8" s="76" t="str">
-        <x:v>LOGIN</x:v>
-      </x:c>
-      <x:c r="H8" s="76" t="str">
-        <x:v>LOGIN</x:v>
-      </x:c>
-      <x:c r="I8" s="76" t="str">
-        <x:v>LOGIN</x:v>
-      </x:c>
-      <x:c r="J8" s="76" t="str">
-        <x:v>LOGIN</x:v>
-      </x:c>
-      <x:c r="K8" s="76" t="str">
-        <x:v>LOGIN</x:v>
-      </x:c>
-      <x:c r="L8" s="77" t="str">
-        <x:v>LOGIN</x:v>
-      </x:c>
+        <x:v>PASSWORD CHANGE</x:v>
+      </x:c>
+      <x:c r="F8" s="76" t="str"/>
+      <x:c r="G8" s="76" t="str"/>
+      <x:c r="H8" s="76" t="str"/>
+      <x:c r="I8" s="76" t="str"/>
+      <x:c r="J8" s="76" t="str"/>
+      <x:c r="K8" s="76" t="str"/>
+      <x:c r="L8" s="77" t="str"/>
       <x:c r="M8" s="111"/>
       <x:c r="N8" s="48"/>
       <x:c r="O8" s="48"/>
@@ -5668,30 +6529,14 @@
       <x:c r="B9" s="48"/>
       <x:c r="C9" s="48"/>
       <x:c r="D9" s="110"/>
-      <x:c r="E9" s="78" t="str">
-        <x:v>LOGIN</x:v>
-      </x:c>
-      <x:c r="F9" s="79" t="str">
-        <x:v>LOGIN</x:v>
-      </x:c>
-      <x:c r="G9" s="79" t="str">
-        <x:v>LOGIN</x:v>
-      </x:c>
-      <x:c r="H9" s="79" t="str">
-        <x:v>LOGIN</x:v>
-      </x:c>
-      <x:c r="I9" s="79" t="str">
-        <x:v>LOGIN</x:v>
-      </x:c>
-      <x:c r="J9" s="79" t="str">
-        <x:v>LOGIN</x:v>
-      </x:c>
-      <x:c r="K9" s="79" t="str">
-        <x:v>LOGIN</x:v>
-      </x:c>
-      <x:c r="L9" s="80" t="str">
-        <x:v>LOGIN</x:v>
-      </x:c>
+      <x:c r="E9" s="78" t="str"/>
+      <x:c r="F9" s="79" t="str"/>
+      <x:c r="G9" s="79" t="str"/>
+      <x:c r="H9" s="79" t="str"/>
+      <x:c r="I9" s="79" t="str"/>
+      <x:c r="J9" s="79" t="str"/>
+      <x:c r="K9" s="79" t="str"/>
+      <x:c r="L9" s="80" t="str"/>
       <x:c r="M9" s="111"/>
       <x:c r="N9" s="48"/>
       <x:c r="O9" s="48"/>
@@ -5721,15 +6566,13 @@
       <x:c r="C11" s="48"/>
       <x:c r="D11" s="110"/>
       <x:c r="E11" s="113" t="str">
-        <x:v>1. ユーザー名</x:v>
-      </x:c>
-      <x:c r="F11" s="113" t="str">
-        <x:v>1. ユーザー名</x:v>
-      </x:c>
-      <x:c r="G11" s="113" t="str">
-        <x:v>1. ユーザー名</x:v>
-      </x:c>
-      <x:c r="H11" s="85" t="str"/>
+        <x:v>1. 現在Password</x:v>
+      </x:c>
+      <x:c r="F11" s="113" t="str"/>
+      <x:c r="G11" s="113" t="str"/>
+      <x:c r="H11" s="85" t="str">
+        <x:v>********</x:v>
+      </x:c>
       <x:c r="I11" s="85" t="str"/>
       <x:c r="J11" s="85" t="str"/>
       <x:c r="K11" s="85" t="str"/>
@@ -5763,29 +6606,17 @@
       <x:c r="C13" s="48"/>
       <x:c r="D13" s="110"/>
       <x:c r="E13" s="113" t="str">
-        <x:v>2. パスワード</x:v>
-      </x:c>
-      <x:c r="F13" s="113" t="str">
-        <x:v>2. パスワード</x:v>
-      </x:c>
-      <x:c r="G13" s="113" t="str">
-        <x:v>2. パスワード</x:v>
-      </x:c>
+        <x:v>2. 新Password</x:v>
+      </x:c>
+      <x:c r="F13" s="113" t="str"/>
+      <x:c r="G13" s="113" t="str"/>
       <x:c r="H13" s="85" t="str">
         <x:v>********</x:v>
       </x:c>
-      <x:c r="I13" s="85" t="str">
-        <x:v>********</x:v>
-      </x:c>
-      <x:c r="J13" s="85" t="str">
-        <x:v>********</x:v>
-      </x:c>
-      <x:c r="K13" s="85" t="str">
-        <x:v>********</x:v>
-      </x:c>
-      <x:c r="L13" s="85" t="str">
-        <x:v>********</x:v>
-      </x:c>
+      <x:c r="I13" s="85" t="str"/>
+      <x:c r="J13" s="85" t="str"/>
+      <x:c r="K13" s="85" t="str"/>
+      <x:c r="L13" s="85" t="str"/>
       <x:c r="M13" s="111"/>
       <x:c r="N13" s="48"/>
       <x:c r="O13" s="48"/>
@@ -5815,15 +6646,13 @@
       <x:c r="C15" s="48"/>
       <x:c r="D15" s="110"/>
       <x:c r="E15" s="113" t="str">
-        <x:v>3. ログイン保持</x:v>
-      </x:c>
-      <x:c r="F15" s="113" t="str">
-        <x:v>3. ログイン保持</x:v>
-      </x:c>
-      <x:c r="G15" s="113" t="str">
-        <x:v>3. ログイン保持</x:v>
-      </x:c>
-      <x:c r="H15" s="85" t="str"/>
+        <x:v>3. 確認</x:v>
+      </x:c>
+      <x:c r="F15" s="113" t="str"/>
+      <x:c r="G15" s="113" t="str"/>
+      <x:c r="H15" s="85" t="str">
+        <x:v>********</x:v>
+      </x:c>
       <x:c r="I15" s="85" t="str"/>
       <x:c r="J15" s="85" t="str"/>
       <x:c r="K15" s="85" t="str"/>
@@ -5856,30 +6685,18 @@
       <x:c r="B17" s="48"/>
       <x:c r="C17" s="48"/>
       <x:c r="D17" s="110"/>
-      <x:c r="E17" s="99" t="str">
-        <x:v>Login</x:v>
-      </x:c>
-      <x:c r="F17" s="100" t="str">
-        <x:v>Login</x:v>
-      </x:c>
-      <x:c r="G17" s="100" t="str">
-        <x:v>Login</x:v>
-      </x:c>
-      <x:c r="H17" s="100" t="str">
-        <x:v>Login</x:v>
-      </x:c>
-      <x:c r="I17" s="100" t="str">
-        <x:v>Login</x:v>
-      </x:c>
-      <x:c r="J17" s="100" t="str">
-        <x:v>Login</x:v>
-      </x:c>
-      <x:c r="K17" s="100" t="str">
-        <x:v>Login</x:v>
-      </x:c>
-      <x:c r="L17" s="101" t="str">
-        <x:v>Login</x:v>
-      </x:c>
+      <x:c r="E17" s="452" t="str">
+        <x:v>変更</x:v>
+      </x:c>
+      <x:c r="F17" s="452" t="str"/>
+      <x:c r="G17" s="452" t="str"/>
+      <x:c r="H17" s="452" t="str"/>
+      <x:c r="I17" s="462" t="str">
+        <x:v>取消</x:v>
+      </x:c>
+      <x:c r="J17" s="462" t="str"/>
+      <x:c r="K17" s="462" t="str"/>
+      <x:c r="L17" s="462" t="str"/>
       <x:c r="M17" s="111"/>
       <x:c r="N17" s="48"/>
       <x:c r="O17" s="48"/>
@@ -5890,30 +6707,14 @@
       <x:c r="B18" s="48"/>
       <x:c r="C18" s="48"/>
       <x:c r="D18" s="110"/>
-      <x:c r="E18" s="102" t="str">
-        <x:v>Login</x:v>
-      </x:c>
-      <x:c r="F18" s="103" t="str">
-        <x:v>Login</x:v>
-      </x:c>
-      <x:c r="G18" s="103" t="str">
-        <x:v>Login</x:v>
-      </x:c>
-      <x:c r="H18" s="103" t="str">
-        <x:v>Login</x:v>
-      </x:c>
-      <x:c r="I18" s="103" t="str">
-        <x:v>Login</x:v>
-      </x:c>
-      <x:c r="J18" s="103" t="str">
-        <x:v>Login</x:v>
-      </x:c>
-      <x:c r="K18" s="103" t="str">
-        <x:v>Login</x:v>
-      </x:c>
-      <x:c r="L18" s="104" t="str">
-        <x:v>Login</x:v>
-      </x:c>
+      <x:c r="E18" s="452" t="str"/>
+      <x:c r="F18" s="452" t="str"/>
+      <x:c r="G18" s="452" t="str"/>
+      <x:c r="H18" s="452" t="str"/>
+      <x:c r="I18" s="462" t="str"/>
+      <x:c r="J18" s="462" t="str"/>
+      <x:c r="K18" s="462" t="str"/>
+      <x:c r="L18" s="462" t="str"/>
       <x:c r="M18" s="111"/>
       <x:c r="N18" s="48"/>
       <x:c r="O18" s="48"/>
@@ -5942,30 +6743,16 @@
       <x:c r="B20" s="48"/>
       <x:c r="C20" s="48"/>
       <x:c r="D20" s="110"/>
-      <x:c r="E20" s="114" t="str">
-        <x:v>Passwordをお忘れの場合</x:v>
-      </x:c>
-      <x:c r="F20" s="114" t="str">
-        <x:v>Passwordをお忘れの場合</x:v>
-      </x:c>
-      <x:c r="G20" s="114" t="str">
-        <x:v>Passwordをお忘れの場合</x:v>
-      </x:c>
-      <x:c r="H20" s="114" t="str">
-        <x:v>Passwordをお忘れの場合</x:v>
-      </x:c>
-      <x:c r="I20" s="114" t="str">
-        <x:v>Passwordをお忘れの場合</x:v>
-      </x:c>
-      <x:c r="J20" s="114" t="str">
-        <x:v>Passwordをお忘れの場合</x:v>
-      </x:c>
-      <x:c r="K20" s="114" t="str">
-        <x:v>Passwordをお忘れの場合</x:v>
-      </x:c>
-      <x:c r="L20" s="114" t="str">
-        <x:v>Passwordをお忘れの場合</x:v>
-      </x:c>
+      <x:c r="E20" s="466" t="str">
+        <x:v>変更成功後はSessionを終了し、Login画面へ遷移します。</x:v>
+      </x:c>
+      <x:c r="F20" s="466" t="str"/>
+      <x:c r="G20" s="466" t="str"/>
+      <x:c r="H20" s="466" t="str"/>
+      <x:c r="I20" s="466" t="str"/>
+      <x:c r="J20" s="466" t="str"/>
+      <x:c r="K20" s="466" t="str"/>
+      <x:c r="L20" s="466" t="str"/>
       <x:c r="M20" s="111"/>
       <x:c r="N20" s="48"/>
       <x:c r="O20" s="48"/>
@@ -5976,14 +6763,14 @@
       <x:c r="B21" s="48"/>
       <x:c r="C21" s="48"/>
       <x:c r="D21" s="110"/>
-      <x:c r="E21" s="112"/>
-      <x:c r="F21" s="112"/>
-      <x:c r="G21" s="112"/>
-      <x:c r="H21" s="112"/>
-      <x:c r="I21" s="112"/>
-      <x:c r="J21" s="112"/>
-      <x:c r="K21" s="112"/>
-      <x:c r="L21" s="112"/>
+      <x:c r="E21" s="466" t="str"/>
+      <x:c r="F21" s="466" t="str"/>
+      <x:c r="G21" s="466" t="str"/>
+      <x:c r="H21" s="466" t="str"/>
+      <x:c r="I21" s="466" t="str"/>
+      <x:c r="J21" s="466" t="str"/>
+      <x:c r="K21" s="466" t="str"/>
+      <x:c r="L21" s="466" t="str"/>
       <x:c r="M21" s="111"/>
       <x:c r="N21" s="48"/>
       <x:c r="O21" s="48"/>
@@ -6201,8 +6988,9 @@
     <x:mergeCell ref="H13:L13"/>
     <x:mergeCell ref="E15:G15"/>
     <x:mergeCell ref="H15:L15"/>
-    <x:mergeCell ref="E17:L18"/>
-    <x:mergeCell ref="E20:L20"/>
+    <x:mergeCell ref="E17:H18"/>
+    <x:mergeCell ref="I17:L18"/>
+    <x:mergeCell ref="E20:L21"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -6212,2912 +7000,115 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="11" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="11" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="11" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="9" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="9" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="9" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="9" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="9" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="9" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="9" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="9" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="9" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="9" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="9" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="9" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="9" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="21" customHeight="1">
-      <x:c r="A1" s="52" t="str">
-        <x:v>SCR-002  ホームダッシュボード  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="B1" s="52" t="str">
-        <x:v>SCR-002  ホームダッシュボード  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="C1" s="52" t="str">
-        <x:v>SCR-002  ホームダッシュボード  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="D1" s="52" t="str">
-        <x:v>SCR-002  ホームダッシュボード  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="E1" s="52" t="str">
-        <x:v>SCR-002  ホームダッシュボード  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="F1" s="52" t="str">
-        <x:v>SCR-002  ホームダッシュボード  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="G1" s="52" t="str">
-        <x:v>SCR-002  ホームダッシュボード  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="H1" s="52" t="str">
-        <x:v>SCR-002  ホームダッシュボード  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="I1" s="52" t="str">
-        <x:v>SCR-002  ホームダッシュボード  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="J1" s="52" t="str">
-        <x:v>SCR-002  ホームダッシュボード  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="K1" s="52" t="str">
-        <x:v>SCR-002  ホームダッシュボード  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="L1" s="52" t="str">
-        <x:v>SCR-002  ホームダッシュボード  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="M1" s="52" t="str">
-        <x:v>SCR-002  ホームダッシュボード  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="N1" s="52" t="str">
-        <x:v>SCR-002  ホームダッシュボード  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="O1" s="52" t="str">
-        <x:v>SCR-002  ホームダッシュボード  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="P1" s="52" t="str">
-        <x:v>SCR-002  ホームダッシュボード  画面レイアウト</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="21" customHeight="1">
-      <x:c r="A2" s="54" t="str">
-        <x:v>画面ID: SCR-002    画面名: ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="B2" s="54" t="str">
-        <x:v>画面ID: SCR-002    画面名: ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="C2" s="54" t="str">
-        <x:v>画面ID: SCR-002    画面名: ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="D2" s="54" t="str">
-        <x:v>画面ID: SCR-002    画面名: ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="E2" s="54" t="str">
-        <x:v>画面ID: SCR-002    画面名: ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="F2" s="54" t="str">
-        <x:v>画面ID: SCR-002    画面名: ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="G2" s="54" t="str">
-        <x:v>画面ID: SCR-002    画面名: ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="H2" s="54" t="str">
-        <x:v>画面ID: SCR-002    画面名: ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="I2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="J2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="K2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="L2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="M2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="N2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="O2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="P2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="21" customHeight="1">
-      <x:c r="A3" s="48"/>
-      <x:c r="B3" s="48"/>
-      <x:c r="C3" s="48"/>
-      <x:c r="D3" s="48"/>
-      <x:c r="E3" s="48"/>
-      <x:c r="F3" s="48"/>
-      <x:c r="G3" s="48"/>
-      <x:c r="H3" s="48"/>
-      <x:c r="I3" s="48"/>
-      <x:c r="J3" s="48"/>
-      <x:c r="K3" s="48"/>
-      <x:c r="L3" s="48"/>
-      <x:c r="M3" s="48"/>
-      <x:c r="N3" s="48"/>
-      <x:c r="O3" s="48"/>
-      <x:c r="P3" s="48"/>
-    </x:row>
-    <x:row r="4" ht="21" customHeight="1">
-      <x:c r="A4" s="130" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="B4" s="131" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="C4" s="131" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="D4" s="131" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="E4" s="131" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="F4" s="131" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="G4" s="131" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="H4" s="131" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="I4" s="131" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="J4" s="131" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="K4" s="131" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="L4" s="131" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="M4" s="131" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="N4" s="131" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="O4" s="131" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="P4" s="132" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="21" customHeight="1">
-      <x:c r="A5" s="133" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="B5" s="134" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="C5" s="134" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="D5" s="134" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="E5" s="134" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="F5" s="134" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="G5" s="134" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="H5" s="134" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="I5" s="134" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="J5" s="134" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="K5" s="134" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="L5" s="134" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="M5" s="134" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="N5" s="134" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="O5" s="134" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-      <x:c r="P5" s="135" t="str">
-        <x:v>Company WorkHub    通知 3    ユーザー: 山田 太郎    Logout</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="21" customHeight="1">
-      <x:c r="A6" s="165" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B6" s="166" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C6" s="167" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="D6" s="176" t="str">
-        <x:v>Home  &gt;  ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="E6" s="176" t="str">
-        <x:v>Home  &gt;  ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="F6" s="176" t="str">
-        <x:v>Home  &gt;  ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="G6" s="176" t="str">
-        <x:v>Home  &gt;  ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="H6" s="176" t="str">
-        <x:v>Home  &gt;  ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="I6" s="176" t="str">
-        <x:v>Home  &gt;  ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="J6" s="176" t="str">
-        <x:v>Home  &gt;  ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="K6" s="176" t="str">
-        <x:v>Home  &gt;  ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="L6" s="176" t="str">
-        <x:v>Home  &gt;  ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="M6" s="176" t="str">
-        <x:v>Home  &gt;  ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="N6" s="176" t="str">
-        <x:v>Home  &gt;  ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="O6" s="176" t="str">
-        <x:v>Home  &gt;  ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="P6" s="176" t="str">
-        <x:v>Home  &gt;  ホームダッシュボード</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="21" customHeight="1">
-      <x:c r="A7" s="168" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B7" s="169" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C7" s="170" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="D7" s="178" t="str">
+    <x:row r="1">
+      <x:c r="A1" s="477" t="str">
+        <x:v>12_対象画面INDEX</x:v>
+      </x:c>
+      <x:c r="B1" s="476"/>
+      <x:c r="C1" s="476"/>
+      <x:c r="D1" s="476"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="476"/>
+      <x:c r="B2" s="476"/>
+      <x:c r="C2" s="476"/>
+      <x:c r="D2" s="476"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="476" t="str">
+        <x:v>Company WorkHub</x:v>
+      </x:c>
+      <x:c r="B3" s="476"/>
+      <x:c r="C3" s="476"/>
+      <x:c r="D3" s="476"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="476"/>
+      <x:c r="B4" s="476"/>
+      <x:c r="C4" s="476"/>
+      <x:c r="D4" s="476"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="476" t="str">
+        <x:v>BL-2026-09-24 / Review中</x:v>
+      </x:c>
+      <x:c r="B5" s="476"/>
+      <x:c r="C5" s="476"/>
+      <x:c r="D5" s="476"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="476"/>
+      <x:c r="B6" s="476"/>
+      <x:c r="C6" s="476"/>
+      <x:c r="D6" s="476"/>
+    </x:row>
+    <x:row r="7" ht="32" customHeight="1">
+      <x:c r="A7" s="479" t="str">
+        <x:v>画面ID</x:v>
+      </x:c>
+      <x:c r="B7" s="479" t="str">
+        <x:v>画面名</x:v>
+      </x:c>
+      <x:c r="C7" s="479" t="str">
+        <x:v>目的・主要操作</x:v>
+      </x:c>
+      <x:c r="D7" s="479" t="str">
+        <x:v>正本参照</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="A8" s="481" t="str">
+        <x:v>SCR-001</x:v>
+      </x:c>
+      <x:c r="B8" s="481" t="str">
+        <x:v>ログイン</x:v>
+      </x:c>
+      <x:c r="C8" s="481" t="str">
+        <x:v>ログイン</x:v>
+      </x:c>
+      <x:c r="D8" s="481" t="str">
+        <x:v>03／12_画面一覧・20_画面Route定義</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="A9" s="480" t="str">
+        <x:v>SCR-002</x:v>
+      </x:c>
+      <x:c r="B9" s="480" t="str">
         <x:v>ホームダッシュボード</x:v>
       </x:c>
-      <x:c r="E7" s="178" t="str">
-        <x:v>ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="F7" s="178" t="str">
-        <x:v>ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="G7" s="178" t="str">
-        <x:v>ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="H7" s="178" t="str">
-        <x:v>ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="I7" s="178" t="str">
-        <x:v>ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="J7" s="178" t="str">
-        <x:v>ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="K7" s="178" t="str">
-        <x:v>ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="L7" s="178" t="str">
-        <x:v>ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="M7" s="48"/>
-      <x:c r="N7" s="48"/>
-      <x:c r="O7" s="48"/>
-      <x:c r="P7" s="48"/>
-    </x:row>
-    <x:row r="8" ht="21" customHeight="1">
-      <x:c r="A8" s="168" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B8" s="169" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C8" s="170" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="D8" s="178" t="str">
-        <x:v>ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="E8" s="178" t="str">
-        <x:v>ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="F8" s="178" t="str">
-        <x:v>ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="G8" s="178" t="str">
-        <x:v>ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="H8" s="178" t="str">
-        <x:v>ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="I8" s="178" t="str">
-        <x:v>ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="J8" s="178" t="str">
-        <x:v>ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="K8" s="178" t="str">
-        <x:v>ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="L8" s="178" t="str">
-        <x:v>ホームダッシュボード</x:v>
-      </x:c>
-      <x:c r="M8" s="48"/>
-      <x:c r="N8" s="48"/>
-      <x:c r="O8" s="48"/>
-      <x:c r="P8" s="48"/>
-    </x:row>
-    <x:row r="9" ht="21" customHeight="1">
-      <x:c r="A9" s="168" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B9" s="169" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C9" s="170" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="D9" s="48"/>
-      <x:c r="E9" s="48"/>
-      <x:c r="F9" s="48"/>
-      <x:c r="G9" s="48"/>
-      <x:c r="H9" s="48"/>
-      <x:c r="I9" s="48"/>
-      <x:c r="J9" s="48"/>
-      <x:c r="K9" s="48"/>
-      <x:c r="L9" s="48"/>
-      <x:c r="M9" s="48"/>
-      <x:c r="N9" s="48"/>
-      <x:c r="O9" s="48"/>
-      <x:c r="P9" s="48"/>
-    </x:row>
-    <x:row r="10" ht="21" customHeight="1">
-      <x:c r="A10" s="168" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B10" s="169" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C10" s="170" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="D10" s="207" t="str">
-        <x:v>未完了Task
-24</x:v>
-      </x:c>
-      <x:c r="E10" s="208" t="str">
-        <x:v>未完了Task
-24</x:v>
-      </x:c>
-      <x:c r="F10" s="208" t="str">
-        <x:v>未完了Task
-24</x:v>
-      </x:c>
-      <x:c r="G10" s="209" t="str">
-        <x:v>未完了Task
-24</x:v>
-      </x:c>
-      <x:c r="H10" s="207" t="str">
-        <x:v>進行中PJ
-5</x:v>
-      </x:c>
-      <x:c r="I10" s="208" t="str">
-        <x:v>進行中PJ
-5</x:v>
-      </x:c>
-      <x:c r="J10" s="208" t="str">
-        <x:v>進行中PJ
-5</x:v>
-      </x:c>
-      <x:c r="K10" s="209" t="str">
-        <x:v>進行中PJ
-5</x:v>
-      </x:c>
-      <x:c r="L10" s="207" t="str">
-        <x:v>未読通知
-3</x:v>
-      </x:c>
-      <x:c r="M10" s="208" t="str">
-        <x:v>未読通知
-3</x:v>
-      </x:c>
-      <x:c r="N10" s="208" t="str">
-        <x:v>未読通知
-3</x:v>
-      </x:c>
-      <x:c r="O10" s="208" t="str">
-        <x:v>未読通知
-3</x:v>
-      </x:c>
-      <x:c r="P10" s="209" t="str">
-        <x:v>未読通知
-3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="21" customHeight="1">
-      <x:c r="A11" s="168" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B11" s="169" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C11" s="170" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="D11" s="210" t="str">
-        <x:v>未完了Task
-24</x:v>
-      </x:c>
-      <x:c r="E11" s="211" t="str">
-        <x:v>未完了Task
-24</x:v>
-      </x:c>
-      <x:c r="F11" s="211" t="str">
-        <x:v>未完了Task
-24</x:v>
-      </x:c>
-      <x:c r="G11" s="212" t="str">
-        <x:v>未完了Task
-24</x:v>
-      </x:c>
-      <x:c r="H11" s="210" t="str">
-        <x:v>進行中PJ
-5</x:v>
-      </x:c>
-      <x:c r="I11" s="211" t="str">
-        <x:v>進行中PJ
-5</x:v>
-      </x:c>
-      <x:c r="J11" s="211" t="str">
-        <x:v>進行中PJ
-5</x:v>
-      </x:c>
-      <x:c r="K11" s="212" t="str">
-        <x:v>進行中PJ
-5</x:v>
-      </x:c>
-      <x:c r="L11" s="210" t="str">
-        <x:v>未読通知
-3</x:v>
-      </x:c>
-      <x:c r="M11" s="211" t="str">
-        <x:v>未読通知
-3</x:v>
-      </x:c>
-      <x:c r="N11" s="211" t="str">
-        <x:v>未読通知
-3</x:v>
-      </x:c>
-      <x:c r="O11" s="211" t="str">
-        <x:v>未読通知
-3</x:v>
-      </x:c>
-      <x:c r="P11" s="212" t="str">
-        <x:v>未読通知
-3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="21" customHeight="1">
-      <x:c r="A12" s="168" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B12" s="169" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C12" s="170" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="D12" s="210" t="str">
-        <x:v>未完了Task
-24</x:v>
-      </x:c>
-      <x:c r="E12" s="211" t="str">
-        <x:v>未完了Task
-24</x:v>
-      </x:c>
-      <x:c r="F12" s="211" t="str">
-        <x:v>未完了Task
-24</x:v>
-      </x:c>
-      <x:c r="G12" s="212" t="str">
-        <x:v>未完了Task
-24</x:v>
-      </x:c>
-      <x:c r="H12" s="210" t="str">
-        <x:v>進行中PJ
-5</x:v>
-      </x:c>
-      <x:c r="I12" s="211" t="str">
-        <x:v>進行中PJ
-5</x:v>
-      </x:c>
-      <x:c r="J12" s="211" t="str">
-        <x:v>進行中PJ
-5</x:v>
-      </x:c>
-      <x:c r="K12" s="212" t="str">
-        <x:v>進行中PJ
-5</x:v>
-      </x:c>
-      <x:c r="L12" s="210" t="str">
-        <x:v>未読通知
-3</x:v>
-      </x:c>
-      <x:c r="M12" s="211" t="str">
-        <x:v>未読通知
-3</x:v>
-      </x:c>
-      <x:c r="N12" s="211" t="str">
-        <x:v>未読通知
-3</x:v>
-      </x:c>
-      <x:c r="O12" s="211" t="str">
-        <x:v>未読通知
-3</x:v>
-      </x:c>
-      <x:c r="P12" s="212" t="str">
-        <x:v>未読通知
-3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="21" customHeight="1">
-      <x:c r="A13" s="168" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B13" s="169" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C13" s="170" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="D13" s="213" t="str">
-        <x:v>未完了Task
-24</x:v>
-      </x:c>
-      <x:c r="E13" s="214" t="str">
-        <x:v>未完了Task
-24</x:v>
-      </x:c>
-      <x:c r="F13" s="214" t="str">
-        <x:v>未完了Task
-24</x:v>
-      </x:c>
-      <x:c r="G13" s="215" t="str">
-        <x:v>未完了Task
-24</x:v>
-      </x:c>
-      <x:c r="H13" s="213" t="str">
-        <x:v>進行中PJ
-5</x:v>
-      </x:c>
-      <x:c r="I13" s="214" t="str">
-        <x:v>進行中PJ
-5</x:v>
-      </x:c>
-      <x:c r="J13" s="214" t="str">
-        <x:v>進行中PJ
-5</x:v>
-      </x:c>
-      <x:c r="K13" s="215" t="str">
-        <x:v>進行中PJ
-5</x:v>
-      </x:c>
-      <x:c r="L13" s="213" t="str">
-        <x:v>未読通知
-3</x:v>
-      </x:c>
-      <x:c r="M13" s="214" t="str">
-        <x:v>未読通知
-3</x:v>
-      </x:c>
-      <x:c r="N13" s="214" t="str">
-        <x:v>未読通知
-3</x:v>
-      </x:c>
-      <x:c r="O13" s="214" t="str">
-        <x:v>未読通知
-3</x:v>
-      </x:c>
-      <x:c r="P13" s="215" t="str">
-        <x:v>未読通知
-3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="21" customHeight="1">
-      <x:c r="A14" s="168" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B14" s="169" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C14" s="170" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="D14" s="48"/>
-      <x:c r="E14" s="48"/>
-      <x:c r="F14" s="48"/>
-      <x:c r="G14" s="48"/>
-      <x:c r="H14" s="48"/>
-      <x:c r="I14" s="48"/>
-      <x:c r="J14" s="48"/>
-      <x:c r="K14" s="48"/>
-      <x:c r="L14" s="48"/>
-      <x:c r="M14" s="48"/>
-      <x:c r="N14" s="48"/>
-      <x:c r="O14" s="48"/>
-      <x:c r="P14" s="48"/>
-    </x:row>
-    <x:row r="15" ht="21" customHeight="1">
-      <x:c r="A15" s="168" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B15" s="169" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C15" s="170" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="D15" s="222" t="str">
-        <x:v>Task状態</x:v>
-      </x:c>
-      <x:c r="E15" s="223" t="str">
-        <x:v>Task状態</x:v>
-      </x:c>
-      <x:c r="F15" s="223" t="str">
-        <x:v>Task状態</x:v>
-      </x:c>
-      <x:c r="G15" s="223" t="str">
-        <x:v>Task状態</x:v>
-      </x:c>
-      <x:c r="H15" s="223" t="str">
-        <x:v>Task状態</x:v>
-      </x:c>
-      <x:c r="I15" s="223" t="str">
-        <x:v>Task状態</x:v>
-      </x:c>
-      <x:c r="J15" s="224" t="str">
-        <x:v>Task状態</x:v>
-      </x:c>
-      <x:c r="K15" s="222" t="str">
-        <x:v>最近の通知</x:v>
-      </x:c>
-      <x:c r="L15" s="223" t="str">
-        <x:v>最近の通知</x:v>
-      </x:c>
-      <x:c r="M15" s="223" t="str">
-        <x:v>最近の通知</x:v>
-      </x:c>
-      <x:c r="N15" s="223" t="str">
-        <x:v>最近の通知</x:v>
-      </x:c>
-      <x:c r="O15" s="223" t="str">
-        <x:v>最近の通知</x:v>
-      </x:c>
-      <x:c r="P15" s="224" t="str">
-        <x:v>最近の通知</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="21" customHeight="1">
-      <x:c r="A16" s="168" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B16" s="169" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C16" s="170" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="D16" s="225" t="str">
-        <x:v>Task状態</x:v>
-      </x:c>
-      <x:c r="E16" s="226" t="str">
-        <x:v>Task状態</x:v>
-      </x:c>
-      <x:c r="F16" s="226" t="str">
-        <x:v>Task状態</x:v>
-      </x:c>
-      <x:c r="G16" s="226" t="str">
-        <x:v>Task状態</x:v>
-      </x:c>
-      <x:c r="H16" s="226" t="str">
-        <x:v>Task状態</x:v>
-      </x:c>
-      <x:c r="I16" s="226" t="str">
-        <x:v>Task状態</x:v>
-      </x:c>
-      <x:c r="J16" s="227" t="str">
-        <x:v>Task状態</x:v>
-      </x:c>
-      <x:c r="K16" s="225" t="str">
-        <x:v>最近の通知</x:v>
-      </x:c>
-      <x:c r="L16" s="226" t="str">
-        <x:v>最近の通知</x:v>
-      </x:c>
-      <x:c r="M16" s="226" t="str">
-        <x:v>最近の通知</x:v>
-      </x:c>
-      <x:c r="N16" s="226" t="str">
-        <x:v>最近の通知</x:v>
-      </x:c>
-      <x:c r="O16" s="226" t="str">
-        <x:v>最近の通知</x:v>
-      </x:c>
-      <x:c r="P16" s="227" t="str">
-        <x:v>最近の通知</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="21" customHeight="1">
-      <x:c r="A17" s="168" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B17" s="169" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C17" s="170" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="D17" s="256" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="E17" s="257" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="F17" s="257" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="G17" s="257" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="H17" s="257" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="I17" s="257" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="J17" s="258" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="K17" s="267" t="str">
-        <x:v>2026-08-01  サンプル通知</x:v>
-      </x:c>
-      <x:c r="L17" s="267" t="str">
-        <x:v>2026-08-01  サンプル通知</x:v>
-      </x:c>
-      <x:c r="M17" s="267" t="str">
-        <x:v>2026-08-01  サンプル通知</x:v>
-      </x:c>
-      <x:c r="N17" s="267" t="str">
-        <x:v>2026-08-01  サンプル通知</x:v>
-      </x:c>
-      <x:c r="O17" s="267" t="str">
-        <x:v>2026-08-01  サンプル通知</x:v>
-      </x:c>
-      <x:c r="P17" s="267" t="str">
-        <x:v>2026-08-01  サンプル通知</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="21" customHeight="1">
-      <x:c r="A18" s="168" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B18" s="169" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C18" s="170" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="D18" s="259" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="E18" s="260" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="F18" s="260" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="G18" s="260" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="H18" s="260" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="I18" s="260" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="J18" s="261" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="K18" s="267" t="str">
-        <x:v>2026-08-01  サンプル通知</x:v>
-      </x:c>
-      <x:c r="L18" s="267" t="str">
-        <x:v>2026-08-01  サンプル通知</x:v>
-      </x:c>
-      <x:c r="M18" s="267" t="str">
-        <x:v>2026-08-01  サンプル通知</x:v>
-      </x:c>
-      <x:c r="N18" s="267" t="str">
-        <x:v>2026-08-01  サンプル通知</x:v>
-      </x:c>
-      <x:c r="O18" s="267" t="str">
-        <x:v>2026-08-01  サンプル通知</x:v>
-      </x:c>
-      <x:c r="P18" s="267" t="str">
-        <x:v>2026-08-01  サンプル通知</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="21" customHeight="1">
-      <x:c r="A19" s="168" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B19" s="169" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C19" s="170" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="D19" s="259" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="E19" s="260" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="F19" s="260" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="G19" s="260" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="H19" s="260" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="I19" s="260" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="J19" s="261" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="K19" s="270" t="str">
-        <x:v>2026-08-02  サンプル通知</x:v>
-      </x:c>
-      <x:c r="L19" s="270" t="str">
-        <x:v>2026-08-02  サンプル通知</x:v>
-      </x:c>
-      <x:c r="M19" s="270" t="str">
-        <x:v>2026-08-02  サンプル通知</x:v>
-      </x:c>
-      <x:c r="N19" s="270" t="str">
-        <x:v>2026-08-02  サンプル通知</x:v>
-      </x:c>
-      <x:c r="O19" s="270" t="str">
-        <x:v>2026-08-02  サンプル通知</x:v>
-      </x:c>
-      <x:c r="P19" s="270" t="str">
-        <x:v>2026-08-02  サンプル通知</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="21" customHeight="1">
-      <x:c r="A20" s="168" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B20" s="169" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C20" s="170" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="D20" s="259" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="E20" s="260" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="F20" s="260" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="G20" s="260" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="H20" s="260" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="I20" s="260" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="J20" s="261" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="K20" s="270" t="str">
-        <x:v>2026-08-02  サンプル通知</x:v>
-      </x:c>
-      <x:c r="L20" s="270" t="str">
-        <x:v>2026-08-02  サンプル通知</x:v>
-      </x:c>
-      <x:c r="M20" s="270" t="str">
-        <x:v>2026-08-02  サンプル通知</x:v>
-      </x:c>
-      <x:c r="N20" s="270" t="str">
-        <x:v>2026-08-02  サンプル通知</x:v>
-      </x:c>
-      <x:c r="O20" s="270" t="str">
-        <x:v>2026-08-02  サンプル通知</x:v>
-      </x:c>
-      <x:c r="P20" s="270" t="str">
-        <x:v>2026-08-02  サンプル通知</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="21" customHeight="1">
-      <x:c r="A21" s="168" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B21" s="169" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C21" s="170" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="D21" s="259" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="E21" s="260" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="F21" s="260" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="G21" s="260" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="H21" s="260" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="I21" s="260" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="J21" s="261" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="K21" s="267" t="str">
-        <x:v>2026-08-03  サンプル通知</x:v>
-      </x:c>
-      <x:c r="L21" s="267" t="str">
-        <x:v>2026-08-03  サンプル通知</x:v>
-      </x:c>
-      <x:c r="M21" s="267" t="str">
-        <x:v>2026-08-03  サンプル通知</x:v>
-      </x:c>
-      <x:c r="N21" s="267" t="str">
-        <x:v>2026-08-03  サンプル通知</x:v>
-      </x:c>
-      <x:c r="O21" s="267" t="str">
-        <x:v>2026-08-03  サンプル通知</x:v>
-      </x:c>
-      <x:c r="P21" s="267" t="str">
-        <x:v>2026-08-03  サンプル通知</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="21" customHeight="1">
-      <x:c r="A22" s="168" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B22" s="169" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C22" s="170" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="D22" s="259" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="E22" s="260" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="F22" s="260" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="G22" s="260" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="H22" s="260" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="I22" s="260" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="J22" s="261" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="K22" s="267" t="str">
-        <x:v>2026-08-03  サンプル通知</x:v>
-      </x:c>
-      <x:c r="L22" s="267" t="str">
-        <x:v>2026-08-03  サンプル通知</x:v>
-      </x:c>
-      <x:c r="M22" s="267" t="str">
-        <x:v>2026-08-03  サンプル通知</x:v>
-      </x:c>
-      <x:c r="N22" s="267" t="str">
-        <x:v>2026-08-03  サンプル通知</x:v>
-      </x:c>
-      <x:c r="O22" s="267" t="str">
-        <x:v>2026-08-03  サンプル通知</x:v>
-      </x:c>
-      <x:c r="P22" s="267" t="str">
-        <x:v>2026-08-03  サンプル通知</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="21" customHeight="1">
-      <x:c r="A23" s="168" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B23" s="169" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C23" s="170" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="D23" s="259" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="E23" s="260" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="F23" s="260" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="G23" s="260" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="H23" s="260" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="I23" s="260" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="J23" s="261" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="K23" s="270" t="str">
-        <x:v>2026-08-04  サンプル通知</x:v>
-      </x:c>
-      <x:c r="L23" s="270" t="str">
-        <x:v>2026-08-04  サンプル通知</x:v>
-      </x:c>
-      <x:c r="M23" s="270" t="str">
-        <x:v>2026-08-04  サンプル通知</x:v>
-      </x:c>
-      <x:c r="N23" s="270" t="str">
-        <x:v>2026-08-04  サンプル通知</x:v>
-      </x:c>
-      <x:c r="O23" s="270" t="str">
-        <x:v>2026-08-04  サンプル通知</x:v>
-      </x:c>
-      <x:c r="P23" s="270" t="str">
-        <x:v>2026-08-04  サンプル通知</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="21" customHeight="1">
-      <x:c r="A24" s="168" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B24" s="169" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C24" s="170" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="D24" s="259" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="E24" s="260" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="F24" s="260" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="G24" s="260" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="H24" s="260" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="I24" s="260" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="J24" s="261" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="K24" s="270" t="str">
-        <x:v>2026-08-04  サンプル通知</x:v>
-      </x:c>
-      <x:c r="L24" s="270" t="str">
-        <x:v>2026-08-04  サンプル通知</x:v>
-      </x:c>
-      <x:c r="M24" s="270" t="str">
-        <x:v>2026-08-04  サンプル通知</x:v>
-      </x:c>
-      <x:c r="N24" s="270" t="str">
-        <x:v>2026-08-04  サンプル通知</x:v>
-      </x:c>
-      <x:c r="O24" s="270" t="str">
-        <x:v>2026-08-04  サンプル通知</x:v>
-      </x:c>
-      <x:c r="P24" s="270" t="str">
-        <x:v>2026-08-04  サンプル通知</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="21" customHeight="1">
-      <x:c r="A25" s="168" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B25" s="169" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C25" s="170" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="D25" s="262" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="E25" s="263" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="F25" s="263" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="G25" s="263" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="H25" s="263" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="I25" s="263" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="J25" s="264" t="str">
-        <x:v>TODO  35%
-IN PROGRESS  30%
-REVIEW  15%
-COMPLETED  20%</x:v>
-      </x:c>
-      <x:c r="K25" s="267" t="str">
-        <x:v>2026-08-05  サンプル通知</x:v>
-      </x:c>
-      <x:c r="L25" s="267" t="str">
-        <x:v>2026-08-05  サンプル通知</x:v>
-      </x:c>
-      <x:c r="M25" s="267" t="str">
-        <x:v>2026-08-05  サンプル通知</x:v>
-      </x:c>
-      <x:c r="N25" s="267" t="str">
-        <x:v>2026-08-05  サンプル通知</x:v>
-      </x:c>
-      <x:c r="O25" s="267" t="str">
-        <x:v>2026-08-05  サンプル通知</x:v>
-      </x:c>
-      <x:c r="P25" s="267" t="str">
-        <x:v>2026-08-05  サンプル通知</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" ht="21" customHeight="1">
-      <x:c r="A26" s="168" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B26" s="169" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C26" s="170" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="D26" s="48"/>
-      <x:c r="E26" s="48"/>
-      <x:c r="F26" s="48"/>
-      <x:c r="G26" s="48"/>
-      <x:c r="H26" s="48"/>
-      <x:c r="I26" s="48"/>
-      <x:c r="J26" s="48"/>
-      <x:c r="K26" s="267" t="str">
-        <x:v>2026-08-05  サンプル通知</x:v>
-      </x:c>
-      <x:c r="L26" s="267" t="str">
-        <x:v>2026-08-05  サンプル通知</x:v>
-      </x:c>
-      <x:c r="M26" s="267" t="str">
-        <x:v>2026-08-05  サンプル通知</x:v>
-      </x:c>
-      <x:c r="N26" s="267" t="str">
-        <x:v>2026-08-05  サンプル通知</x:v>
-      </x:c>
-      <x:c r="O26" s="267" t="str">
-        <x:v>2026-08-05  サンプル通知</x:v>
-      </x:c>
-      <x:c r="P26" s="267" t="str">
-        <x:v>2026-08-05  サンプル通知</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="21" customHeight="1">
-      <x:c r="A27" s="168" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B27" s="169" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C27" s="170" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="D27" s="48"/>
-      <x:c r="E27" s="48"/>
-      <x:c r="F27" s="48"/>
-      <x:c r="G27" s="48"/>
-      <x:c r="H27" s="48"/>
-      <x:c r="I27" s="48"/>
-      <x:c r="J27" s="48"/>
-      <x:c r="K27" s="48"/>
-      <x:c r="L27" s="48"/>
-      <x:c r="M27" s="48"/>
-      <x:c r="N27" s="48"/>
-      <x:c r="O27" s="48"/>
-      <x:c r="P27" s="48"/>
-    </x:row>
-    <x:row r="28" ht="21" customHeight="1">
-      <x:c r="A28" s="168" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B28" s="169" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C28" s="170" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="D28" s="48"/>
-      <x:c r="E28" s="48"/>
-      <x:c r="F28" s="48"/>
-      <x:c r="G28" s="48"/>
-      <x:c r="H28" s="48"/>
-      <x:c r="I28" s="48"/>
-      <x:c r="J28" s="48"/>
-      <x:c r="K28" s="48"/>
-      <x:c r="L28" s="48"/>
-      <x:c r="M28" s="48"/>
-      <x:c r="N28" s="48"/>
-      <x:c r="O28" s="48"/>
-      <x:c r="P28" s="48"/>
-    </x:row>
-    <x:row r="29" ht="21" customHeight="1">
-      <x:c r="A29" s="168" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B29" s="169" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C29" s="170" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="D29" s="48"/>
-      <x:c r="E29" s="48"/>
-      <x:c r="F29" s="48"/>
-      <x:c r="G29" s="48"/>
-      <x:c r="H29" s="48"/>
-      <x:c r="I29" s="48"/>
-      <x:c r="J29" s="48"/>
-      <x:c r="K29" s="48"/>
-      <x:c r="L29" s="48"/>
-      <x:c r="M29" s="48"/>
-      <x:c r="N29" s="48"/>
-      <x:c r="O29" s="48"/>
-      <x:c r="P29" s="48"/>
-    </x:row>
-    <x:row r="30" ht="21" customHeight="1">
-      <x:c r="A30" s="171" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="B30" s="172" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="C30" s="173" t="str">
-        <x:v>Home
-組織管理
-プロジェクト
-タスク
-日報
-通知
-System</x:v>
-      </x:c>
-      <x:c r="D30" s="48"/>
-      <x:c r="E30" s="48"/>
-      <x:c r="F30" s="48"/>
-      <x:c r="G30" s="48"/>
-      <x:c r="H30" s="48"/>
-      <x:c r="I30" s="48"/>
-      <x:c r="J30" s="48"/>
-      <x:c r="K30" s="48"/>
-      <x:c r="L30" s="48"/>
-      <x:c r="M30" s="48"/>
-      <x:c r="N30" s="48"/>
-      <x:c r="O30" s="48"/>
-      <x:c r="P30" s="48"/>
-    </x:row>
-    <x:row r="31" ht="21" customHeight="1">
-      <x:c r="A31" s="48"/>
-      <x:c r="B31" s="48"/>
-      <x:c r="C31" s="48"/>
-      <x:c r="D31" s="48"/>
-      <x:c r="E31" s="48"/>
-      <x:c r="F31" s="48"/>
-      <x:c r="G31" s="48"/>
-      <x:c r="H31" s="48"/>
-      <x:c r="I31" s="48"/>
-      <x:c r="J31" s="48"/>
-      <x:c r="K31" s="48"/>
-      <x:c r="L31" s="48"/>
-      <x:c r="M31" s="48"/>
-      <x:c r="N31" s="48"/>
-      <x:c r="O31" s="48"/>
-      <x:c r="P31" s="48"/>
-    </x:row>
-    <x:row r="32" ht="21" customHeight="1">
-      <x:c r="A32"/>
-      <x:c r="B32"/>
-      <x:c r="C32"/>
-      <x:c r="D32"/>
-      <x:c r="E32"/>
-      <x:c r="F32"/>
-      <x:c r="G32"/>
-      <x:c r="H32"/>
-      <x:c r="I32"/>
-      <x:c r="J32"/>
-      <x:c r="K32"/>
-      <x:c r="L32"/>
-      <x:c r="M32"/>
-      <x:c r="N32"/>
-      <x:c r="O32"/>
-      <x:c r="P32"/>
+      <x:c r="C9" s="480" t="str">
+        <x:v>期間指定/表示</x:v>
+      </x:c>
+      <x:c r="D9" s="480" t="str">
+        <x:v>03／12_画面一覧・20_画面Route定義</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="42" customHeight="1">
+      <x:c r="A10" s="481" t="str">
+        <x:v>SCR-026</x:v>
+      </x:c>
+      <x:c r="B10" s="481" t="str">
+        <x:v>パスワード変更</x:v>
+      </x:c>
+      <x:c r="C10" s="481" t="str">
+        <x:v>Password変更/取消</x:v>
+      </x:c>
+      <x:c r="D10" s="481" t="str">
+        <x:v>03／12_画面一覧・20_画面Route定義</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:P1"/>
-    <x:mergeCell ref="A2:H2"/>
-    <x:mergeCell ref="I2:P2"/>
-    <x:mergeCell ref="A32:P32"/>
-    <x:mergeCell ref="A4:P5"/>
-    <x:mergeCell ref="A6:C30"/>
-    <x:mergeCell ref="D6:P6"/>
-    <x:mergeCell ref="D7:L8"/>
-    <x:mergeCell ref="D10:G13"/>
-    <x:mergeCell ref="H10:K13"/>
-    <x:mergeCell ref="L10:P13"/>
-    <x:mergeCell ref="D15:J16"/>
-    <x:mergeCell ref="D17:J25"/>
-    <x:mergeCell ref="K15:P16"/>
-    <x:mergeCell ref="K17:P18"/>
-    <x:mergeCell ref="K19:P20"/>
-    <x:mergeCell ref="K21:P22"/>
-    <x:mergeCell ref="K23:P24"/>
-    <x:mergeCell ref="K25:P26"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="11" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="11" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="11" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="9" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="9" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="9" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="9" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="9" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="9" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="9" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="9" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="9" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="9" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="9" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="9" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="9" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="21" customHeight="1">
-      <x:c r="A1" s="52" t="str">
-        <x:v>SCR-026  パスワード変更  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="B1" s="52" t="str">
-        <x:v>SCR-026  パスワード変更  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="C1" s="52" t="str">
-        <x:v>SCR-026  パスワード変更  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="D1" s="52" t="str">
-        <x:v>SCR-026  パスワード変更  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="E1" s="52" t="str">
-        <x:v>SCR-026  パスワード変更  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="F1" s="52" t="str">
-        <x:v>SCR-026  パスワード変更  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="G1" s="52" t="str">
-        <x:v>SCR-026  パスワード変更  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="H1" s="52" t="str">
-        <x:v>SCR-026  パスワード変更  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="I1" s="52" t="str">
-        <x:v>SCR-026  パスワード変更  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="J1" s="52" t="str">
-        <x:v>SCR-026  パスワード変更  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="K1" s="52" t="str">
-        <x:v>SCR-026  パスワード変更  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="L1" s="52" t="str">
-        <x:v>SCR-026  パスワード変更  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="M1" s="52" t="str">
-        <x:v>SCR-026  パスワード変更  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="N1" s="52" t="str">
-        <x:v>SCR-026  パスワード変更  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="O1" s="52" t="str">
-        <x:v>SCR-026  パスワード変更  画面レイアウト</x:v>
-      </x:c>
-      <x:c r="P1" s="52" t="str">
-        <x:v>SCR-026  パスワード変更  画面レイアウト</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="21" customHeight="1">
-      <x:c r="A2" s="54" t="str">
-        <x:v>画面ID: SCR-026    画面名: パスワード変更</x:v>
-      </x:c>
-      <x:c r="B2" s="54" t="str">
-        <x:v>画面ID: SCR-026    画面名: パスワード変更</x:v>
-      </x:c>
-      <x:c r="C2" s="54" t="str">
-        <x:v>画面ID: SCR-026    画面名: パスワード変更</x:v>
-      </x:c>
-      <x:c r="D2" s="54" t="str">
-        <x:v>画面ID: SCR-026    画面名: パスワード変更</x:v>
-      </x:c>
-      <x:c r="E2" s="54" t="str">
-        <x:v>画面ID: SCR-026    画面名: パスワード変更</x:v>
-      </x:c>
-      <x:c r="F2" s="54" t="str">
-        <x:v>画面ID: SCR-026    画面名: パスワード変更</x:v>
-      </x:c>
-      <x:c r="G2" s="54" t="str">
-        <x:v>画面ID: SCR-026    画面名: パスワード変更</x:v>
-      </x:c>
-      <x:c r="H2" s="54" t="str">
-        <x:v>画面ID: SCR-026    画面名: パスワード変更</x:v>
-      </x:c>
-      <x:c r="I2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="J2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="K2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="L2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="M2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="N2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="O2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-      <x:c r="P2" s="55" t="str">
-        <x:v>Ver.1.2    2026-08-05</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="21" customHeight="1">
-      <x:c r="A3" s="48"/>
-      <x:c r="B3" s="48"/>
-      <x:c r="C3" s="48"/>
-      <x:c r="D3" s="48"/>
-      <x:c r="E3" s="48"/>
-      <x:c r="F3" s="48"/>
-      <x:c r="G3" s="48"/>
-      <x:c r="H3" s="48"/>
-      <x:c r="I3" s="48"/>
-      <x:c r="J3" s="48"/>
-      <x:c r="K3" s="48"/>
-      <x:c r="L3" s="48"/>
-      <x:c r="M3" s="48"/>
-      <x:c r="N3" s="48"/>
-      <x:c r="O3" s="48"/>
-      <x:c r="P3" s="48"/>
-    </x:row>
-    <x:row r="4" ht="21" customHeight="1">
-      <x:c r="A4" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="B4" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="C4" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="D4" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="E4" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="F4" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="G4" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="H4" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="I4" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="J4" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="K4" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="L4" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="M4" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="N4" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="O4" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="P4" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="21" customHeight="1">
-      <x:c r="A5" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="B5" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="C5" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="D5" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="E5" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="F5" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="G5" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="H5" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="I5" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="J5" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="K5" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="L5" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="M5" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="N5" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="O5" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="P5" s="61" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="21" customHeight="1">
-      <x:c r="A6" s="48"/>
-      <x:c r="B6" s="48"/>
-      <x:c r="C6" s="48"/>
-      <x:c r="D6" s="48"/>
-      <x:c r="E6" s="48"/>
-      <x:c r="F6" s="48"/>
-      <x:c r="G6" s="48"/>
-      <x:c r="H6" s="48"/>
-      <x:c r="I6" s="48"/>
-      <x:c r="J6" s="48"/>
-      <x:c r="K6" s="48"/>
-      <x:c r="L6" s="48"/>
-      <x:c r="M6" s="48"/>
-      <x:c r="N6" s="48"/>
-      <x:c r="O6" s="48"/>
-      <x:c r="P6" s="48"/>
-    </x:row>
-    <x:row r="7" ht="21" customHeight="1">
-      <x:c r="A7" s="48"/>
-      <x:c r="B7" s="48"/>
-      <x:c r="C7" s="48"/>
-      <x:c r="D7" s="107"/>
-      <x:c r="E7" s="108"/>
-      <x:c r="F7" s="108"/>
-      <x:c r="G7" s="108"/>
-      <x:c r="H7" s="108"/>
-      <x:c r="I7" s="108"/>
-      <x:c r="J7" s="108"/>
-      <x:c r="K7" s="108"/>
-      <x:c r="L7" s="108"/>
-      <x:c r="M7" s="109"/>
-      <x:c r="N7" s="48"/>
-      <x:c r="O7" s="48"/>
-      <x:c r="P7" s="48"/>
-    </x:row>
-    <x:row r="8" ht="21" customHeight="1">
-      <x:c r="A8" s="48"/>
-      <x:c r="B8" s="48"/>
-      <x:c r="C8" s="48"/>
-      <x:c r="D8" s="110"/>
-      <x:c r="E8" s="75" t="str">
-        <x:v>PASSWORD CHANGE</x:v>
-      </x:c>
-      <x:c r="F8" s="76" t="str">
-        <x:v>PASSWORD CHANGE</x:v>
-      </x:c>
-      <x:c r="G8" s="76" t="str">
-        <x:v>PASSWORD CHANGE</x:v>
-      </x:c>
-      <x:c r="H8" s="76" t="str">
-        <x:v>PASSWORD CHANGE</x:v>
-      </x:c>
-      <x:c r="I8" s="76" t="str">
-        <x:v>PASSWORD CHANGE</x:v>
-      </x:c>
-      <x:c r="J8" s="76" t="str">
-        <x:v>PASSWORD CHANGE</x:v>
-      </x:c>
-      <x:c r="K8" s="76" t="str">
-        <x:v>PASSWORD CHANGE</x:v>
-      </x:c>
-      <x:c r="L8" s="77" t="str">
-        <x:v>PASSWORD CHANGE</x:v>
-      </x:c>
-      <x:c r="M8" s="111"/>
-      <x:c r="N8" s="48"/>
-      <x:c r="O8" s="48"/>
-      <x:c r="P8" s="48"/>
-    </x:row>
-    <x:row r="9" ht="21" customHeight="1">
-      <x:c r="A9" s="48"/>
-      <x:c r="B9" s="48"/>
-      <x:c r="C9" s="48"/>
-      <x:c r="D9" s="110"/>
-      <x:c r="E9" s="78" t="str">
-        <x:v>PASSWORD CHANGE</x:v>
-      </x:c>
-      <x:c r="F9" s="79" t="str">
-        <x:v>PASSWORD CHANGE</x:v>
-      </x:c>
-      <x:c r="G9" s="79" t="str">
-        <x:v>PASSWORD CHANGE</x:v>
-      </x:c>
-      <x:c r="H9" s="79" t="str">
-        <x:v>PASSWORD CHANGE</x:v>
-      </x:c>
-      <x:c r="I9" s="79" t="str">
-        <x:v>PASSWORD CHANGE</x:v>
-      </x:c>
-      <x:c r="J9" s="79" t="str">
-        <x:v>PASSWORD CHANGE</x:v>
-      </x:c>
-      <x:c r="K9" s="79" t="str">
-        <x:v>PASSWORD CHANGE</x:v>
-      </x:c>
-      <x:c r="L9" s="80" t="str">
-        <x:v>PASSWORD CHANGE</x:v>
-      </x:c>
-      <x:c r="M9" s="111"/>
-      <x:c r="N9" s="48"/>
-      <x:c r="O9" s="48"/>
-      <x:c r="P9" s="48"/>
-    </x:row>
-    <x:row r="10" ht="21" customHeight="1">
-      <x:c r="A10" s="48"/>
-      <x:c r="B10" s="48"/>
-      <x:c r="C10" s="48"/>
-      <x:c r="D10" s="110"/>
-      <x:c r="E10" s="112"/>
-      <x:c r="F10" s="112"/>
-      <x:c r="G10" s="112"/>
-      <x:c r="H10" s="112"/>
-      <x:c r="I10" s="112"/>
-      <x:c r="J10" s="112"/>
-      <x:c r="K10" s="112"/>
-      <x:c r="L10" s="112"/>
-      <x:c r="M10" s="111"/>
-      <x:c r="N10" s="48"/>
-      <x:c r="O10" s="48"/>
-      <x:c r="P10" s="48"/>
-    </x:row>
-    <x:row r="11" ht="21" customHeight="1">
-      <x:c r="A11" s="48"/>
-      <x:c r="B11" s="48"/>
-      <x:c r="C11" s="48"/>
-      <x:c r="D11" s="110"/>
-      <x:c r="E11" s="113" t="str">
-        <x:v>1. 現在Password</x:v>
-      </x:c>
-      <x:c r="F11" s="113" t="str">
-        <x:v>1. 現在Password</x:v>
-      </x:c>
-      <x:c r="G11" s="113" t="str">
-        <x:v>1. 現在Password</x:v>
-      </x:c>
-      <x:c r="H11" s="85" t="str">
-        <x:v>********</x:v>
-      </x:c>
-      <x:c r="I11" s="85" t="str">
-        <x:v>********</x:v>
-      </x:c>
-      <x:c r="J11" s="85" t="str">
-        <x:v>********</x:v>
-      </x:c>
-      <x:c r="K11" s="85" t="str">
-        <x:v>********</x:v>
-      </x:c>
-      <x:c r="L11" s="85" t="str">
-        <x:v>********</x:v>
-      </x:c>
-      <x:c r="M11" s="111"/>
-      <x:c r="N11" s="48"/>
-      <x:c r="O11" s="48"/>
-      <x:c r="P11" s="48"/>
-    </x:row>
-    <x:row r="12" ht="21" customHeight="1">
-      <x:c r="A12" s="48"/>
-      <x:c r="B12" s="48"/>
-      <x:c r="C12" s="48"/>
-      <x:c r="D12" s="110"/>
-      <x:c r="E12" s="112"/>
-      <x:c r="F12" s="112"/>
-      <x:c r="G12" s="112"/>
-      <x:c r="H12" s="112"/>
-      <x:c r="I12" s="112"/>
-      <x:c r="J12" s="112"/>
-      <x:c r="K12" s="112"/>
-      <x:c r="L12" s="112"/>
-      <x:c r="M12" s="111"/>
-      <x:c r="N12" s="48"/>
-      <x:c r="O12" s="48"/>
-      <x:c r="P12" s="48"/>
-    </x:row>
-    <x:row r="13" ht="21" customHeight="1">
-      <x:c r="A13" s="48"/>
-      <x:c r="B13" s="48"/>
-      <x:c r="C13" s="48"/>
-      <x:c r="D13" s="110"/>
-      <x:c r="E13" s="113" t="str">
-        <x:v>2. 新Password</x:v>
-      </x:c>
-      <x:c r="F13" s="113" t="str">
-        <x:v>2. 新Password</x:v>
-      </x:c>
-      <x:c r="G13" s="113" t="str">
-        <x:v>2. 新Password</x:v>
-      </x:c>
-      <x:c r="H13" s="85" t="str">
-        <x:v>********</x:v>
-      </x:c>
-      <x:c r="I13" s="85" t="str">
-        <x:v>********</x:v>
-      </x:c>
-      <x:c r="J13" s="85" t="str">
-        <x:v>********</x:v>
-      </x:c>
-      <x:c r="K13" s="85" t="str">
-        <x:v>********</x:v>
-      </x:c>
-      <x:c r="L13" s="85" t="str">
-        <x:v>********</x:v>
-      </x:c>
-      <x:c r="M13" s="111"/>
-      <x:c r="N13" s="48"/>
-      <x:c r="O13" s="48"/>
-      <x:c r="P13" s="48"/>
-    </x:row>
-    <x:row r="14" ht="21" customHeight="1">
-      <x:c r="A14" s="48"/>
-      <x:c r="B14" s="48"/>
-      <x:c r="C14" s="48"/>
-      <x:c r="D14" s="110"/>
-      <x:c r="E14" s="112"/>
-      <x:c r="F14" s="112"/>
-      <x:c r="G14" s="112"/>
-      <x:c r="H14" s="112"/>
-      <x:c r="I14" s="112"/>
-      <x:c r="J14" s="112"/>
-      <x:c r="K14" s="112"/>
-      <x:c r="L14" s="112"/>
-      <x:c r="M14" s="111"/>
-      <x:c r="N14" s="48"/>
-      <x:c r="O14" s="48"/>
-      <x:c r="P14" s="48"/>
-    </x:row>
-    <x:row r="15" ht="21" customHeight="1">
-      <x:c r="A15" s="48"/>
-      <x:c r="B15" s="48"/>
-      <x:c r="C15" s="48"/>
-      <x:c r="D15" s="110"/>
-      <x:c r="E15" s="113" t="str">
-        <x:v>3. 確認</x:v>
-      </x:c>
-      <x:c r="F15" s="113" t="str">
-        <x:v>3. 確認</x:v>
-      </x:c>
-      <x:c r="G15" s="113" t="str">
-        <x:v>3. 確認</x:v>
-      </x:c>
-      <x:c r="H15" s="85" t="str">
-        <x:v>********</x:v>
-      </x:c>
-      <x:c r="I15" s="85" t="str">
-        <x:v>********</x:v>
-      </x:c>
-      <x:c r="J15" s="85" t="str">
-        <x:v>********</x:v>
-      </x:c>
-      <x:c r="K15" s="85" t="str">
-        <x:v>********</x:v>
-      </x:c>
-      <x:c r="L15" s="85" t="str">
-        <x:v>********</x:v>
-      </x:c>
-      <x:c r="M15" s="111"/>
-      <x:c r="N15" s="48"/>
-      <x:c r="O15" s="48"/>
-      <x:c r="P15" s="48"/>
-    </x:row>
-    <x:row r="16" ht="21" customHeight="1">
-      <x:c r="A16" s="48"/>
-      <x:c r="B16" s="48"/>
-      <x:c r="C16" s="48"/>
-      <x:c r="D16" s="110"/>
-      <x:c r="E16" s="112"/>
-      <x:c r="F16" s="112"/>
-      <x:c r="G16" s="112"/>
-      <x:c r="H16" s="112"/>
-      <x:c r="I16" s="112"/>
-      <x:c r="J16" s="112"/>
-      <x:c r="K16" s="112"/>
-      <x:c r="L16" s="112"/>
-      <x:c r="M16" s="111"/>
-      <x:c r="N16" s="48"/>
-      <x:c r="O16" s="48"/>
-      <x:c r="P16" s="48"/>
-    </x:row>
-    <x:row r="17" ht="21" customHeight="1">
-      <x:c r="A17" s="48"/>
-      <x:c r="B17" s="48"/>
-      <x:c r="C17" s="48"/>
-      <x:c r="D17" s="110"/>
-      <x:c r="E17" s="99" t="str">
-        <x:v>保存</x:v>
-      </x:c>
-      <x:c r="F17" s="100" t="str">
-        <x:v>保存</x:v>
-      </x:c>
-      <x:c r="G17" s="100" t="str">
-        <x:v>保存</x:v>
-      </x:c>
-      <x:c r="H17" s="100" t="str">
-        <x:v>保存</x:v>
-      </x:c>
-      <x:c r="I17" s="100" t="str">
-        <x:v>保存</x:v>
-      </x:c>
-      <x:c r="J17" s="100" t="str">
-        <x:v>保存</x:v>
-      </x:c>
-      <x:c r="K17" s="100" t="str">
-        <x:v>保存</x:v>
-      </x:c>
-      <x:c r="L17" s="101" t="str">
-        <x:v>保存</x:v>
-      </x:c>
-      <x:c r="M17" s="111"/>
-      <x:c r="N17" s="48"/>
-      <x:c r="O17" s="48"/>
-      <x:c r="P17" s="48"/>
-    </x:row>
-    <x:row r="18" ht="21" customHeight="1">
-      <x:c r="A18" s="48"/>
-      <x:c r="B18" s="48"/>
-      <x:c r="C18" s="48"/>
-      <x:c r="D18" s="110"/>
-      <x:c r="E18" s="102" t="str">
-        <x:v>保存</x:v>
-      </x:c>
-      <x:c r="F18" s="103" t="str">
-        <x:v>保存</x:v>
-      </x:c>
-      <x:c r="G18" s="103" t="str">
-        <x:v>保存</x:v>
-      </x:c>
-      <x:c r="H18" s="103" t="str">
-        <x:v>保存</x:v>
-      </x:c>
-      <x:c r="I18" s="103" t="str">
-        <x:v>保存</x:v>
-      </x:c>
-      <x:c r="J18" s="103" t="str">
-        <x:v>保存</x:v>
-      </x:c>
-      <x:c r="K18" s="103" t="str">
-        <x:v>保存</x:v>
-      </x:c>
-      <x:c r="L18" s="104" t="str">
-        <x:v>保存</x:v>
-      </x:c>
-      <x:c r="M18" s="111"/>
-      <x:c r="N18" s="48"/>
-      <x:c r="O18" s="48"/>
-      <x:c r="P18" s="48"/>
-    </x:row>
-    <x:row r="19" ht="21" customHeight="1">
-      <x:c r="A19" s="48"/>
-      <x:c r="B19" s="48"/>
-      <x:c r="C19" s="48"/>
-      <x:c r="D19" s="110"/>
-      <x:c r="E19" s="112"/>
-      <x:c r="F19" s="112"/>
-      <x:c r="G19" s="112"/>
-      <x:c r="H19" s="112"/>
-      <x:c r="I19" s="112"/>
-      <x:c r="J19" s="112"/>
-      <x:c r="K19" s="112"/>
-      <x:c r="L19" s="112"/>
-      <x:c r="M19" s="111"/>
-      <x:c r="N19" s="48"/>
-      <x:c r="O19" s="48"/>
-      <x:c r="P19" s="48"/>
-    </x:row>
-    <x:row r="20" ht="21" customHeight="1">
-      <x:c r="A20" s="48"/>
-      <x:c r="B20" s="48"/>
-      <x:c r="C20" s="48"/>
-      <x:c r="D20" s="110"/>
-      <x:c r="E20" s="112"/>
-      <x:c r="F20" s="112"/>
-      <x:c r="G20" s="112"/>
-      <x:c r="H20" s="112"/>
-      <x:c r="I20" s="112"/>
-      <x:c r="J20" s="112"/>
-      <x:c r="K20" s="112"/>
-      <x:c r="L20" s="112"/>
-      <x:c r="M20" s="111"/>
-      <x:c r="N20" s="48"/>
-      <x:c r="O20" s="48"/>
-      <x:c r="P20" s="48"/>
-    </x:row>
-    <x:row r="21" ht="21" customHeight="1">
-      <x:c r="A21" s="48"/>
-      <x:c r="B21" s="48"/>
-      <x:c r="C21" s="48"/>
-      <x:c r="D21" s="110"/>
-      <x:c r="E21" s="112"/>
-      <x:c r="F21" s="112"/>
-      <x:c r="G21" s="112"/>
-      <x:c r="H21" s="112"/>
-      <x:c r="I21" s="112"/>
-      <x:c r="J21" s="112"/>
-      <x:c r="K21" s="112"/>
-      <x:c r="L21" s="112"/>
-      <x:c r="M21" s="111"/>
-      <x:c r="N21" s="48"/>
-      <x:c r="O21" s="48"/>
-      <x:c r="P21" s="48"/>
-    </x:row>
-    <x:row r="22" ht="21" customHeight="1">
-      <x:c r="A22" s="48"/>
-      <x:c r="B22" s="48"/>
-      <x:c r="C22" s="48"/>
-      <x:c r="D22" s="110"/>
-      <x:c r="E22" s="112"/>
-      <x:c r="F22" s="112"/>
-      <x:c r="G22" s="112"/>
-      <x:c r="H22" s="112"/>
-      <x:c r="I22" s="112"/>
-      <x:c r="J22" s="112"/>
-      <x:c r="K22" s="112"/>
-      <x:c r="L22" s="112"/>
-      <x:c r="M22" s="111"/>
-      <x:c r="N22" s="48"/>
-      <x:c r="O22" s="48"/>
-      <x:c r="P22" s="48"/>
-    </x:row>
-    <x:row r="23" ht="21" customHeight="1">
-      <x:c r="A23" s="48"/>
-      <x:c r="B23" s="48"/>
-      <x:c r="C23" s="48"/>
-      <x:c r="D23" s="110"/>
-      <x:c r="E23" s="112"/>
-      <x:c r="F23" s="112"/>
-      <x:c r="G23" s="112"/>
-      <x:c r="H23" s="112"/>
-      <x:c r="I23" s="112"/>
-      <x:c r="J23" s="112"/>
-      <x:c r="K23" s="112"/>
-      <x:c r="L23" s="112"/>
-      <x:c r="M23" s="111"/>
-      <x:c r="N23" s="48"/>
-      <x:c r="O23" s="48"/>
-      <x:c r="P23" s="48"/>
-    </x:row>
-    <x:row r="24" ht="21" customHeight="1">
-      <x:c r="A24" s="48"/>
-      <x:c r="B24" s="48"/>
-      <x:c r="C24" s="48"/>
-      <x:c r="D24" s="110"/>
-      <x:c r="E24" s="112"/>
-      <x:c r="F24" s="112"/>
-      <x:c r="G24" s="112"/>
-      <x:c r="H24" s="112"/>
-      <x:c r="I24" s="112"/>
-      <x:c r="J24" s="112"/>
-      <x:c r="K24" s="112"/>
-      <x:c r="L24" s="112"/>
-      <x:c r="M24" s="111"/>
-      <x:c r="N24" s="48"/>
-      <x:c r="O24" s="48"/>
-      <x:c r="P24" s="48"/>
-    </x:row>
-    <x:row r="25" ht="21" customHeight="1">
-      <x:c r="A25" s="48"/>
-      <x:c r="B25" s="48"/>
-      <x:c r="C25" s="48"/>
-      <x:c r="D25" s="110"/>
-      <x:c r="E25" s="112"/>
-      <x:c r="F25" s="112"/>
-      <x:c r="G25" s="112"/>
-      <x:c r="H25" s="112"/>
-      <x:c r="I25" s="112"/>
-      <x:c r="J25" s="112"/>
-      <x:c r="K25" s="112"/>
-      <x:c r="L25" s="112"/>
-      <x:c r="M25" s="111"/>
-      <x:c r="N25" s="48"/>
-      <x:c r="O25" s="48"/>
-      <x:c r="P25" s="48"/>
-    </x:row>
-    <x:row r="26" ht="21" customHeight="1">
-      <x:c r="A26" s="48"/>
-      <x:c r="B26" s="48"/>
-      <x:c r="C26" s="48"/>
-      <x:c r="D26" s="110"/>
-      <x:c r="E26" s="112"/>
-      <x:c r="F26" s="112"/>
-      <x:c r="G26" s="112"/>
-      <x:c r="H26" s="112"/>
-      <x:c r="I26" s="112"/>
-      <x:c r="J26" s="112"/>
-      <x:c r="K26" s="112"/>
-      <x:c r="L26" s="112"/>
-      <x:c r="M26" s="111"/>
-      <x:c r="N26" s="48"/>
-      <x:c r="O26" s="48"/>
-      <x:c r="P26" s="48"/>
-    </x:row>
-    <x:row r="27" ht="21" customHeight="1">
-      <x:c r="A27" s="48"/>
-      <x:c r="B27" s="48"/>
-      <x:c r="C27" s="48"/>
-      <x:c r="D27" s="115"/>
-      <x:c r="E27" s="116"/>
-      <x:c r="F27" s="116"/>
-      <x:c r="G27" s="116"/>
-      <x:c r="H27" s="116"/>
-      <x:c r="I27" s="116"/>
-      <x:c r="J27" s="116"/>
-      <x:c r="K27" s="116"/>
-      <x:c r="L27" s="116"/>
-      <x:c r="M27" s="117"/>
-      <x:c r="N27" s="48"/>
-      <x:c r="O27" s="48"/>
-      <x:c r="P27" s="48"/>
-    </x:row>
-    <x:row r="28" ht="21" customHeight="1">
-      <x:c r="A28" s="48"/>
-      <x:c r="B28" s="48"/>
-      <x:c r="C28" s="48"/>
-      <x:c r="D28" s="48"/>
-      <x:c r="E28" s="48"/>
-      <x:c r="F28" s="48"/>
-      <x:c r="G28" s="48"/>
-      <x:c r="H28" s="48"/>
-      <x:c r="I28" s="48"/>
-      <x:c r="J28" s="48"/>
-      <x:c r="K28" s="48"/>
-      <x:c r="L28" s="48"/>
-      <x:c r="M28" s="48"/>
-      <x:c r="N28" s="48"/>
-      <x:c r="O28" s="48"/>
-      <x:c r="P28" s="48"/>
-    </x:row>
-    <x:row r="29" ht="21" customHeight="1">
-      <x:c r="A29" s="48"/>
-      <x:c r="B29" s="48"/>
-      <x:c r="C29" s="48"/>
-      <x:c r="D29" s="48"/>
-      <x:c r="E29" s="48"/>
-      <x:c r="F29" s="48"/>
-      <x:c r="G29" s="48"/>
-      <x:c r="H29" s="48"/>
-      <x:c r="I29" s="48"/>
-      <x:c r="J29" s="48"/>
-      <x:c r="K29" s="48"/>
-      <x:c r="L29" s="48"/>
-      <x:c r="M29" s="48"/>
-      <x:c r="N29" s="48"/>
-      <x:c r="O29" s="48"/>
-      <x:c r="P29" s="48"/>
-    </x:row>
-    <x:row r="30" ht="21" customHeight="1">
-      <x:c r="A30" s="48"/>
-      <x:c r="B30" s="48"/>
-      <x:c r="C30" s="48"/>
-      <x:c r="D30" s="48"/>
-      <x:c r="E30" s="48"/>
-      <x:c r="F30" s="48"/>
-      <x:c r="G30" s="48"/>
-      <x:c r="H30" s="48"/>
-      <x:c r="I30" s="48"/>
-      <x:c r="J30" s="48"/>
-      <x:c r="K30" s="48"/>
-      <x:c r="L30" s="48"/>
-      <x:c r="M30" s="48"/>
-      <x:c r="N30" s="48"/>
-      <x:c r="O30" s="48"/>
-      <x:c r="P30" s="48"/>
-    </x:row>
-    <x:row r="31" ht="21" customHeight="1">
-      <x:c r="A31" s="48"/>
-      <x:c r="B31" s="48"/>
-      <x:c r="C31" s="48"/>
-      <x:c r="D31" s="48"/>
-      <x:c r="E31" s="48"/>
-      <x:c r="F31" s="48"/>
-      <x:c r="G31" s="48"/>
-      <x:c r="H31" s="48"/>
-      <x:c r="I31" s="48"/>
-      <x:c r="J31" s="48"/>
-      <x:c r="K31" s="48"/>
-      <x:c r="L31" s="48"/>
-      <x:c r="M31" s="48"/>
-      <x:c r="N31" s="48"/>
-      <x:c r="O31" s="48"/>
-      <x:c r="P31" s="48"/>
-    </x:row>
-    <x:row r="32" ht="21" customHeight="1">
-      <x:c r="A32"/>
-      <x:c r="B32"/>
-      <x:c r="C32"/>
-      <x:c r="D32"/>
-      <x:c r="E32"/>
-      <x:c r="F32"/>
-      <x:c r="G32"/>
-      <x:c r="H32"/>
-      <x:c r="I32"/>
-      <x:c r="J32"/>
-      <x:c r="K32"/>
-      <x:c r="L32"/>
-      <x:c r="M32"/>
-      <x:c r="N32"/>
-      <x:c r="O32"/>
-      <x:c r="P32"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:P1"/>
-    <x:mergeCell ref="A2:H2"/>
-    <x:mergeCell ref="I2:P2"/>
-    <x:mergeCell ref="A32:P32"/>
-    <x:mergeCell ref="A4:P5"/>
-    <x:mergeCell ref="E8:L9"/>
-    <x:mergeCell ref="E11:G11"/>
-    <x:mergeCell ref="H11:L11"/>
-    <x:mergeCell ref="E13:G13"/>
-    <x:mergeCell ref="H13:L13"/>
-    <x:mergeCell ref="E15:G15"/>
-    <x:mergeCell ref="H15:L15"/>
-    <x:mergeCell ref="E17:L18"/>
+    <x:mergeCell ref="A1:D1"/>
+    <x:mergeCell ref="A3:D3"/>
+    <x:mergeCell ref="A5:D5"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
